--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2156" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2162" uniqueCount="431">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -949,10 +949,10 @@
     <t>['44', '63', '76', '84', '86']</t>
   </si>
   <si>
-    <t>['25', '32', '37', '44', '56']</t>
+    <t>['60', '72']</t>
   </si>
   <si>
-    <t>['60', '72']</t>
+    <t>['25', '32', '37', '44', '56']</t>
   </si>
   <si>
     <t>['32', '75']</t>
@@ -965,6 +965,9 @@
   </si>
   <si>
     <t>['28', '78']</t>
+  </si>
+  <si>
+    <t>['39', '78']</t>
   </si>
   <si>
     <t>['67', '88']</t>
@@ -1300,10 +1303,10 @@
     <t>['61']</t>
   </si>
   <si>
-    <t>['72', '88']</t>
+    <t>['58', '90']</t>
   </si>
   <si>
-    <t>['58', '90']</t>
+    <t>['72', '88']</t>
   </si>
 </sst>
 </file>
@@ -1665,7 +1668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP349"/>
+  <dimension ref="A1:BP350"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1921,7 +1924,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -1999,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ2">
         <v>0.47</v>
@@ -2127,7 +2130,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2333,7 +2336,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2745,7 +2748,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -3157,7 +3160,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3569,7 +3572,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -4187,7 +4190,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4393,7 +4396,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -5217,7 +5220,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5710,7 +5713,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ20">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5835,7 +5838,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -6041,7 +6044,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6865,7 +6868,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -7689,7 +7692,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -8591,7 +8594,7 @@
         <v>0</v>
       </c>
       <c r="AP34">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ34">
         <v>0.57</v>
@@ -8719,7 +8722,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8925,7 +8928,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9337,7 +9340,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9749,7 +9752,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -9955,7 +9958,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10367,7 +10370,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -11478,7 +11481,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ48">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR48">
         <v>1.23</v>
@@ -11809,7 +11812,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -13045,7 +13048,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13741,7 +13744,7 @@
         <v>0.5</v>
       </c>
       <c r="AP59">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ59">
         <v>1</v>
@@ -13869,7 +13872,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13950,7 +13953,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ60">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR60">
         <v>1.85</v>
@@ -14075,7 +14078,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14281,7 +14284,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -15105,7 +15108,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15723,7 +15726,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -16135,7 +16138,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16753,7 +16756,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -17037,7 +17040,7 @@
         <v>1.67</v>
       </c>
       <c r="AP75">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ75">
         <v>1.29</v>
@@ -17165,7 +17168,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17371,7 +17374,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17783,7 +17786,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -18195,7 +18198,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -18276,7 +18279,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ81">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR81">
         <v>1.39</v>
@@ -19843,7 +19846,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -20461,7 +20464,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -21697,7 +21700,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -22396,7 +22399,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ101">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22521,7 +22524,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22727,7 +22730,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -25199,7 +25202,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25405,7 +25408,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25817,7 +25820,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -26101,7 +26104,7 @@
         <v>0.75</v>
       </c>
       <c r="AP119">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ119">
         <v>0.93</v>
@@ -26847,7 +26850,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -27053,7 +27056,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -28367,7 +28370,7 @@
         <v>2</v>
       </c>
       <c r="AP130">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ130">
         <v>1.27</v>
@@ -28495,7 +28498,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -29113,7 +29116,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29525,7 +29528,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -30761,7 +30764,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -30842,7 +30845,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ142">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR142">
         <v>1.64</v>
@@ -31379,7 +31382,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31585,7 +31588,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31791,7 +31794,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -31997,7 +32000,7 @@
         <v>199</v>
       </c>
       <c r="P148" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q148">
         <v>2.88</v>
@@ -32203,7 +32206,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32281,7 +32284,7 @@
         <v>1.33</v>
       </c>
       <c r="AP149">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ149">
         <v>1.87</v>
@@ -32409,7 +32412,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32821,7 +32824,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33233,7 +33236,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33645,7 +33648,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -34057,7 +34060,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34675,7 +34678,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -35499,7 +35502,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35577,7 +35580,7 @@
         <v>0.67</v>
       </c>
       <c r="AP165">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ165">
         <v>0.71</v>
@@ -35705,7 +35708,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q166">
         <v>2.5</v>
@@ -36941,7 +36944,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37147,7 +37150,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37559,7 +37562,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -37846,7 +37849,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ176">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR176">
         <v>1.24</v>
@@ -37971,7 +37974,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38589,7 +38592,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -39001,7 +39004,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39413,7 +39416,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -40237,7 +40240,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40855,7 +40858,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41061,7 +41064,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41554,7 +41557,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ194">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR194">
         <v>1.32</v>
@@ -41885,7 +41888,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -42915,7 +42918,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -44151,7 +44154,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44435,7 +44438,7 @@
         <v>1.63</v>
       </c>
       <c r="AP208">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ208">
         <v>1.57</v>
@@ -44769,7 +44772,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44975,7 +44978,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45387,7 +45390,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45593,7 +45596,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45799,7 +45802,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -46498,7 +46501,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ218">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR218">
         <v>1.44</v>
@@ -47653,7 +47656,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47859,7 +47862,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -48271,7 +48274,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q227">
         <v>3</v>
@@ -48683,7 +48686,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49507,7 +49510,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49713,7 +49716,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -49794,7 +49797,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ234">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR234">
         <v>1.65</v>
@@ -50949,7 +50952,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51567,7 +51570,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51773,7 +51776,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -52185,7 +52188,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52469,7 +52472,7 @@
         <v>0.44</v>
       </c>
       <c r="AP247">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ247">
         <v>0.29</v>
@@ -52803,7 +52806,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53421,7 +53424,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53833,7 +53836,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54863,7 +54866,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -55069,7 +55072,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55150,7 +55153,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ260">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR260">
         <v>1.65</v>
@@ -55481,7 +55484,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -56099,7 +56102,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56305,7 +56308,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56923,7 +56926,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57001,7 +57004,7 @@
         <v>1.64</v>
       </c>
       <c r="AP269">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ269">
         <v>1.53</v>
@@ -57541,7 +57544,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57747,7 +57750,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -58159,7 +58162,7 @@
         <v>278</v>
       </c>
       <c r="P275" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q275">
         <v>3.2</v>
@@ -58365,7 +58368,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58571,7 +58574,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58777,7 +58780,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -59473,7 +59476,7 @@
         <v>0.73</v>
       </c>
       <c r="AP281">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ281">
         <v>1.21</v>
@@ -60631,7 +60634,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -61043,7 +61046,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61124,7 +61127,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ289">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR289">
         <v>1.34</v>
@@ -61249,7 +61252,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -62073,7 +62076,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62691,7 +62694,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63387,7 +63390,7 @@
         <v>1.92</v>
       </c>
       <c r="AP300">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ300">
         <v>2.07</v>
@@ -63515,7 +63518,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63721,7 +63724,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -64133,7 +64136,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64339,7 +64342,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64751,7 +64754,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -65369,7 +65372,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -65859,7 +65862,7 @@
         <v>0.54</v>
       </c>
       <c r="AP312">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ312">
         <v>0.47</v>
@@ -67429,7 +67432,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -67922,7 +67925,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ322">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR322">
         <v>1.41</v>
@@ -68459,7 +68462,7 @@
         <v>302</v>
       </c>
       <c r="P325" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q325">
         <v>2.5</v>
@@ -68540,7 +68543,7 @@
         <v>2.07</v>
       </c>
       <c r="AQ325">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="AR325">
         <v>1.43</v>
@@ -68665,7 +68668,7 @@
         <v>303</v>
       </c>
       <c r="P326" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q326">
         <v>3</v>
@@ -69077,7 +69080,7 @@
         <v>296</v>
       </c>
       <c r="P328" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69489,7 +69492,7 @@
         <v>95</v>
       </c>
       <c r="P330" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q330">
         <v>3.4</v>
@@ -69567,7 +69570,7 @@
         <v>0.79</v>
       </c>
       <c r="AP330">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AQ330">
         <v>0.93</v>
@@ -69695,7 +69698,7 @@
         <v>305</v>
       </c>
       <c r="P331" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q331">
         <v>2.88</v>
@@ -69901,7 +69904,7 @@
         <v>306</v>
       </c>
       <c r="P332" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q332">
         <v>2.63</v>
@@ -70313,7 +70316,7 @@
         <v>308</v>
       </c>
       <c r="P334" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q334">
         <v>3.1</v>
@@ -70519,7 +70522,7 @@
         <v>309</v>
       </c>
       <c r="P335" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q335">
         <v>3</v>
@@ -70725,7 +70728,7 @@
         <v>95</v>
       </c>
       <c r="P336" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q336">
         <v>5.5</v>
@@ -70931,7 +70934,7 @@
         <v>95</v>
       </c>
       <c r="P337" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q337">
         <v>2.2</v>
@@ -71137,7 +71140,7 @@
         <v>95</v>
       </c>
       <c r="P338" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q338">
         <v>2.75</v>
@@ -71713,7 +71716,7 @@
         <v>340</v>
       </c>
       <c r="B341">
-        <v>7479091</v>
+        <v>7479090</v>
       </c>
       <c r="C341" t="s">
         <v>68</v>
@@ -71728,82 +71731,82 @@
         <v>29</v>
       </c>
       <c r="G341" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="H341" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="I341">
+        <v>0</v>
+      </c>
+      <c r="J341">
+        <v>0</v>
+      </c>
+      <c r="K341">
+        <v>0</v>
+      </c>
+      <c r="L341">
+        <v>2</v>
+      </c>
+      <c r="M341">
+        <v>2</v>
+      </c>
+      <c r="N341">
         <v>4</v>
-      </c>
-      <c r="J341">
-        <v>0</v>
-      </c>
-      <c r="K341">
-        <v>4</v>
-      </c>
-      <c r="L341">
-        <v>5</v>
-      </c>
-      <c r="M341">
-        <v>1</v>
-      </c>
-      <c r="N341">
-        <v>6</v>
       </c>
       <c r="O341" t="s">
         <v>311</v>
       </c>
       <c r="P341" t="s">
-        <v>136</v>
+        <v>429</v>
       </c>
       <c r="Q341">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="R341">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S341">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="T341">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U341">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="V341">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="W341">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="X341">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y341">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z341">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AA341">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AB341">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AC341">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD341">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AE341">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AF341">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AG341">
         <v>1.76</v>
@@ -71812,106 +71815,106 @@
         <v>1.95</v>
       </c>
       <c r="AI341">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AJ341">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AK341">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AL341">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AM341">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AN341">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="AO341">
-        <v>0.5</v>
+        <v>0.21</v>
       </c>
       <c r="AP341">
-        <v>1.79</v>
+        <v>2.29</v>
       </c>
       <c r="AQ341">
-        <v>0.47</v>
+        <v>0.27</v>
       </c>
       <c r="AR341">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AS341">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="AT341">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AU341">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AV341">
         <v>4</v>
       </c>
       <c r="AW341">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX341">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AY341">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ341">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="BA341">
         <v>7</v>
       </c>
       <c r="BB341">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC341">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BD341">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="BE341">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="BF341">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="BG341">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="BH341">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="BI341">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="BJ341">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="BK341">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="BL341">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="BM341">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="BN341">
-        <v>1.95</v>
+        <v>1.72</v>
       </c>
       <c r="BO341">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="BP341">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="342" spans="1:68">
@@ -71961,7 +71964,7 @@
         <v>95</v>
       </c>
       <c r="P342" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Q342">
         <v>3.2</v>
@@ -72125,7 +72128,7 @@
         <v>342</v>
       </c>
       <c r="B343">
-        <v>7479090</v>
+        <v>7479091</v>
       </c>
       <c r="C343" t="s">
         <v>68</v>
@@ -72140,82 +72143,82 @@
         <v>29</v>
       </c>
       <c r="G343" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="H343" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="I343">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J343">
         <v>0</v>
       </c>
       <c r="K343">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L343">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M343">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N343">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O343" t="s">
         <v>312</v>
       </c>
       <c r="P343" t="s">
-        <v>429</v>
+        <v>136</v>
       </c>
       <c r="Q343">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="R343">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S343">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="T343">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U343">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="V343">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="W343">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="X343">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y343">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z343">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AA343">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="AB343">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AC343">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD343">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE343">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AF343">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AG343">
         <v>1.76</v>
@@ -72224,106 +72227,106 @@
         <v>1.95</v>
       </c>
       <c r="AI343">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AJ343">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AK343">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AL343">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AM343">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="AN343">
+        <v>1.69</v>
+      </c>
+      <c r="AO343">
+        <v>0.5</v>
+      </c>
+      <c r="AP343">
+        <v>1.79</v>
+      </c>
+      <c r="AQ343">
+        <v>0.47</v>
+      </c>
+      <c r="AR343">
+        <v>1.42</v>
+      </c>
+      <c r="AS343">
+        <v>0.96</v>
+      </c>
+      <c r="AT343">
         <v>2.38</v>
       </c>
-      <c r="AO343">
-        <v>0.21</v>
-      </c>
-      <c r="AP343">
-        <v>2.29</v>
-      </c>
-      <c r="AQ343">
-        <v>0.27</v>
-      </c>
-      <c r="AR343">
-        <v>1.59</v>
-      </c>
-      <c r="AS343">
-        <v>0.75</v>
-      </c>
-      <c r="AT343">
-        <v>2.34</v>
-      </c>
       <c r="AU343">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AV343">
         <v>4</v>
       </c>
       <c r="AW343">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AX343">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AY343">
+        <v>22</v>
+      </c>
+      <c r="AZ343">
         <v>17</v>
-      </c>
-      <c r="AZ343">
-        <v>8</v>
       </c>
       <c r="BA343">
         <v>7</v>
       </c>
       <c r="BB343">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC343">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BD343">
-        <v>1.18</v>
+        <v>1.45</v>
       </c>
       <c r="BE343">
-        <v>9.5</v>
+        <v>7.5</v>
       </c>
       <c r="BF343">
-        <v>5.1</v>
+        <v>3.05</v>
       </c>
       <c r="BG343">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="BH343">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BI343">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="BJ343">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="BK343">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="BL343">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="BM343">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="BN343">
-        <v>1.72</v>
+        <v>1.95</v>
       </c>
       <c r="BO343">
-        <v>2.48</v>
+        <v>2.14</v>
       </c>
       <c r="BP343">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="344" spans="1:68">
@@ -72579,7 +72582,7 @@
         <v>314</v>
       </c>
       <c r="P345" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q345">
         <v>3</v>
@@ -73560,6 +73563,212 @@
       </c>
       <c r="BP349">
         <v>1.74</v>
+      </c>
+    </row>
+    <row r="350" spans="1:68">
+      <c r="A350" s="1">
+        <v>349</v>
+      </c>
+      <c r="B350">
+        <v>7479092</v>
+      </c>
+      <c r="C350" t="s">
+        <v>68</v>
+      </c>
+      <c r="D350" t="s">
+        <v>69</v>
+      </c>
+      <c r="E350" s="2">
+        <v>45688.70833333334</v>
+      </c>
+      <c r="F350">
+        <v>30</v>
+      </c>
+      <c r="G350" t="s">
+        <v>70</v>
+      </c>
+      <c r="H350" t="s">
+        <v>71</v>
+      </c>
+      <c r="I350">
+        <v>1</v>
+      </c>
+      <c r="J350">
+        <v>0</v>
+      </c>
+      <c r="K350">
+        <v>1</v>
+      </c>
+      <c r="L350">
+        <v>2</v>
+      </c>
+      <c r="M350">
+        <v>1</v>
+      </c>
+      <c r="N350">
+        <v>3</v>
+      </c>
+      <c r="O350" t="s">
+        <v>317</v>
+      </c>
+      <c r="P350" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q350">
+        <v>2.88</v>
+      </c>
+      <c r="R350">
+        <v>2.05</v>
+      </c>
+      <c r="S350">
+        <v>4.33</v>
+      </c>
+      <c r="T350">
+        <v>1.5</v>
+      </c>
+      <c r="U350">
+        <v>2.5</v>
+      </c>
+      <c r="V350">
+        <v>3.4</v>
+      </c>
+      <c r="W350">
+        <v>1.3</v>
+      </c>
+      <c r="X350">
+        <v>10</v>
+      </c>
+      <c r="Y350">
+        <v>1.06</v>
+      </c>
+      <c r="Z350">
+        <v>2.06</v>
+      </c>
+      <c r="AA350">
+        <v>3.28</v>
+      </c>
+      <c r="AB350">
+        <v>3.76</v>
+      </c>
+      <c r="AC350">
+        <v>1.08</v>
+      </c>
+      <c r="AD350">
+        <v>7.5</v>
+      </c>
+      <c r="AE350">
+        <v>1.4</v>
+      </c>
+      <c r="AF350">
+        <v>2.9</v>
+      </c>
+      <c r="AG350">
+        <v>2.19</v>
+      </c>
+      <c r="AH350">
+        <v>1.68</v>
+      </c>
+      <c r="AI350">
+        <v>1.91</v>
+      </c>
+      <c r="AJ350">
+        <v>1.8</v>
+      </c>
+      <c r="AK350">
+        <v>1.25</v>
+      </c>
+      <c r="AL350">
+        <v>1.28</v>
+      </c>
+      <c r="AM350">
+        <v>1.73</v>
+      </c>
+      <c r="AN350">
+        <v>1.73</v>
+      </c>
+      <c r="AO350">
+        <v>0.86</v>
+      </c>
+      <c r="AP350">
+        <v>1.81</v>
+      </c>
+      <c r="AQ350">
+        <v>0.8</v>
+      </c>
+      <c r="AR350">
+        <v>1.29</v>
+      </c>
+      <c r="AS350">
+        <v>1.09</v>
+      </c>
+      <c r="AT350">
+        <v>2.38</v>
+      </c>
+      <c r="AU350">
+        <v>3</v>
+      </c>
+      <c r="AV350">
+        <v>2</v>
+      </c>
+      <c r="AW350">
+        <v>11</v>
+      </c>
+      <c r="AX350">
+        <v>9</v>
+      </c>
+      <c r="AY350">
+        <v>18</v>
+      </c>
+      <c r="AZ350">
+        <v>13</v>
+      </c>
+      <c r="BA350">
+        <v>7</v>
+      </c>
+      <c r="BB350">
+        <v>3</v>
+      </c>
+      <c r="BC350">
+        <v>10</v>
+      </c>
+      <c r="BD350">
+        <v>1.65</v>
+      </c>
+      <c r="BE350">
+        <v>6.75</v>
+      </c>
+      <c r="BF350">
+        <v>2.48</v>
+      </c>
+      <c r="BG350">
+        <v>1.22</v>
+      </c>
+      <c r="BH350">
+        <v>3.82</v>
+      </c>
+      <c r="BI350">
+        <v>1.45</v>
+      </c>
+      <c r="BJ350">
+        <v>2.66</v>
+      </c>
+      <c r="BK350">
+        <v>1.78</v>
+      </c>
+      <c r="BL350">
+        <v>2.04</v>
+      </c>
+      <c r="BM350">
+        <v>2.22</v>
+      </c>
+      <c r="BN350">
+        <v>1.65</v>
+      </c>
+      <c r="BO350">
+        <v>2.92</v>
+      </c>
+      <c r="BP350">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="438">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -979,6 +979,9 @@
     <t>['1', '25']</t>
   </si>
   <si>
+    <t>['11', '59']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -1322,6 +1325,9 @@
   </si>
   <si>
     <t>['43', '74']</t>
+  </si>
+  <si>
+    <t>['33', '51', '87']</t>
   </si>
 </sst>
 </file>
@@ -1683,7 +1689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP360"/>
+  <dimension ref="A1:BP361"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1939,7 +1945,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -2145,7 +2151,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2351,7 +2357,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2763,7 +2769,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -3175,7 +3181,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3587,7 +3593,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -3668,7 +3674,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ10">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3871,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ11">
         <v>0.93</v>
@@ -4205,7 +4211,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4411,7 +4417,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -5235,7 +5241,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5853,7 +5859,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -6059,7 +6065,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6883,7 +6889,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -7707,7 +7713,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -7785,7 +7791,7 @@
         <v>1</v>
       </c>
       <c r="AP30">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ30">
         <v>0.47</v>
@@ -8737,7 +8743,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8943,7 +8949,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9355,7 +9361,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9767,7 +9773,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -9973,7 +9979,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10385,7 +10391,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -10466,7 +10472,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ43">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR43">
         <v>1.59</v>
@@ -11827,7 +11833,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -13063,7 +13069,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13144,7 +13150,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ56">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR56">
         <v>1.63</v>
@@ -13887,7 +13893,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13965,7 +13971,7 @@
         <v>0</v>
       </c>
       <c r="AP60">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ60">
         <v>0.8</v>
@@ -14093,7 +14099,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14299,7 +14305,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -15123,7 +15129,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15741,7 +15747,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -16153,7 +16159,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16771,7 +16777,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -17183,7 +17189,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17389,7 +17395,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17801,7 +17807,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17882,7 +17888,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ79">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR79">
         <v>1.74</v>
@@ -18085,7 +18091,7 @@
         <v>1</v>
       </c>
       <c r="AP80">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ80">
         <v>0.87</v>
@@ -18213,7 +18219,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -19861,7 +19867,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -20479,7 +20485,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -21715,7 +21721,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -22539,7 +22545,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22745,7 +22751,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -25217,7 +25223,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25423,7 +25429,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25835,7 +25841,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -25913,7 +25919,7 @@
         <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ118">
         <v>1</v>
@@ -26534,7 +26540,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ121">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR121">
         <v>1.53</v>
@@ -26865,7 +26871,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -27071,7 +27077,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -28513,7 +28519,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -28594,7 +28600,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ131">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR131">
         <v>1.3</v>
@@ -29003,7 +29009,7 @@
         <v>1.6</v>
       </c>
       <c r="AP133">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ133">
         <v>1.94</v>
@@ -29131,7 +29137,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29543,7 +29549,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -30779,7 +30785,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -31397,7 +31403,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31603,7 +31609,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31809,7 +31815,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -32015,7 +32021,7 @@
         <v>199</v>
       </c>
       <c r="P148" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q148">
         <v>2.88</v>
@@ -32221,7 +32227,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32427,7 +32433,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32839,7 +32845,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33126,7 +33132,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ153">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR153">
         <v>1.73</v>
@@ -33251,7 +33257,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33663,7 +33669,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -33741,7 +33747,7 @@
         <v>0.5</v>
       </c>
       <c r="AP156">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ156">
         <v>1.06</v>
@@ -34075,7 +34081,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34693,7 +34699,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -35517,7 +35523,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35723,7 +35729,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q166">
         <v>2.5</v>
@@ -36216,7 +36222,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ168">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR168">
         <v>1.18</v>
@@ -36831,7 +36837,7 @@
         <v>0.67</v>
       </c>
       <c r="AP171">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ171">
         <v>0.33</v>
@@ -36959,7 +36965,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37165,7 +37171,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37577,7 +37583,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -37989,7 +37995,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38607,7 +38613,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -39019,7 +39025,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39431,7 +39437,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -40130,7 +40136,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ187">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR187">
         <v>1.36</v>
@@ -40255,7 +40261,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40873,7 +40879,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41079,7 +41085,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41903,7 +41909,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -42933,7 +42939,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -43217,7 +43223,7 @@
         <v>0.86</v>
       </c>
       <c r="AP202">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ202">
         <v>1.14</v>
@@ -43632,7 +43638,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ204">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR204">
         <v>1.53</v>
@@ -44169,7 +44175,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44247,7 +44253,7 @@
         <v>1</v>
       </c>
       <c r="AP207">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ207">
         <v>1.21</v>
@@ -44787,7 +44793,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44993,7 +44999,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45405,7 +45411,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45611,7 +45617,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45817,7 +45823,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -47671,7 +47677,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47877,7 +47883,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -48289,7 +48295,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q227">
         <v>3</v>
@@ -48701,7 +48707,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49525,7 +49531,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49731,7 +49737,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -50967,7 +50973,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51457,7 +51463,7 @@
         <v>1</v>
       </c>
       <c r="AP242">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ242">
         <v>1.14</v>
@@ -51585,7 +51591,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51791,7 +51797,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -51872,7 +51878,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ244">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR244">
         <v>1.43</v>
@@ -52203,7 +52209,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52821,7 +52827,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53439,7 +53445,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53851,7 +53857,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54881,7 +54887,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -55087,7 +55093,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55499,7 +55505,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -56117,7 +56123,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56323,7 +56329,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56401,7 +56407,7 @@
         <v>1.6</v>
       </c>
       <c r="AP266">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ266">
         <v>1.43</v>
@@ -56941,7 +56947,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57022,7 +57028,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ269">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR269">
         <v>1.31</v>
@@ -57559,7 +57565,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57765,7 +57771,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -58383,7 +58389,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58589,7 +58595,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58795,7 +58801,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -59082,7 +59088,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ279">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR279">
         <v>1.22</v>
@@ -60315,7 +60321,7 @@
         <v>2</v>
       </c>
       <c r="AP285">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ285">
         <v>2</v>
@@ -60649,7 +60655,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -61061,7 +61067,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61267,7 +61273,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -62091,7 +62097,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62709,7 +62715,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63533,7 +63539,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63739,7 +63745,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -64151,7 +64157,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64357,7 +64363,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64769,7 +64775,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -64847,7 +64853,7 @@
         <v>0.75</v>
       </c>
       <c r="AP307">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ307">
         <v>0.73</v>
@@ -65387,7 +65393,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -66086,7 +66092,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ313">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR313">
         <v>1.47</v>
@@ -67447,7 +67453,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -68477,7 +68483,7 @@
         <v>302</v>
       </c>
       <c r="P325" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q325">
         <v>2.5</v>
@@ -68683,7 +68689,7 @@
         <v>303</v>
       </c>
       <c r="P326" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q326">
         <v>3</v>
@@ -68967,7 +68973,7 @@
         <v>1.36</v>
       </c>
       <c r="AP327">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="AQ327">
         <v>1.19</v>
@@ -69095,7 +69101,7 @@
         <v>296</v>
       </c>
       <c r="P328" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69382,7 +69388,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ329">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AR329">
         <v>1.39</v>
@@ -69507,7 +69513,7 @@
         <v>95</v>
       </c>
       <c r="P330" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q330">
         <v>3.4</v>
@@ -69713,7 +69719,7 @@
         <v>305</v>
       </c>
       <c r="P331" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q331">
         <v>2.88</v>
@@ -69919,7 +69925,7 @@
         <v>306</v>
       </c>
       <c r="P332" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q332">
         <v>2.63</v>
@@ -70331,7 +70337,7 @@
         <v>308</v>
       </c>
       <c r="P334" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q334">
         <v>3.1</v>
@@ -70537,7 +70543,7 @@
         <v>309</v>
       </c>
       <c r="P335" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q335">
         <v>3</v>
@@ -70743,7 +70749,7 @@
         <v>95</v>
       </c>
       <c r="P336" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q336">
         <v>5.5</v>
@@ -70949,7 +70955,7 @@
         <v>95</v>
       </c>
       <c r="P337" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q337">
         <v>2.2</v>
@@ -71155,7 +71161,7 @@
         <v>95</v>
       </c>
       <c r="P338" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q338">
         <v>2.75</v>
@@ -71773,7 +71779,7 @@
         <v>311</v>
       </c>
       <c r="P341" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q341">
         <v>1.83</v>
@@ -71979,7 +71985,7 @@
         <v>95</v>
       </c>
       <c r="P342" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q342">
         <v>3.2</v>
@@ -72597,7 +72603,7 @@
         <v>314</v>
       </c>
       <c r="P345" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q345">
         <v>3</v>
@@ -73833,7 +73839,7 @@
         <v>95</v>
       </c>
       <c r="P351" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q351">
         <v>3.1</v>
@@ -73944,13 +73950,13 @@
         <v>23</v>
       </c>
       <c r="BA351">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB351">
         <v>6</v>
       </c>
       <c r="BC351">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD351">
         <v>1.7</v>
@@ -74245,7 +74251,7 @@
         <v>146</v>
       </c>
       <c r="P353" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q353">
         <v>5.5</v>
@@ -74451,7 +74457,7 @@
         <v>197</v>
       </c>
       <c r="P354" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q354">
         <v>2.75</v>
@@ -74863,7 +74869,7 @@
         <v>95</v>
       </c>
       <c r="P356" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q356">
         <v>3.2</v>
@@ -75275,7 +75281,7 @@
         <v>289</v>
       </c>
       <c r="P358" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q358">
         <v>2.63</v>
@@ -75481,7 +75487,7 @@
         <v>95</v>
       </c>
       <c r="P359" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q359">
         <v>4.33</v>
@@ -75844,6 +75850,212 @@
       </c>
       <c r="BP360">
         <v>1.55</v>
+      </c>
+    </row>
+    <row r="361" spans="1:68">
+      <c r="A361" s="1">
+        <v>360</v>
+      </c>
+      <c r="B361">
+        <v>7479095</v>
+      </c>
+      <c r="C361" t="s">
+        <v>68</v>
+      </c>
+      <c r="D361" t="s">
+        <v>69</v>
+      </c>
+      <c r="E361" s="2">
+        <v>45691.70833333334</v>
+      </c>
+      <c r="F361">
+        <v>30</v>
+      </c>
+      <c r="G361" t="s">
+        <v>79</v>
+      </c>
+      <c r="H361" t="s">
+        <v>93</v>
+      </c>
+      <c r="I361">
+        <v>1</v>
+      </c>
+      <c r="J361">
+        <v>1</v>
+      </c>
+      <c r="K361">
+        <v>2</v>
+      </c>
+      <c r="L361">
+        <v>2</v>
+      </c>
+      <c r="M361">
+        <v>3</v>
+      </c>
+      <c r="N361">
+        <v>5</v>
+      </c>
+      <c r="O361" t="s">
+        <v>321</v>
+      </c>
+      <c r="P361" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q361">
+        <v>3</v>
+      </c>
+      <c r="R361">
+        <v>2.2</v>
+      </c>
+      <c r="S361">
+        <v>3.6</v>
+      </c>
+      <c r="T361">
+        <v>1.4</v>
+      </c>
+      <c r="U361">
+        <v>2.75</v>
+      </c>
+      <c r="V361">
+        <v>2.75</v>
+      </c>
+      <c r="W361">
+        <v>1.4</v>
+      </c>
+      <c r="X361">
+        <v>8</v>
+      </c>
+      <c r="Y361">
+        <v>1.08</v>
+      </c>
+      <c r="Z361">
+        <v>2.21</v>
+      </c>
+      <c r="AA361">
+        <v>3.45</v>
+      </c>
+      <c r="AB361">
+        <v>3.04</v>
+      </c>
+      <c r="AC361">
+        <v>1.05</v>
+      </c>
+      <c r="AD361">
+        <v>11</v>
+      </c>
+      <c r="AE361">
+        <v>1.32</v>
+      </c>
+      <c r="AF361">
+        <v>3.4</v>
+      </c>
+      <c r="AG361">
+        <v>1.87</v>
+      </c>
+      <c r="AH361">
+        <v>1.87</v>
+      </c>
+      <c r="AI361">
+        <v>1.67</v>
+      </c>
+      <c r="AJ361">
+        <v>2.1</v>
+      </c>
+      <c r="AK361">
+        <v>1.37</v>
+      </c>
+      <c r="AL361">
+        <v>1.31</v>
+      </c>
+      <c r="AM361">
+        <v>1.58</v>
+      </c>
+      <c r="AN361">
+        <v>1.73</v>
+      </c>
+      <c r="AO361">
+        <v>1.53</v>
+      </c>
+      <c r="AP361">
+        <v>1.63</v>
+      </c>
+      <c r="AQ361">
+        <v>1.63</v>
+      </c>
+      <c r="AR361">
+        <v>1.49</v>
+      </c>
+      <c r="AS361">
+        <v>1.35</v>
+      </c>
+      <c r="AT361">
+        <v>2.84</v>
+      </c>
+      <c r="AU361">
+        <v>5</v>
+      </c>
+      <c r="AV361">
+        <v>10</v>
+      </c>
+      <c r="AW361">
+        <v>8</v>
+      </c>
+      <c r="AX361">
+        <v>3</v>
+      </c>
+      <c r="AY361">
+        <v>16</v>
+      </c>
+      <c r="AZ361">
+        <v>15</v>
+      </c>
+      <c r="BA361">
+        <v>1</v>
+      </c>
+      <c r="BB361">
+        <v>5</v>
+      </c>
+      <c r="BC361">
+        <v>6</v>
+      </c>
+      <c r="BD361">
+        <v>1.79</v>
+      </c>
+      <c r="BE361">
+        <v>6.75</v>
+      </c>
+      <c r="BF361">
+        <v>2.23</v>
+      </c>
+      <c r="BG361">
+        <v>1.21</v>
+      </c>
+      <c r="BH361">
+        <v>3.7</v>
+      </c>
+      <c r="BI361">
+        <v>1.38</v>
+      </c>
+      <c r="BJ361">
+        <v>2.75</v>
+      </c>
+      <c r="BK361">
+        <v>1.64</v>
+      </c>
+      <c r="BL361">
+        <v>2.1</v>
+      </c>
+      <c r="BM361">
+        <v>1.98</v>
+      </c>
+      <c r="BN361">
+        <v>1.72</v>
+      </c>
+      <c r="BO361">
+        <v>2.48</v>
+      </c>
+      <c r="BP361">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="440">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -982,6 +982,9 @@
     <t>['11', '59']</t>
   </si>
   <si>
+    <t>['5', '76']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -1328,6 +1331,9 @@
   </si>
   <si>
     <t>['33', '51', '87']</t>
+  </si>
+  <si>
+    <t>['17', '26']</t>
   </si>
 </sst>
 </file>
@@ -1689,7 +1695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP361"/>
+  <dimension ref="A1:BP364"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1945,7 +1951,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -2151,7 +2157,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2357,7 +2363,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2435,7 +2441,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ4">
         <v>1.19</v>
@@ -2769,7 +2775,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -3181,7 +3187,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3593,7 +3599,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -4211,7 +4217,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4417,7 +4423,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -4495,10 +4501,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ14">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4704,7 +4710,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ15">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5241,7 +5247,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5859,7 +5865,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -6065,7 +6071,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6146,7 +6152,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ22">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR22">
         <v>0</v>
@@ -6349,7 +6355,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ23">
         <v>0.73</v>
@@ -6889,7 +6895,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6970,7 +6976,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ26">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR26">
         <v>2.62</v>
@@ -7379,7 +7385,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ28">
         <v>0.27</v>
@@ -7713,7 +7719,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -8618,7 +8624,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ34">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR34">
         <v>1.56</v>
@@ -8743,7 +8749,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8949,7 +8955,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9361,7 +9367,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9645,10 +9651,10 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ39">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR39">
         <v>1.03</v>
@@ -9773,7 +9779,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -9979,7 +9985,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10057,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -10391,7 +10397,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -11833,7 +11839,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -13069,7 +13075,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13893,7 +13899,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -14099,7 +14105,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14305,7 +14311,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -15001,7 +15007,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ65">
         <v>1.14</v>
@@ -15129,7 +15135,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15210,7 +15216,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ66">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR66">
         <v>1.23</v>
@@ -15622,7 +15628,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ68">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR68">
         <v>1.6</v>
@@ -15747,7 +15753,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -15825,7 +15831,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ69">
         <v>0.47</v>
@@ -16159,7 +16165,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16237,7 +16243,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ71">
         <v>0.93</v>
@@ -16652,7 +16658,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ73">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR73">
         <v>0.68</v>
@@ -16777,7 +16783,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -17189,7 +17195,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17395,7 +17401,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17807,7 +17813,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -18219,7 +18225,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -19327,7 +19333,7 @@
         <v>0.33</v>
       </c>
       <c r="AP86">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ86">
         <v>0.27</v>
@@ -19739,10 +19745,10 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ88">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR88">
         <v>2.03</v>
@@ -19867,7 +19873,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -19948,7 +19954,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ89">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR89">
         <v>1.26</v>
@@ -20360,7 +20366,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ91">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -20485,7 +20491,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -20563,7 +20569,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ92">
         <v>1.21</v>
@@ -21721,7 +21727,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21802,7 +21808,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ98">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR98">
         <v>1.22</v>
@@ -22008,7 +22014,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ99">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR99">
         <v>1.08</v>
@@ -22417,7 +22423,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ101">
         <v>0.8</v>
@@ -22545,7 +22551,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22623,7 +22629,7 @@
         <v>0.25</v>
       </c>
       <c r="AP102">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ102">
         <v>1.43</v>
@@ -22751,7 +22757,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -22832,7 +22838,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ103">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR103">
         <v>1.59</v>
@@ -25223,7 +25229,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25429,7 +25435,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25507,7 +25513,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ116">
         <v>0.47</v>
@@ -25841,7 +25847,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -26871,7 +26877,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -27077,7 +27083,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -27979,7 +27985,7 @@
         <v>0.4</v>
       </c>
       <c r="AP128">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ128">
         <v>1.06</v>
@@ -28519,7 +28525,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -29137,7 +29143,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29424,7 +29430,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ135">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR135">
         <v>1.5</v>
@@ -29549,7 +29555,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -29627,7 +29633,7 @@
         <v>0.8</v>
       </c>
       <c r="AP136">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ136">
         <v>0.33</v>
@@ -29836,7 +29842,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ137">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR137">
         <v>1.56</v>
@@ -30454,7 +30460,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ140">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR140">
         <v>1.3</v>
@@ -30785,7 +30791,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -31275,7 +31281,7 @@
         <v>1</v>
       </c>
       <c r="AP144">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ144">
         <v>1.2</v>
@@ -31403,7 +31409,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31609,7 +31615,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31815,7 +31821,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -32021,7 +32027,7 @@
         <v>199</v>
       </c>
       <c r="P148" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q148">
         <v>2.88</v>
@@ -32227,7 +32233,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32433,7 +32439,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32845,7 +32851,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33129,7 +33135,7 @@
         <v>2</v>
       </c>
       <c r="AP153">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ153">
         <v>1.63</v>
@@ -33257,7 +33263,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33669,7 +33675,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -34081,7 +34087,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34159,7 +34165,7 @@
         <v>1.17</v>
       </c>
       <c r="AP158">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ158">
         <v>1.29</v>
@@ -34699,7 +34705,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -35398,7 +35404,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ164">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR164">
         <v>1.43</v>
@@ -35523,7 +35529,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35729,7 +35735,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q166">
         <v>2.5</v>
@@ -35807,7 +35813,7 @@
         <v>0.29</v>
       </c>
       <c r="AP166">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ166">
         <v>0.47</v>
@@ -36634,7 +36640,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ170">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR170">
         <v>1.45</v>
@@ -36965,7 +36971,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37171,7 +37177,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37252,7 +37258,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ173">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR173">
         <v>1.5</v>
@@ -37583,7 +37589,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -37995,7 +38001,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38613,7 +38619,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -38897,7 +38903,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ181">
         <v>0.93</v>
@@ -39025,7 +39031,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39437,7 +39443,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -39515,7 +39521,7 @@
         <v>1.75</v>
       </c>
       <c r="AP184">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ184">
         <v>1.94</v>
@@ -40261,7 +40267,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40751,7 +40757,7 @@
         <v>1</v>
       </c>
       <c r="AP190">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ190">
         <v>0.87</v>
@@ -40879,7 +40885,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41085,7 +41091,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41166,7 +41172,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ192">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR192">
         <v>1.35</v>
@@ -41784,7 +41790,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ195">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR195">
         <v>1.46</v>
@@ -41909,7 +41915,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -42193,7 +42199,7 @@
         <v>0.88</v>
       </c>
       <c r="AP197">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ197">
         <v>1.06</v>
@@ -42939,7 +42945,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -43226,7 +43232,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ202">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR202">
         <v>1.65</v>
@@ -44175,7 +44181,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44462,7 +44468,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ208">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR208">
         <v>1.36</v>
@@ -44793,7 +44799,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44999,7 +45005,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45077,7 +45083,7 @@
         <v>0.5</v>
       </c>
       <c r="AP211">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ211">
         <v>0.73</v>
@@ -45411,7 +45417,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45617,7 +45623,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45823,7 +45829,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -46107,7 +46113,7 @@
         <v>1.63</v>
       </c>
       <c r="AP216">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ216">
         <v>1.29</v>
@@ -46934,7 +46940,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ220">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR220">
         <v>1.32</v>
@@ -47549,7 +47555,7 @@
         <v>1</v>
       </c>
       <c r="AP223">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ223">
         <v>1</v>
@@ -47677,7 +47683,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47883,7 +47889,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -48295,7 +48301,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q227">
         <v>3</v>
@@ -48376,7 +48382,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ227">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR227">
         <v>1.42</v>
@@ -48707,7 +48713,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49197,7 +49203,7 @@
         <v>0.6</v>
       </c>
       <c r="AP231">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ231">
         <v>0.47</v>
@@ -49531,7 +49537,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49737,7 +49743,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -50227,10 +50233,10 @@
         <v>0.25</v>
       </c>
       <c r="AP236">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ236">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR236">
         <v>1.67</v>
@@ -50848,7 +50854,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ239">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR239">
         <v>1.26</v>
@@ -50973,7 +50979,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51051,7 +51057,7 @@
         <v>0.89</v>
       </c>
       <c r="AP240">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ240">
         <v>1.21</v>
@@ -51591,7 +51597,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51797,7 +51803,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -52209,7 +52215,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52827,7 +52833,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53445,7 +53451,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53857,7 +53863,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54141,7 +54147,7 @@
         <v>0.8</v>
       </c>
       <c r="AP255">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ255">
         <v>0.8</v>
@@ -54556,7 +54562,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ257">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR257">
         <v>1.86</v>
@@ -54762,7 +54768,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ258">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR258">
         <v>1.31</v>
@@ -54887,7 +54893,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -55093,7 +55099,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55171,7 +55177,7 @@
         <v>0.8</v>
       </c>
       <c r="AP260">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ260">
         <v>0.8</v>
@@ -55505,7 +55511,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -56123,7 +56129,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56329,7 +56335,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56947,7 +56953,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57437,7 +57443,7 @@
         <v>0.18</v>
       </c>
       <c r="AP271">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ271">
         <v>0.27</v>
@@ -57565,7 +57571,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57771,7 +57777,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -57852,7 +57858,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ273">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR273">
         <v>1.28</v>
@@ -58389,7 +58395,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58595,7 +58601,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58801,7 +58807,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -59703,7 +59709,7 @@
         <v>0.8</v>
       </c>
       <c r="AP282">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ282">
         <v>1.14</v>
@@ -60118,7 +60124,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ284">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR284">
         <v>1.42</v>
@@ -60527,7 +60533,7 @@
         <v>0.73</v>
       </c>
       <c r="AP286">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ286">
         <v>0.8</v>
@@ -60655,7 +60661,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -60942,7 +60948,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ288">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR288">
         <v>1.32</v>
@@ -61067,7 +61073,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61273,7 +61279,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61972,7 +61978,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ293">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR293">
         <v>1.93</v>
@@ -62097,7 +62103,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62381,7 +62387,7 @@
         <v>0.73</v>
       </c>
       <c r="AP295">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ295">
         <v>0.87</v>
@@ -62715,7 +62721,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63539,7 +63545,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63745,7 +63751,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -63826,7 +63832,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ302">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR302">
         <v>1.22</v>
@@ -64157,7 +64163,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64363,7 +64369,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64444,7 +64450,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ305">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR305">
         <v>1.29</v>
@@ -64775,7 +64781,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -65265,7 +65271,7 @@
         <v>0.33</v>
       </c>
       <c r="AP309">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ309">
         <v>0.33</v>
@@ -65393,7 +65399,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -65680,7 +65686,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ311">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR311">
         <v>1.49</v>
@@ -66089,7 +66095,7 @@
         <v>1.46</v>
       </c>
       <c r="AP313">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ313">
         <v>1.63</v>
@@ -67122,7 +67128,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ318">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR318">
         <v>1.1</v>
@@ -67453,7 +67459,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -67737,7 +67743,7 @@
         <v>1.08</v>
       </c>
       <c r="AP321">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ321">
         <v>1</v>
@@ -68483,7 +68489,7 @@
         <v>302</v>
       </c>
       <c r="P325" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q325">
         <v>2.5</v>
@@ -68689,7 +68695,7 @@
         <v>303</v>
       </c>
       <c r="P326" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q326">
         <v>3</v>
@@ -69101,7 +69107,7 @@
         <v>296</v>
       </c>
       <c r="P328" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69513,7 +69519,7 @@
         <v>95</v>
       </c>
       <c r="P330" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q330">
         <v>3.4</v>
@@ -69719,7 +69725,7 @@
         <v>305</v>
       </c>
       <c r="P331" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q331">
         <v>2.88</v>
@@ -69925,7 +69931,7 @@
         <v>306</v>
       </c>
       <c r="P332" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q332">
         <v>2.63</v>
@@ -70337,7 +70343,7 @@
         <v>308</v>
       </c>
       <c r="P334" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q334">
         <v>3.1</v>
@@ -70543,7 +70549,7 @@
         <v>309</v>
       </c>
       <c r="P335" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q335">
         <v>3</v>
@@ -70749,7 +70755,7 @@
         <v>95</v>
       </c>
       <c r="P336" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q336">
         <v>5.5</v>
@@ -70955,7 +70961,7 @@
         <v>95</v>
       </c>
       <c r="P337" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q337">
         <v>2.2</v>
@@ -71161,7 +71167,7 @@
         <v>95</v>
       </c>
       <c r="P338" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q338">
         <v>2.75</v>
@@ -71448,7 +71454,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ339">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="AR339">
         <v>1.25</v>
@@ -71779,7 +71785,7 @@
         <v>311</v>
       </c>
       <c r="P341" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q341">
         <v>1.83</v>
@@ -71985,7 +71991,7 @@
         <v>95</v>
       </c>
       <c r="P342" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q342">
         <v>3.2</v>
@@ -72063,7 +72069,7 @@
         <v>1.31</v>
       </c>
       <c r="AP342">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AQ342">
         <v>1.43</v>
@@ -72475,7 +72481,7 @@
         <v>0.86</v>
       </c>
       <c r="AP344">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AQ344">
         <v>0.8</v>
@@ -72603,7 +72609,7 @@
         <v>314</v>
       </c>
       <c r="P345" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q345">
         <v>3</v>
@@ -72890,7 +72896,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ346">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR346">
         <v>1.46</v>
@@ -73299,10 +73305,10 @@
         <v>1.62</v>
       </c>
       <c r="AP348">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AQ348">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AR348">
         <v>1.45</v>
@@ -73839,7 +73845,7 @@
         <v>95</v>
       </c>
       <c r="P351" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q351">
         <v>3.1</v>
@@ -74251,7 +74257,7 @@
         <v>146</v>
       </c>
       <c r="P353" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q353">
         <v>5.5</v>
@@ -74457,7 +74463,7 @@
         <v>197</v>
       </c>
       <c r="P354" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q354">
         <v>2.75</v>
@@ -74869,7 +74875,7 @@
         <v>95</v>
       </c>
       <c r="P356" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q356">
         <v>3.2</v>
@@ -75281,7 +75287,7 @@
         <v>289</v>
       </c>
       <c r="P358" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q358">
         <v>2.63</v>
@@ -75487,7 +75493,7 @@
         <v>95</v>
       </c>
       <c r="P359" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q359">
         <v>4.33</v>
@@ -75899,7 +75905,7 @@
         <v>321</v>
       </c>
       <c r="P361" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q361">
         <v>3</v>
@@ -76056,6 +76062,624 @@
       </c>
       <c r="BP361">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="362" spans="1:68">
+      <c r="A362" s="1">
+        <v>361</v>
+      </c>
+      <c r="B362">
+        <v>7479104</v>
+      </c>
+      <c r="C362" t="s">
+        <v>68</v>
+      </c>
+      <c r="D362" t="s">
+        <v>69</v>
+      </c>
+      <c r="E362" s="2">
+        <v>45692.69791666666</v>
+      </c>
+      <c r="F362">
+        <v>31</v>
+      </c>
+      <c r="G362" t="s">
+        <v>91</v>
+      </c>
+      <c r="H362" t="s">
+        <v>73</v>
+      </c>
+      <c r="I362">
+        <v>1</v>
+      </c>
+      <c r="J362">
+        <v>0</v>
+      </c>
+      <c r="K362">
+        <v>1</v>
+      </c>
+      <c r="L362">
+        <v>1</v>
+      </c>
+      <c r="M362">
+        <v>0</v>
+      </c>
+      <c r="N362">
+        <v>1</v>
+      </c>
+      <c r="O362" t="s">
+        <v>222</v>
+      </c>
+      <c r="P362" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q362">
+        <v>2.05</v>
+      </c>
+      <c r="R362">
+        <v>2.2</v>
+      </c>
+      <c r="S362">
+        <v>7.5</v>
+      </c>
+      <c r="T362">
+        <v>1.47</v>
+      </c>
+      <c r="U362">
+        <v>2.7</v>
+      </c>
+      <c r="V362">
+        <v>3.25</v>
+      </c>
+      <c r="W362">
+        <v>1.33</v>
+      </c>
+      <c r="X362">
+        <v>8.5</v>
+      </c>
+      <c r="Y362">
+        <v>1.06</v>
+      </c>
+      <c r="Z362">
+        <v>1.37</v>
+      </c>
+      <c r="AA362">
+        <v>4.2</v>
+      </c>
+      <c r="AB362">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC362">
+        <v>1.07</v>
+      </c>
+      <c r="AD362">
+        <v>9.5</v>
+      </c>
+      <c r="AE362">
+        <v>1.4</v>
+      </c>
+      <c r="AF362">
+        <v>3</v>
+      </c>
+      <c r="AG362">
+        <v>1.98</v>
+      </c>
+      <c r="AH362">
+        <v>1.77</v>
+      </c>
+      <c r="AI362">
+        <v>2.45</v>
+      </c>
+      <c r="AJ362">
+        <v>1.55</v>
+      </c>
+      <c r="AK362">
+        <v>1.07</v>
+      </c>
+      <c r="AL362">
+        <v>1.19</v>
+      </c>
+      <c r="AM362">
+        <v>2.75</v>
+      </c>
+      <c r="AN362">
+        <v>1.86</v>
+      </c>
+      <c r="AO362">
+        <v>0.57</v>
+      </c>
+      <c r="AP362">
+        <v>1.93</v>
+      </c>
+      <c r="AQ362">
+        <v>0.53</v>
+      </c>
+      <c r="AR362">
+        <v>1.39</v>
+      </c>
+      <c r="AS362">
+        <v>1.03</v>
+      </c>
+      <c r="AT362">
+        <v>2.42</v>
+      </c>
+      <c r="AU362">
+        <v>8</v>
+      </c>
+      <c r="AV362">
+        <v>2</v>
+      </c>
+      <c r="AW362">
+        <v>9</v>
+      </c>
+      <c r="AX362">
+        <v>6</v>
+      </c>
+      <c r="AY362">
+        <v>20</v>
+      </c>
+      <c r="AZ362">
+        <v>10</v>
+      </c>
+      <c r="BA362">
+        <v>12</v>
+      </c>
+      <c r="BB362">
+        <v>3</v>
+      </c>
+      <c r="BC362">
+        <v>15</v>
+      </c>
+      <c r="BD362">
+        <v>1.19</v>
+      </c>
+      <c r="BE362">
+        <v>9</v>
+      </c>
+      <c r="BF362">
+        <v>5.1</v>
+      </c>
+      <c r="BG362">
+        <v>1.23</v>
+      </c>
+      <c r="BH362">
+        <v>3.65</v>
+      </c>
+      <c r="BI362">
+        <v>1.4</v>
+      </c>
+      <c r="BJ362">
+        <v>2.65</v>
+      </c>
+      <c r="BK362">
+        <v>1.65</v>
+      </c>
+      <c r="BL362">
+        <v>2.08</v>
+      </c>
+      <c r="BM362">
+        <v>2</v>
+      </c>
+      <c r="BN362">
+        <v>1.7</v>
+      </c>
+      <c r="BO362">
+        <v>2.5</v>
+      </c>
+      <c r="BP362">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="363" spans="1:68">
+      <c r="A363" s="1">
+        <v>362</v>
+      </c>
+      <c r="B363">
+        <v>7479110</v>
+      </c>
+      <c r="C363" t="s">
+        <v>68</v>
+      </c>
+      <c r="D363" t="s">
+        <v>69</v>
+      </c>
+      <c r="E363" s="2">
+        <v>45692.69791666666</v>
+      </c>
+      <c r="F363">
+        <v>31</v>
+      </c>
+      <c r="G363" t="s">
+        <v>72</v>
+      </c>
+      <c r="H363" t="s">
+        <v>70</v>
+      </c>
+      <c r="I363">
+        <v>1</v>
+      </c>
+      <c r="J363">
+        <v>0</v>
+      </c>
+      <c r="K363">
+        <v>1</v>
+      </c>
+      <c r="L363">
+        <v>2</v>
+      </c>
+      <c r="M363">
+        <v>1</v>
+      </c>
+      <c r="N363">
+        <v>3</v>
+      </c>
+      <c r="O363" t="s">
+        <v>322</v>
+      </c>
+      <c r="P363" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q363">
+        <v>3.25</v>
+      </c>
+      <c r="R363">
+        <v>2</v>
+      </c>
+      <c r="S363">
+        <v>3.75</v>
+      </c>
+      <c r="T363">
+        <v>1.52</v>
+      </c>
+      <c r="U363">
+        <v>2.6</v>
+      </c>
+      <c r="V363">
+        <v>3.3</v>
+      </c>
+      <c r="W363">
+        <v>1.32</v>
+      </c>
+      <c r="X363">
+        <v>9</v>
+      </c>
+      <c r="Y363">
+        <v>1.05</v>
+      </c>
+      <c r="Z363">
+        <v>2.49</v>
+      </c>
+      <c r="AA363">
+        <v>3.29</v>
+      </c>
+      <c r="AB363">
+        <v>2.74</v>
+      </c>
+      <c r="AC363">
+        <v>1.08</v>
+      </c>
+      <c r="AD363">
+        <v>8.5</v>
+      </c>
+      <c r="AE363">
+        <v>1.42</v>
+      </c>
+      <c r="AF363">
+        <v>2.9</v>
+      </c>
+      <c r="AG363">
+        <v>2.1</v>
+      </c>
+      <c r="AH363">
+        <v>1.65</v>
+      </c>
+      <c r="AI363">
+        <v>1.92</v>
+      </c>
+      <c r="AJ363">
+        <v>1.85</v>
+      </c>
+      <c r="AK363">
+        <v>1.42</v>
+      </c>
+      <c r="AL363">
+        <v>1.32</v>
+      </c>
+      <c r="AM363">
+        <v>1.55</v>
+      </c>
+      <c r="AN363">
+        <v>1.33</v>
+      </c>
+      <c r="AO363">
+        <v>1.14</v>
+      </c>
+      <c r="AP363">
+        <v>1.44</v>
+      </c>
+      <c r="AQ363">
+        <v>1.07</v>
+      </c>
+      <c r="AR363">
+        <v>1.59</v>
+      </c>
+      <c r="AS363">
+        <v>0.99</v>
+      </c>
+      <c r="AT363">
+        <v>2.58</v>
+      </c>
+      <c r="AU363">
+        <v>6</v>
+      </c>
+      <c r="AV363">
+        <v>6</v>
+      </c>
+      <c r="AW363">
+        <v>13</v>
+      </c>
+      <c r="AX363">
+        <v>5</v>
+      </c>
+      <c r="AY363">
+        <v>21</v>
+      </c>
+      <c r="AZ363">
+        <v>14</v>
+      </c>
+      <c r="BA363">
+        <v>11</v>
+      </c>
+      <c r="BB363">
+        <v>2</v>
+      </c>
+      <c r="BC363">
+        <v>13</v>
+      </c>
+      <c r="BD363">
+        <v>1.75</v>
+      </c>
+      <c r="BE363">
+        <v>8.5</v>
+      </c>
+      <c r="BF363">
+        <v>2.3</v>
+      </c>
+      <c r="BG363">
+        <v>1.2</v>
+      </c>
+      <c r="BH363">
+        <v>3.95</v>
+      </c>
+      <c r="BI363">
+        <v>1.35</v>
+      </c>
+      <c r="BJ363">
+        <v>2.9</v>
+      </c>
+      <c r="BK363">
+        <v>1.58</v>
+      </c>
+      <c r="BL363">
+        <v>2.2</v>
+      </c>
+      <c r="BM363">
+        <v>1.92</v>
+      </c>
+      <c r="BN363">
+        <v>1.77</v>
+      </c>
+      <c r="BO363">
+        <v>2.38</v>
+      </c>
+      <c r="BP363">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="364" spans="1:68">
+      <c r="A364" s="1">
+        <v>363</v>
+      </c>
+      <c r="B364">
+        <v>7479106</v>
+      </c>
+      <c r="C364" t="s">
+        <v>68</v>
+      </c>
+      <c r="D364" t="s">
+        <v>69</v>
+      </c>
+      <c r="E364" s="2">
+        <v>45693.69791666666</v>
+      </c>
+      <c r="F364">
+        <v>31</v>
+      </c>
+      <c r="G364" t="s">
+        <v>82</v>
+      </c>
+      <c r="H364" t="s">
+        <v>76</v>
+      </c>
+      <c r="I364">
+        <v>0</v>
+      </c>
+      <c r="J364">
+        <v>2</v>
+      </c>
+      <c r="K364">
+        <v>2</v>
+      </c>
+      <c r="L364">
+        <v>0</v>
+      </c>
+      <c r="M364">
+        <v>2</v>
+      </c>
+      <c r="N364">
+        <v>2</v>
+      </c>
+      <c r="O364" t="s">
+        <v>95</v>
+      </c>
+      <c r="P364" t="s">
+        <v>439</v>
+      </c>
+      <c r="Q364">
+        <v>4.5</v>
+      </c>
+      <c r="R364">
+        <v>2.2</v>
+      </c>
+      <c r="S364">
+        <v>2.5</v>
+      </c>
+      <c r="T364">
+        <v>1.42</v>
+      </c>
+      <c r="U364">
+        <v>2.95</v>
+      </c>
+      <c r="V364">
+        <v>2.9</v>
+      </c>
+      <c r="W364">
+        <v>1.4</v>
+      </c>
+      <c r="X364">
+        <v>7.5</v>
+      </c>
+      <c r="Y364">
+        <v>1.08</v>
+      </c>
+      <c r="Z364">
+        <v>4.5</v>
+      </c>
+      <c r="AA364">
+        <v>3.61</v>
+      </c>
+      <c r="AB364">
+        <v>1.75</v>
+      </c>
+      <c r="AC364">
+        <v>1.05</v>
+      </c>
+      <c r="AD364">
+        <v>11</v>
+      </c>
+      <c r="AE364">
+        <v>1.32</v>
+      </c>
+      <c r="AF364">
+        <v>3.4</v>
+      </c>
+      <c r="AG364">
+        <v>1.87</v>
+      </c>
+      <c r="AH364">
+        <v>1.87</v>
+      </c>
+      <c r="AI364">
+        <v>1.85</v>
+      </c>
+      <c r="AJ364">
+        <v>1.95</v>
+      </c>
+      <c r="AK364">
+        <v>2</v>
+      </c>
+      <c r="AL364">
+        <v>1.24</v>
+      </c>
+      <c r="AM364">
+        <v>1.22</v>
+      </c>
+      <c r="AN364">
+        <v>1.71</v>
+      </c>
+      <c r="AO364">
+        <v>1.57</v>
+      </c>
+      <c r="AP364">
+        <v>1.6</v>
+      </c>
+      <c r="AQ364">
+        <v>1.67</v>
+      </c>
+      <c r="AR364">
+        <v>1.82</v>
+      </c>
+      <c r="AS364">
+        <v>1.52</v>
+      </c>
+      <c r="AT364">
+        <v>3.34</v>
+      </c>
+      <c r="AU364">
+        <v>5</v>
+      </c>
+      <c r="AV364">
+        <v>9</v>
+      </c>
+      <c r="AW364">
+        <v>5</v>
+      </c>
+      <c r="AX364">
+        <v>12</v>
+      </c>
+      <c r="AY364">
+        <v>12</v>
+      </c>
+      <c r="AZ364">
+        <v>23</v>
+      </c>
+      <c r="BA364">
+        <v>3</v>
+      </c>
+      <c r="BB364">
+        <v>8</v>
+      </c>
+      <c r="BC364">
+        <v>11</v>
+      </c>
+      <c r="BD364">
+        <v>2.55</v>
+      </c>
+      <c r="BE364">
+        <v>6.75</v>
+      </c>
+      <c r="BF364">
+        <v>1.58</v>
+      </c>
+      <c r="BG364">
+        <v>1.2</v>
+      </c>
+      <c r="BH364">
+        <v>3.9</v>
+      </c>
+      <c r="BI364">
+        <v>1.36</v>
+      </c>
+      <c r="BJ364">
+        <v>2.8</v>
+      </c>
+      <c r="BK364">
+        <v>1.58</v>
+      </c>
+      <c r="BL364">
+        <v>2.18</v>
+      </c>
+      <c r="BM364">
+        <v>1.96</v>
+      </c>
+      <c r="BN364">
+        <v>1.74</v>
+      </c>
+      <c r="BO364">
+        <v>2.43</v>
+      </c>
+      <c r="BP364">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2246" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="443">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -985,6 +985,12 @@
     <t>['5', '76']</t>
   </si>
   <si>
+    <t>['74', '90+6']</t>
+  </si>
+  <si>
+    <t>['16', '89']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -1334,6 +1340,9 @@
   </si>
   <si>
     <t>['17', '26']</t>
+  </si>
+  <si>
+    <t>['43', '46']</t>
   </si>
 </sst>
 </file>
@@ -1695,7 +1704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP364"/>
+  <dimension ref="A1:BP366"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1951,7 +1960,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -2157,7 +2166,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2363,7 +2372,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2775,7 +2784,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -2856,7 +2865,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -3187,7 +3196,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3599,7 +3608,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -4217,7 +4226,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4423,7 +4432,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -4707,7 +4716,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ15">
         <v>1.67</v>
@@ -5247,7 +5256,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5865,7 +5874,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -6071,7 +6080,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6767,10 +6776,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ25">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6895,7 +6904,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -7719,7 +7728,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -8209,7 +8218,7 @@
         <v>3</v>
       </c>
       <c r="AP32">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ32">
         <v>2</v>
@@ -8749,7 +8758,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8955,7 +8964,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9367,7 +9376,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9779,7 +9788,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -9985,7 +9994,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10269,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="AP42">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ42">
         <v>0.93</v>
@@ -10397,7 +10406,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -10890,7 +10899,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ45">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR45">
         <v>1.47</v>
@@ -11714,7 +11723,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ49">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR49">
         <v>1.17</v>
@@ -11839,7 +11848,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -13075,7 +13084,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13899,7 +13908,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -14105,7 +14114,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14311,7 +14320,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14595,7 +14604,7 @@
         <v>1.5</v>
       </c>
       <c r="AP63">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ63">
         <v>1.29</v>
@@ -14804,7 +14813,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ64">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR64">
         <v>1.36</v>
@@ -15135,7 +15144,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15419,7 +15428,7 @@
         <v>0.5</v>
       </c>
       <c r="AP67">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ67">
         <v>0.27</v>
@@ -15753,7 +15762,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -16040,7 +16049,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ70">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR70">
         <v>1.2</v>
@@ -16165,7 +16174,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16783,7 +16792,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -17195,7 +17204,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17401,7 +17410,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17813,7 +17822,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -18225,7 +18234,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -19873,7 +19882,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -20157,7 +20166,7 @@
         <v>0</v>
       </c>
       <c r="AP90">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ90">
         <v>0.47</v>
@@ -20491,7 +20500,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -20775,7 +20784,7 @@
         <v>1</v>
       </c>
       <c r="AP93">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ93">
         <v>1.29</v>
@@ -21190,7 +21199,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ95">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR95">
         <v>0.98</v>
@@ -21602,7 +21611,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ97">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR97">
         <v>1.65</v>
@@ -21727,7 +21736,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21805,7 +21814,7 @@
         <v>2</v>
       </c>
       <c r="AP98">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ98">
         <v>1.67</v>
@@ -22551,7 +22560,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22632,7 +22641,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ102">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR102">
         <v>2.01</v>
@@ -22757,7 +22766,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -23659,7 +23668,7 @@
         <v>0.5</v>
       </c>
       <c r="AP107">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ107">
         <v>1.14</v>
@@ -24692,7 +24701,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ112">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR112">
         <v>1.26</v>
@@ -25229,7 +25238,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25435,7 +25444,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25847,7 +25856,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -26877,7 +26886,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -27083,7 +27092,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -27370,7 +27379,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ125">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR125">
         <v>1.76</v>
@@ -28525,7 +28534,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -29143,7 +29152,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29224,7 +29233,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ134">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -29555,7 +29564,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -30251,7 +30260,7 @@
         <v>0.4</v>
       </c>
       <c r="AP139">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ139">
         <v>0.73</v>
@@ -30457,7 +30466,7 @@
         <v>0.4</v>
       </c>
       <c r="AP140">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ140">
         <v>0.53</v>
@@ -30791,7 +30800,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -31409,7 +31418,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31615,7 +31624,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31821,7 +31830,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -32027,7 +32036,7 @@
         <v>199</v>
       </c>
       <c r="P148" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q148">
         <v>2.88</v>
@@ -32233,7 +32242,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32439,7 +32448,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32851,7 +32860,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33263,7 +33272,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33344,7 +33353,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ154">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR154">
         <v>1.43</v>
@@ -33675,7 +33684,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -34087,7 +34096,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34705,7 +34714,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -34992,7 +35001,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ162">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR162">
         <v>1.39</v>
@@ -35529,7 +35538,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35735,7 +35744,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q166">
         <v>2.5</v>
@@ -36431,7 +36440,7 @@
         <v>1.57</v>
       </c>
       <c r="AP169">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ169">
         <v>2</v>
@@ -36971,7 +36980,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37177,7 +37186,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37589,7 +37598,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -37667,7 +37676,7 @@
         <v>0.86</v>
       </c>
       <c r="AP175">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ175">
         <v>1.06</v>
@@ -38001,7 +38010,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38494,7 +38503,7 @@
         <v>2.29</v>
       </c>
       <c r="AQ179">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR179">
         <v>1.59</v>
@@ -38619,7 +38628,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -39031,7 +39040,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39112,7 +39121,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ182">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR182">
         <v>1.52</v>
@@ -39443,7 +39452,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -40267,7 +40276,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40885,7 +40894,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -40963,7 +40972,7 @@
         <v>1</v>
       </c>
       <c r="AP191">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ191">
         <v>1</v>
@@ -41091,7 +41100,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41915,7 +41924,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -41996,7 +42005,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ196">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR196">
         <v>1.31</v>
@@ -42611,7 +42620,7 @@
         <v>1.88</v>
       </c>
       <c r="AP199">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ199">
         <v>1.19</v>
@@ -42945,7 +42954,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -44181,7 +44190,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44799,7 +44808,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -45005,7 +45014,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45417,7 +45426,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45623,7 +45632,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45829,7 +45838,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -45910,7 +45919,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ215">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR215">
         <v>1.4</v>
@@ -46731,7 +46740,7 @@
         <v>1</v>
       </c>
       <c r="AP219">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ219">
         <v>0.87</v>
@@ -47683,7 +47692,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47889,7 +47898,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -47967,7 +47976,7 @@
         <v>1.67</v>
       </c>
       <c r="AP225">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ225">
         <v>1.94</v>
@@ -48173,7 +48182,7 @@
         <v>1.2</v>
       </c>
       <c r="AP226">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ226">
         <v>1</v>
@@ -48301,7 +48310,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q227">
         <v>3</v>
@@ -48713,7 +48722,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49537,7 +49546,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49743,7 +49752,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -50030,7 +50039,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ235">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR235">
         <v>1.35</v>
@@ -50439,7 +50448,7 @@
         <v>1</v>
       </c>
       <c r="AP237">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ237">
         <v>1.06</v>
@@ -50979,7 +50988,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51597,7 +51606,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51803,7 +51812,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -52215,7 +52224,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52296,7 +52305,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ246">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR246">
         <v>1.05</v>
@@ -52833,7 +52842,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53451,7 +53460,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53863,7 +53872,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -53941,7 +53950,7 @@
         <v>0.91</v>
       </c>
       <c r="AP254">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ254">
         <v>1</v>
@@ -54150,7 +54159,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ255">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR255">
         <v>1.44</v>
@@ -54893,7 +54902,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -55099,7 +55108,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55383,7 +55392,7 @@
         <v>1.18</v>
       </c>
       <c r="AP261">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ261">
         <v>1</v>
@@ -55511,7 +55520,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -56129,7 +56138,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56335,7 +56344,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56416,7 +56425,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ266">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR266">
         <v>1.6</v>
@@ -56953,7 +56962,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57571,7 +57580,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57777,7 +57786,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -58270,7 +58279,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ275">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR275">
         <v>1.19</v>
@@ -58395,7 +58404,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58601,7 +58610,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58807,7 +58816,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -60536,7 +60545,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ286">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR286">
         <v>1.65</v>
@@ -60661,7 +60670,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -61073,7 +61082,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61151,7 +61160,7 @@
         <v>0.73</v>
       </c>
       <c r="AP289">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ289">
         <v>0.8</v>
@@ -61279,7 +61288,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -62103,7 +62112,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62721,7 +62730,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -62799,7 +62808,7 @@
         <v>1.83</v>
       </c>
       <c r="AP297">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ297">
         <v>1.94</v>
@@ -63545,7 +63554,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63751,7 +63760,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -64163,7 +64172,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64369,7 +64378,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64781,7 +64790,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -65065,7 +65074,7 @@
         <v>0.58</v>
       </c>
       <c r="AP308">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ308">
         <v>0.47</v>
@@ -65399,7 +65408,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -65480,7 +65489,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ310">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR310">
         <v>1.52</v>
@@ -66919,7 +66928,7 @@
         <v>0.75</v>
       </c>
       <c r="AP317">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ317">
         <v>0.87</v>
@@ -67459,7 +67468,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -67540,7 +67549,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ320">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR320">
         <v>1.35</v>
@@ -68364,7 +68373,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ324">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR324">
         <v>1.89</v>
@@ -68489,7 +68498,7 @@
         <v>302</v>
       </c>
       <c r="P325" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q325">
         <v>2.5</v>
@@ -68695,7 +68704,7 @@
         <v>303</v>
       </c>
       <c r="P326" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Q326">
         <v>3</v>
@@ -69107,7 +69116,7 @@
         <v>296</v>
       </c>
       <c r="P328" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69519,7 +69528,7 @@
         <v>95</v>
       </c>
       <c r="P330" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q330">
         <v>3.4</v>
@@ -69725,7 +69734,7 @@
         <v>305</v>
       </c>
       <c r="P331" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="Q331">
         <v>2.88</v>
@@ -69931,7 +69940,7 @@
         <v>306</v>
       </c>
       <c r="P332" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q332">
         <v>2.63</v>
@@ -70343,7 +70352,7 @@
         <v>308</v>
       </c>
       <c r="P334" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Q334">
         <v>3.1</v>
@@ -70549,7 +70558,7 @@
         <v>309</v>
       </c>
       <c r="P335" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Q335">
         <v>3</v>
@@ -70755,7 +70764,7 @@
         <v>95</v>
       </c>
       <c r="P336" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Q336">
         <v>5.5</v>
@@ -70961,7 +70970,7 @@
         <v>95</v>
       </c>
       <c r="P337" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Q337">
         <v>2.2</v>
@@ -71167,7 +71176,7 @@
         <v>95</v>
       </c>
       <c r="P338" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q338">
         <v>2.75</v>
@@ -71785,7 +71794,7 @@
         <v>311</v>
       </c>
       <c r="P341" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Q341">
         <v>1.83</v>
@@ -71863,7 +71872,7 @@
         <v>0.21</v>
       </c>
       <c r="AP341">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AQ341">
         <v>0.27</v>
@@ -71991,7 +72000,7 @@
         <v>95</v>
       </c>
       <c r="P342" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Q342">
         <v>3.2</v>
@@ -72072,7 +72081,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ342">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AR342">
         <v>1.61</v>
@@ -72275,7 +72284,7 @@
         <v>0.5</v>
       </c>
       <c r="AP343">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ343">
         <v>0.47</v>
@@ -72484,7 +72493,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ344">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR344">
         <v>1.86</v>
@@ -72609,7 +72618,7 @@
         <v>314</v>
       </c>
       <c r="P345" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q345">
         <v>3</v>
@@ -73845,7 +73854,7 @@
         <v>95</v>
       </c>
       <c r="P351" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q351">
         <v>3.1</v>
@@ -74257,7 +74266,7 @@
         <v>146</v>
       </c>
       <c r="P353" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q353">
         <v>5.5</v>
@@ -74463,7 +74472,7 @@
         <v>197</v>
       </c>
       <c r="P354" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q354">
         <v>2.75</v>
@@ -74875,7 +74884,7 @@
         <v>95</v>
       </c>
       <c r="P356" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q356">
         <v>3.2</v>
@@ -75287,7 +75296,7 @@
         <v>289</v>
       </c>
       <c r="P358" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q358">
         <v>2.63</v>
@@ -75493,7 +75502,7 @@
         <v>95</v>
       </c>
       <c r="P359" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q359">
         <v>4.33</v>
@@ -75905,7 +75914,7 @@
         <v>321</v>
       </c>
       <c r="P361" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Q361">
         <v>3</v>
@@ -76523,7 +76532,7 @@
         <v>95</v>
       </c>
       <c r="P364" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Q364">
         <v>4.5</v>
@@ -76680,6 +76689,418 @@
       </c>
       <c r="BP364">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="365" spans="1:68">
+      <c r="A365" s="1">
+        <v>364</v>
+      </c>
+      <c r="B365">
+        <v>7479114</v>
+      </c>
+      <c r="C365" t="s">
+        <v>68</v>
+      </c>
+      <c r="D365" t="s">
+        <v>69</v>
+      </c>
+      <c r="E365" s="2">
+        <v>45696.39583333334</v>
+      </c>
+      <c r="F365">
+        <v>31</v>
+      </c>
+      <c r="G365" t="s">
+        <v>83</v>
+      </c>
+      <c r="H365" t="s">
+        <v>80</v>
+      </c>
+      <c r="I365">
+        <v>0</v>
+      </c>
+      <c r="J365">
+        <v>0</v>
+      </c>
+      <c r="K365">
+        <v>0</v>
+      </c>
+      <c r="L365">
+        <v>2</v>
+      </c>
+      <c r="M365">
+        <v>1</v>
+      </c>
+      <c r="N365">
+        <v>3</v>
+      </c>
+      <c r="O365" t="s">
+        <v>323</v>
+      </c>
+      <c r="P365" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q365">
+        <v>2.88</v>
+      </c>
+      <c r="R365">
+        <v>2.1</v>
+      </c>
+      <c r="S365">
+        <v>4</v>
+      </c>
+      <c r="T365">
+        <v>1.44</v>
+      </c>
+      <c r="U365">
+        <v>2.63</v>
+      </c>
+      <c r="V365">
+        <v>3.25</v>
+      </c>
+      <c r="W365">
+        <v>1.33</v>
+      </c>
+      <c r="X365">
+        <v>9</v>
+      </c>
+      <c r="Y365">
+        <v>1.07</v>
+      </c>
+      <c r="Z365">
+        <v>2.05</v>
+      </c>
+      <c r="AA365">
+        <v>3.45</v>
+      </c>
+      <c r="AB365">
+        <v>3.45</v>
+      </c>
+      <c r="AC365">
+        <v>1.05</v>
+      </c>
+      <c r="AD365">
+        <v>9</v>
+      </c>
+      <c r="AE365">
+        <v>1.33</v>
+      </c>
+      <c r="AF365">
+        <v>3.2</v>
+      </c>
+      <c r="AG365">
+        <v>1.94</v>
+      </c>
+      <c r="AH365">
+        <v>1.79</v>
+      </c>
+      <c r="AI365">
+        <v>1.83</v>
+      </c>
+      <c r="AJ365">
+        <v>1.83</v>
+      </c>
+      <c r="AK365">
+        <v>1.3</v>
+      </c>
+      <c r="AL365">
+        <v>1.25</v>
+      </c>
+      <c r="AM365">
+        <v>1.7</v>
+      </c>
+      <c r="AN365">
+        <v>1.79</v>
+      </c>
+      <c r="AO365">
+        <v>1.43</v>
+      </c>
+      <c r="AP365">
+        <v>1.87</v>
+      </c>
+      <c r="AQ365">
+        <v>1.33</v>
+      </c>
+      <c r="AR365">
+        <v>1.47</v>
+      </c>
+      <c r="AS365">
+        <v>1.23</v>
+      </c>
+      <c r="AT365">
+        <v>2.7</v>
+      </c>
+      <c r="AU365">
+        <v>6</v>
+      </c>
+      <c r="AV365">
+        <v>6</v>
+      </c>
+      <c r="AW365">
+        <v>11</v>
+      </c>
+      <c r="AX365">
+        <v>9</v>
+      </c>
+      <c r="AY365">
+        <v>20</v>
+      </c>
+      <c r="AZ365">
+        <v>17</v>
+      </c>
+      <c r="BA365">
+        <v>12</v>
+      </c>
+      <c r="BB365">
+        <v>2</v>
+      </c>
+      <c r="BC365">
+        <v>14</v>
+      </c>
+      <c r="BD365">
+        <v>1.95</v>
+      </c>
+      <c r="BE365">
+        <v>7.8</v>
+      </c>
+      <c r="BF365">
+        <v>2.45</v>
+      </c>
+      <c r="BG365">
+        <v>1.1</v>
+      </c>
+      <c r="BH365">
+        <v>5.47</v>
+      </c>
+      <c r="BI365">
+        <v>1.26</v>
+      </c>
+      <c r="BJ365">
+        <v>3.54</v>
+      </c>
+      <c r="BK365">
+        <v>1.49</v>
+      </c>
+      <c r="BL365">
+        <v>2.55</v>
+      </c>
+      <c r="BM365">
+        <v>1.82</v>
+      </c>
+      <c r="BN365">
+        <v>1.99</v>
+      </c>
+      <c r="BO365">
+        <v>2.25</v>
+      </c>
+      <c r="BP365">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="366" spans="1:68">
+      <c r="A366" s="1">
+        <v>365</v>
+      </c>
+      <c r="B366">
+        <v>7479113</v>
+      </c>
+      <c r="C366" t="s">
+        <v>68</v>
+      </c>
+      <c r="D366" t="s">
+        <v>69</v>
+      </c>
+      <c r="E366" s="2">
+        <v>45696.39583333334</v>
+      </c>
+      <c r="F366">
+        <v>31</v>
+      </c>
+      <c r="G366" t="s">
+        <v>93</v>
+      </c>
+      <c r="H366" t="s">
+        <v>87</v>
+      </c>
+      <c r="I366">
+        <v>1</v>
+      </c>
+      <c r="J366">
+        <v>1</v>
+      </c>
+      <c r="K366">
+        <v>2</v>
+      </c>
+      <c r="L366">
+        <v>2</v>
+      </c>
+      <c r="M366">
+        <v>2</v>
+      </c>
+      <c r="N366">
+        <v>4</v>
+      </c>
+      <c r="O366" t="s">
+        <v>324</v>
+      </c>
+      <c r="P366" t="s">
+        <v>442</v>
+      </c>
+      <c r="Q366">
+        <v>2.1</v>
+      </c>
+      <c r="R366">
+        <v>2.3</v>
+      </c>
+      <c r="S366">
+        <v>6</v>
+      </c>
+      <c r="T366">
+        <v>1.36</v>
+      </c>
+      <c r="U366">
+        <v>3</v>
+      </c>
+      <c r="V366">
+        <v>2.75</v>
+      </c>
+      <c r="W366">
+        <v>1.4</v>
+      </c>
+      <c r="X366">
+        <v>7</v>
+      </c>
+      <c r="Y366">
+        <v>1.1</v>
+      </c>
+      <c r="Z366">
+        <v>1.67</v>
+      </c>
+      <c r="AA366">
+        <v>4</v>
+      </c>
+      <c r="AB366">
+        <v>4.5</v>
+      </c>
+      <c r="AC366">
+        <v>1.05</v>
+      </c>
+      <c r="AD366">
+        <v>9.5</v>
+      </c>
+      <c r="AE366">
+        <v>1.28</v>
+      </c>
+      <c r="AF366">
+        <v>3.6</v>
+      </c>
+      <c r="AG366">
+        <v>1.94</v>
+      </c>
+      <c r="AH366">
+        <v>1.8</v>
+      </c>
+      <c r="AI366">
+        <v>1.91</v>
+      </c>
+      <c r="AJ366">
+        <v>1.8</v>
+      </c>
+      <c r="AK366">
+        <v>1.12</v>
+      </c>
+      <c r="AL366">
+        <v>1.18</v>
+      </c>
+      <c r="AM366">
+        <v>2.4</v>
+      </c>
+      <c r="AN366">
+        <v>2.29</v>
+      </c>
+      <c r="AO366">
+        <v>0.8</v>
+      </c>
+      <c r="AP366">
+        <v>2.2</v>
+      </c>
+      <c r="AQ366">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AR366">
+        <v>1.59</v>
+      </c>
+      <c r="AS366">
+        <v>1.19</v>
+      </c>
+      <c r="AT366">
+        <v>2.78</v>
+      </c>
+      <c r="AU366">
+        <v>8</v>
+      </c>
+      <c r="AV366">
+        <v>6</v>
+      </c>
+      <c r="AW366">
+        <v>7</v>
+      </c>
+      <c r="AX366">
+        <v>6</v>
+      </c>
+      <c r="AY366">
+        <v>18</v>
+      </c>
+      <c r="AZ366">
+        <v>15</v>
+      </c>
+      <c r="BA366">
+        <v>7</v>
+      </c>
+      <c r="BB366">
+        <v>3</v>
+      </c>
+      <c r="BC366">
+        <v>10</v>
+      </c>
+      <c r="BD366">
+        <v>1.27</v>
+      </c>
+      <c r="BE366">
+        <v>10.5</v>
+      </c>
+      <c r="BF366">
+        <v>6</v>
+      </c>
+      <c r="BG366">
+        <v>1.19</v>
+      </c>
+      <c r="BH366">
+        <v>4.11</v>
+      </c>
+      <c r="BI366">
+        <v>1.4</v>
+      </c>
+      <c r="BJ366">
+        <v>2.82</v>
+      </c>
+      <c r="BK366">
+        <v>1.71</v>
+      </c>
+      <c r="BL366">
+        <v>2.13</v>
+      </c>
+      <c r="BM366">
+        <v>2.12</v>
+      </c>
+      <c r="BN366">
+        <v>1.72</v>
+      </c>
+      <c r="BO366">
+        <v>2.74</v>
+      </c>
+      <c r="BP366">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2258" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="444">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -991,6 +991,12 @@
     <t>['16', '89']</t>
   </si>
   <si>
+    <t>['68']</t>
+  </si>
+  <si>
+    <t>['24', '73']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -1133,9 +1139,6 @@
   </si>
   <si>
     <t>['38', '80']</t>
-  </si>
-  <si>
-    <t>['68']</t>
   </si>
   <si>
     <t>['16', '64']</t>
@@ -1704,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP366"/>
+  <dimension ref="A1:BP368"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1960,7 +1963,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -2041,7 +2044,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ2">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2166,7 +2169,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2372,7 +2375,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2784,7 +2787,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -3196,7 +3199,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3277,7 +3280,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ8">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3608,7 +3611,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -4226,7 +4229,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4432,7 +4435,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -5256,7 +5259,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5334,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ18">
         <v>1.2</v>
@@ -5874,7 +5877,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -6080,7 +6083,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6158,7 +6161,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ22">
         <v>1.07</v>
@@ -6904,7 +6907,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -7728,7 +7731,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -7809,7 +7812,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ30">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR30">
         <v>1.4</v>
@@ -8015,7 +8018,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ31">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR31">
         <v>2.07</v>
@@ -8758,7 +8761,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8964,7 +8967,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9042,7 +9045,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ36">
         <v>1.94</v>
@@ -9376,7 +9379,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9788,7 +9791,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -9994,7 +9997,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10406,7 +10409,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -11720,7 +11723,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ49">
         <v>0.8100000000000001</v>
@@ -11848,7 +11851,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -13084,7 +13087,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13908,7 +13911,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -14114,7 +14117,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14320,7 +14323,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14810,7 +14813,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ64">
         <v>0.8100000000000001</v>
@@ -15144,7 +15147,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15762,7 +15765,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -15843,7 +15846,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ69">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR69">
         <v>1.36</v>
@@ -16174,7 +16177,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16458,10 +16461,10 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ72">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR72">
         <v>1.52</v>
@@ -16792,7 +16795,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -17204,7 +17207,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17410,7 +17413,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17822,7 +17825,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -18234,7 +18237,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -19882,7 +19885,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -20169,7 +20172,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ90">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR90">
         <v>1.26</v>
@@ -20372,7 +20375,7 @@
         <v>2.33</v>
       </c>
       <c r="AP91">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ91">
         <v>1.67</v>
@@ -20500,7 +20503,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -20990,7 +20993,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ94">
         <v>0.93</v>
@@ -21405,7 +21408,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ96">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR96">
         <v>1.07</v>
@@ -21736,7 +21739,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -22226,7 +22229,7 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ100">
         <v>1.21</v>
@@ -22560,7 +22563,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22766,7 +22769,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -23050,7 +23053,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ104">
         <v>0.33</v>
@@ -25238,7 +25241,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25444,7 +25447,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25525,7 +25528,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ116">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR116">
         <v>1.81</v>
@@ -25856,7 +25859,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -26349,7 +26352,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ120">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR120">
         <v>1.42</v>
@@ -26886,7 +26889,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -27092,7 +27095,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -27585,7 +27588,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ126">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR126">
         <v>1.35</v>
@@ -27791,7 +27794,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ127">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR127">
         <v>1.11</v>
@@ -28534,7 +28537,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -29152,7 +29155,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29564,7 +29567,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -30672,7 +30675,7 @@
         <v>0.8</v>
       </c>
       <c r="AP141">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ141">
         <v>0.87</v>
@@ -30800,7 +30803,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -31418,7 +31421,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31496,7 +31499,7 @@
         <v>1.2</v>
       </c>
       <c r="AP145">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ145">
         <v>1.29</v>
@@ -31624,7 +31627,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31830,7 +31833,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -32036,7 +32039,7 @@
         <v>199</v>
       </c>
       <c r="P148" t="s">
-        <v>373</v>
+        <v>325</v>
       </c>
       <c r="Q148">
         <v>2.88</v>
@@ -32117,7 +32120,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ148">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR148">
         <v>1.41</v>
@@ -32242,7 +32245,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32448,7 +32451,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32529,7 +32532,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ150">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR150">
         <v>1.35</v>
@@ -32860,7 +32863,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33272,7 +33275,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33684,7 +33687,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -34096,7 +34099,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34714,7 +34717,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -35207,7 +35210,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ163">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR163">
         <v>1.59</v>
@@ -35538,7 +35541,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35744,7 +35747,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q166">
         <v>2.5</v>
@@ -35825,7 +35828,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ166">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR166">
         <v>1.94</v>
@@ -36980,7 +36983,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37186,7 +37189,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37598,7 +37601,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -38010,7 +38013,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38294,7 +38297,7 @@
         <v>1.29</v>
       </c>
       <c r="AP178">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ178">
         <v>1</v>
@@ -38500,7 +38503,7 @@
         <v>1.17</v>
       </c>
       <c r="AP179">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ179">
         <v>1.33</v>
@@ -38628,7 +38631,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -39040,7 +39043,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39452,7 +39455,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -40276,7 +40279,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40563,7 +40566,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ189">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR189">
         <v>1.2</v>
@@ -40894,7 +40897,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41100,7 +41103,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41796,7 +41799,7 @@
         <v>0.29</v>
       </c>
       <c r="AP195">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ195">
         <v>0.53</v>
@@ -41924,7 +41927,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -42414,7 +42417,7 @@
         <v>0.25</v>
       </c>
       <c r="AP198">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ198">
         <v>0.27</v>
@@ -42954,7 +42957,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -43650,7 +43653,7 @@
         <v>1.67</v>
       </c>
       <c r="AP204">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ204">
         <v>1.63</v>
@@ -44190,7 +44193,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44808,7 +44811,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44886,7 +44889,7 @@
         <v>0.5</v>
       </c>
       <c r="AP210">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ210">
         <v>0.33</v>
@@ -45014,7 +45017,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45426,7 +45429,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45507,7 +45510,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ213">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR213">
         <v>1.34</v>
@@ -45632,7 +45635,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45838,7 +45841,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -46331,7 +46334,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ217">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR217">
         <v>1.92</v>
@@ -47692,7 +47695,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47898,7 +47901,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -48310,7 +48313,7 @@
         <v>95</v>
       </c>
       <c r="P227" t="s">
-        <v>373</v>
+        <v>325</v>
       </c>
       <c r="Q227">
         <v>3</v>
@@ -48722,7 +48725,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49215,7 +49218,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ231">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR231">
         <v>1.4</v>
@@ -49546,7 +49549,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49752,7 +49755,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -50657,7 +50660,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ238">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR238">
         <v>1.39</v>
@@ -50988,7 +50991,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51606,7 +51609,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51812,7 +51815,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -52096,7 +52099,7 @@
         <v>0.2</v>
       </c>
       <c r="AP245">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ245">
         <v>0.27</v>
@@ -52224,7 +52227,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52842,7 +52845,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -52920,7 +52923,7 @@
         <v>1.8</v>
       </c>
       <c r="AP249">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ249">
         <v>2</v>
@@ -53129,7 +53132,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ250">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR250">
         <v>1.41</v>
@@ -53460,7 +53463,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53872,7 +53875,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54902,7 +54905,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -55108,7 +55111,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55520,7 +55523,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -56010,7 +56013,7 @@
         <v>0.89</v>
       </c>
       <c r="AP264">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ264">
         <v>1.14</v>
@@ -56138,7 +56141,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56216,7 +56219,7 @@
         <v>1.91</v>
       </c>
       <c r="AP265">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ265">
         <v>2</v>
@@ -56344,7 +56347,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56962,7 +56965,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57249,7 +57252,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ270">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR270">
         <v>1.47</v>
@@ -57580,7 +57583,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57786,7 +57789,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -58070,7 +58073,7 @@
         <v>1.42</v>
       </c>
       <c r="AP274">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ274">
         <v>1.19</v>
@@ -58404,7 +58407,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58482,7 +58485,7 @@
         <v>1</v>
       </c>
       <c r="AP276">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ276">
         <v>1.2</v>
@@ -58610,7 +58613,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58816,7 +58819,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -59927,7 +59930,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ283">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR283">
         <v>1.45</v>
@@ -60670,7 +60673,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -61082,7 +61085,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61288,7 +61291,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61369,7 +61372,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ290">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR290">
         <v>1.4</v>
@@ -62112,7 +62115,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62730,7 +62733,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63554,7 +63557,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63760,7 +63763,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -64044,7 +64047,7 @@
         <v>0.85</v>
       </c>
       <c r="AP303">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ303">
         <v>1.06</v>
@@ -64172,7 +64175,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64378,7 +64381,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64665,7 +64668,7 @@
         <v>1.86</v>
       </c>
       <c r="AQ306">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR306">
         <v>1.49</v>
@@ -64790,7 +64793,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -65077,7 +65080,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ308">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR308">
         <v>1.55</v>
@@ -65408,7 +65411,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -65901,7 +65904,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ312">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR312">
         <v>1.26</v>
@@ -67340,7 +67343,7 @@
         <v>1</v>
       </c>
       <c r="AP319">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ319">
         <v>1</v>
@@ -67468,7 +67471,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -68498,7 +68501,7 @@
         <v>302</v>
       </c>
       <c r="P325" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q325">
         <v>2.5</v>
@@ -68704,7 +68707,7 @@
         <v>303</v>
       </c>
       <c r="P326" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q326">
         <v>3</v>
@@ -69116,7 +69119,7 @@
         <v>296</v>
       </c>
       <c r="P328" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69528,7 +69531,7 @@
         <v>95</v>
       </c>
       <c r="P330" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q330">
         <v>3.4</v>
@@ -69734,7 +69737,7 @@
         <v>305</v>
       </c>
       <c r="P331" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q331">
         <v>2.88</v>
@@ -69940,7 +69943,7 @@
         <v>306</v>
       </c>
       <c r="P332" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q332">
         <v>2.63</v>
@@ -70352,7 +70355,7 @@
         <v>308</v>
       </c>
       <c r="P334" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q334">
         <v>3.1</v>
@@ -70558,7 +70561,7 @@
         <v>309</v>
       </c>
       <c r="P335" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q335">
         <v>3</v>
@@ -70764,7 +70767,7 @@
         <v>95</v>
       </c>
       <c r="P336" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q336">
         <v>5.5</v>
@@ -70970,7 +70973,7 @@
         <v>95</v>
       </c>
       <c r="P337" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q337">
         <v>2.2</v>
@@ -71048,7 +71051,7 @@
         <v>1.08</v>
       </c>
       <c r="AP337">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AQ337">
         <v>1.21</v>
@@ -71176,7 +71179,7 @@
         <v>95</v>
       </c>
       <c r="P338" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q338">
         <v>2.75</v>
@@ -71666,7 +71669,7 @@
         <v>1</v>
       </c>
       <c r="AP340">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AQ340">
         <v>0.93</v>
@@ -71794,7 +71797,7 @@
         <v>311</v>
       </c>
       <c r="P341" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q341">
         <v>1.83</v>
@@ -72000,7 +72003,7 @@
         <v>95</v>
       </c>
       <c r="P342" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q342">
         <v>3.2</v>
@@ -72287,7 +72290,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ343">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="AR343">
         <v>1.42</v>
@@ -72618,7 +72621,7 @@
         <v>314</v>
       </c>
       <c r="P345" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q345">
         <v>3</v>
@@ -72699,7 +72702,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ345">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="AR345">
         <v>1.51</v>
@@ -73854,7 +73857,7 @@
         <v>95</v>
       </c>
       <c r="P351" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q351">
         <v>3.1</v>
@@ -74266,7 +74269,7 @@
         <v>146</v>
       </c>
       <c r="P353" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q353">
         <v>5.5</v>
@@ -74472,7 +74475,7 @@
         <v>197</v>
       </c>
       <c r="P354" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q354">
         <v>2.75</v>
@@ -74884,7 +74887,7 @@
         <v>95</v>
       </c>
       <c r="P356" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q356">
         <v>3.2</v>
@@ -75296,7 +75299,7 @@
         <v>289</v>
       </c>
       <c r="P358" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q358">
         <v>2.63</v>
@@ -75502,7 +75505,7 @@
         <v>95</v>
       </c>
       <c r="P359" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q359">
         <v>4.33</v>
@@ -75914,7 +75917,7 @@
         <v>321</v>
       </c>
       <c r="P361" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q361">
         <v>3</v>
@@ -76532,7 +76535,7 @@
         <v>95</v>
       </c>
       <c r="P364" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q364">
         <v>4.5</v>
@@ -76944,7 +76947,7 @@
         <v>324</v>
       </c>
       <c r="P366" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q366">
         <v>2.1</v>
@@ -77101,6 +77104,418 @@
       </c>
       <c r="BP366">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="367" spans="1:68">
+      <c r="A367" s="1">
+        <v>366</v>
+      </c>
+      <c r="B367">
+        <v>7479108</v>
+      </c>
+      <c r="C367" t="s">
+        <v>68</v>
+      </c>
+      <c r="D367" t="s">
+        <v>69</v>
+      </c>
+      <c r="E367" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F367">
+        <v>31</v>
+      </c>
+      <c r="G367" t="s">
+        <v>90</v>
+      </c>
+      <c r="H367" t="s">
+        <v>84</v>
+      </c>
+      <c r="I367">
+        <v>0</v>
+      </c>
+      <c r="J367">
+        <v>0</v>
+      </c>
+      <c r="K367">
+        <v>0</v>
+      </c>
+      <c r="L367">
+        <v>1</v>
+      </c>
+      <c r="M367">
+        <v>1</v>
+      </c>
+      <c r="N367">
+        <v>2</v>
+      </c>
+      <c r="O367" t="s">
+        <v>325</v>
+      </c>
+      <c r="P367" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q367">
+        <v>2.4</v>
+      </c>
+      <c r="R367">
+        <v>2.1</v>
+      </c>
+      <c r="S367">
+        <v>5</v>
+      </c>
+      <c r="T367">
+        <v>1.44</v>
+      </c>
+      <c r="U367">
+        <v>2.63</v>
+      </c>
+      <c r="V367">
+        <v>3.25</v>
+      </c>
+      <c r="W367">
+        <v>1.33</v>
+      </c>
+      <c r="X367">
+        <v>9</v>
+      </c>
+      <c r="Y367">
+        <v>1.07</v>
+      </c>
+      <c r="Z367">
+        <v>1.73</v>
+      </c>
+      <c r="AA367">
+        <v>3.73</v>
+      </c>
+      <c r="AB367">
+        <v>4.5</v>
+      </c>
+      <c r="AC367">
+        <v>1.06</v>
+      </c>
+      <c r="AD367">
+        <v>8.5</v>
+      </c>
+      <c r="AE367">
+        <v>1.33</v>
+      </c>
+      <c r="AF367">
+        <v>3.2</v>
+      </c>
+      <c r="AG367">
+        <v>1.92</v>
+      </c>
+      <c r="AH367">
+        <v>1.82</v>
+      </c>
+      <c r="AI367">
+        <v>1.91</v>
+      </c>
+      <c r="AJ367">
+        <v>1.8</v>
+      </c>
+      <c r="AK367">
+        <v>1.2</v>
+      </c>
+      <c r="AL367">
+        <v>1.22</v>
+      </c>
+      <c r="AM367">
+        <v>2</v>
+      </c>
+      <c r="AN367">
+        <v>1.86</v>
+      </c>
+      <c r="AO367">
+        <v>0.47</v>
+      </c>
+      <c r="AP367">
+        <v>1.8</v>
+      </c>
+      <c r="AQ367">
+        <v>0.5</v>
+      </c>
+      <c r="AR367">
+        <v>1.55</v>
+      </c>
+      <c r="AS367">
+        <v>1.06</v>
+      </c>
+      <c r="AT367">
+        <v>2.61</v>
+      </c>
+      <c r="AU367">
+        <v>3</v>
+      </c>
+      <c r="AV367">
+        <v>4</v>
+      </c>
+      <c r="AW367">
+        <v>5</v>
+      </c>
+      <c r="AX367">
+        <v>4</v>
+      </c>
+      <c r="AY367">
+        <v>10</v>
+      </c>
+      <c r="AZ367">
+        <v>10</v>
+      </c>
+      <c r="BA367">
+        <v>2</v>
+      </c>
+      <c r="BB367">
+        <v>4</v>
+      </c>
+      <c r="BC367">
+        <v>6</v>
+      </c>
+      <c r="BD367">
+        <v>1.62</v>
+      </c>
+      <c r="BE367">
+        <v>8.1</v>
+      </c>
+      <c r="BF367">
+        <v>3.26</v>
+      </c>
+      <c r="BG367">
+        <v>1.18</v>
+      </c>
+      <c r="BH367">
+        <v>4.2</v>
+      </c>
+      <c r="BI367">
+        <v>1.39</v>
+      </c>
+      <c r="BJ367">
+        <v>2.86</v>
+      </c>
+      <c r="BK367">
+        <v>1.69</v>
+      </c>
+      <c r="BL367">
+        <v>2.16</v>
+      </c>
+      <c r="BM367">
+        <v>2.09</v>
+      </c>
+      <c r="BN367">
+        <v>1.74</v>
+      </c>
+      <c r="BO367">
+        <v>2.69</v>
+      </c>
+      <c r="BP367">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="368" spans="1:68">
+      <c r="A368" s="1">
+        <v>367</v>
+      </c>
+      <c r="B368">
+        <v>7479111</v>
+      </c>
+      <c r="C368" t="s">
+        <v>68</v>
+      </c>
+      <c r="D368" t="s">
+        <v>69</v>
+      </c>
+      <c r="E368" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F368">
+        <v>31</v>
+      </c>
+      <c r="G368" t="s">
+        <v>86</v>
+      </c>
+      <c r="H368" t="s">
+        <v>85</v>
+      </c>
+      <c r="I368">
+        <v>1</v>
+      </c>
+      <c r="J368">
+        <v>1</v>
+      </c>
+      <c r="K368">
+        <v>2</v>
+      </c>
+      <c r="L368">
+        <v>2</v>
+      </c>
+      <c r="M368">
+        <v>1</v>
+      </c>
+      <c r="N368">
+        <v>3</v>
+      </c>
+      <c r="O368" t="s">
+        <v>326</v>
+      </c>
+      <c r="P368" t="s">
+        <v>431</v>
+      </c>
+      <c r="Q368">
+        <v>2.1</v>
+      </c>
+      <c r="R368">
+        <v>2.3</v>
+      </c>
+      <c r="S368">
+        <v>6</v>
+      </c>
+      <c r="T368">
+        <v>1.36</v>
+      </c>
+      <c r="U368">
+        <v>3</v>
+      </c>
+      <c r="V368">
+        <v>2.75</v>
+      </c>
+      <c r="W368">
+        <v>1.4</v>
+      </c>
+      <c r="X368">
+        <v>7</v>
+      </c>
+      <c r="Y368">
+        <v>1.1</v>
+      </c>
+      <c r="Z368">
+        <v>1.51</v>
+      </c>
+      <c r="AA368">
+        <v>4.2</v>
+      </c>
+      <c r="AB368">
+        <v>6</v>
+      </c>
+      <c r="AC368">
+        <v>1.04</v>
+      </c>
+      <c r="AD368">
+        <v>10</v>
+      </c>
+      <c r="AE368">
+        <v>1.25</v>
+      </c>
+      <c r="AF368">
+        <v>3.8</v>
+      </c>
+      <c r="AG368">
+        <v>1.8</v>
+      </c>
+      <c r="AH368">
+        <v>1.94</v>
+      </c>
+      <c r="AI368">
+        <v>1.91</v>
+      </c>
+      <c r="AJ368">
+        <v>1.8</v>
+      </c>
+      <c r="AK368">
+        <v>1.13</v>
+      </c>
+      <c r="AL368">
+        <v>1.17</v>
+      </c>
+      <c r="AM368">
+        <v>2.45</v>
+      </c>
+      <c r="AN368">
+        <v>2.29</v>
+      </c>
+      <c r="AO368">
+        <v>0.47</v>
+      </c>
+      <c r="AP368">
+        <v>2.33</v>
+      </c>
+      <c r="AQ368">
+        <v>0.44</v>
+      </c>
+      <c r="AR368">
+        <v>1.5</v>
+      </c>
+      <c r="AS368">
+        <v>0.98</v>
+      </c>
+      <c r="AT368">
+        <v>2.48</v>
+      </c>
+      <c r="AU368">
+        <v>4</v>
+      </c>
+      <c r="AV368">
+        <v>8</v>
+      </c>
+      <c r="AW368">
+        <v>8</v>
+      </c>
+      <c r="AX368">
+        <v>11</v>
+      </c>
+      <c r="AY368">
+        <v>14</v>
+      </c>
+      <c r="AZ368">
+        <v>22</v>
+      </c>
+      <c r="BA368">
+        <v>5</v>
+      </c>
+      <c r="BB368">
+        <v>5</v>
+      </c>
+      <c r="BC368">
+        <v>10</v>
+      </c>
+      <c r="BD368">
+        <v>1.54</v>
+      </c>
+      <c r="BE368">
+        <v>8.35</v>
+      </c>
+      <c r="BF368">
+        <v>3.58</v>
+      </c>
+      <c r="BG368">
+        <v>1.18</v>
+      </c>
+      <c r="BH368">
+        <v>4.24</v>
+      </c>
+      <c r="BI368">
+        <v>1.38</v>
+      </c>
+      <c r="BJ368">
+        <v>2.88</v>
+      </c>
+      <c r="BK368">
+        <v>1.68</v>
+      </c>
+      <c r="BL368">
+        <v>2.17</v>
+      </c>
+      <c r="BM368">
+        <v>2.08</v>
+      </c>
+      <c r="BN368">
+        <v>1.75</v>
+      </c>
+      <c r="BO368">
+        <v>2.67</v>
+      </c>
+      <c r="BP368">
+        <v>1.45</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="444">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1707,7 +1707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP368"/>
+  <dimension ref="A1:BP369"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3898,7 +3898,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ11">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -5955,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ21">
         <v>1.14</v>
@@ -7603,7 +7603,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ29">
         <v>1.06</v>
@@ -10284,7 +10284,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ42">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR42">
         <v>0.8100000000000001</v>
@@ -15637,7 +15637,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ68">
         <v>0.53</v>
@@ -16258,7 +16258,7 @@
         <v>1.6</v>
       </c>
       <c r="AQ71">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR71">
         <v>2.05</v>
@@ -20996,7 +20996,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ94">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR94">
         <v>1.56</v>
@@ -21611,7 +21611,7 @@
         <v>0</v>
       </c>
       <c r="AP97">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ97">
         <v>1.33</v>
@@ -24083,7 +24083,7 @@
         <v>0.25</v>
       </c>
       <c r="AP109">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ109">
         <v>0.73</v>
@@ -26146,7 +26146,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ119">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR119">
         <v>1.51</v>
@@ -26764,7 +26764,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ122">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR122">
         <v>1.52</v>
@@ -29439,7 +29439,7 @@
         <v>1.8</v>
       </c>
       <c r="AP135">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ135">
         <v>1.67</v>
@@ -31914,7 +31914,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ147">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR147">
         <v>1.08</v>
@@ -34795,7 +34795,7 @@
         <v>1.57</v>
       </c>
       <c r="AP161">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ161">
         <v>1.94</v>
@@ -38918,7 +38918,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ181">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR181">
         <v>1.38</v>
@@ -39327,7 +39327,7 @@
         <v>1.5</v>
       </c>
       <c r="AP183">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ183">
         <v>2</v>
@@ -43450,7 +43450,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ203">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR203">
         <v>1.33</v>
@@ -45301,7 +45301,7 @@
         <v>0.22</v>
       </c>
       <c r="AP212">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ212">
         <v>0.27</v>
@@ -47776,7 +47776,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ224">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR224">
         <v>1.39</v>
@@ -48806,7 +48806,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ229">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR229">
         <v>1.48</v>
@@ -51275,7 +51275,7 @@
         <v>1.11</v>
       </c>
       <c r="AP241">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ241">
         <v>1.2</v>
@@ -53544,7 +53544,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ252">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR252">
         <v>1.34</v>
@@ -56837,7 +56837,7 @@
         <v>0.4</v>
       </c>
       <c r="AP268">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ268">
         <v>0.33</v>
@@ -59927,7 +59927,7 @@
         <v>0.64</v>
       </c>
       <c r="AP283">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ283">
         <v>0.44</v>
@@ -61578,7 +61578,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ291">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR291">
         <v>1.38</v>
@@ -64665,7 +64665,7 @@
         <v>0.54</v>
       </c>
       <c r="AP306">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ306">
         <v>0.5</v>
@@ -66316,7 +66316,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ314">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR314">
         <v>1.51</v>
@@ -71672,7 +71672,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ340">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="AR340">
         <v>1.52</v>
@@ -72905,7 +72905,7 @@
         <v>1.23</v>
       </c>
       <c r="AP346">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="AQ346">
         <v>1.07</v>
@@ -77516,6 +77516,212 @@
       </c>
       <c r="BP368">
         <v>1.45</v>
+      </c>
+    </row>
+    <row r="369" spans="1:68">
+      <c r="A369" s="1">
+        <v>368</v>
+      </c>
+      <c r="B369">
+        <v>7479103</v>
+      </c>
+      <c r="C369" t="s">
+        <v>68</v>
+      </c>
+      <c r="D369" t="s">
+        <v>69</v>
+      </c>
+      <c r="E369" s="2">
+        <v>45697.375</v>
+      </c>
+      <c r="F369">
+        <v>31</v>
+      </c>
+      <c r="G369" t="s">
+        <v>89</v>
+      </c>
+      <c r="H369" t="s">
+        <v>88</v>
+      </c>
+      <c r="I369">
+        <v>0</v>
+      </c>
+      <c r="J369">
+        <v>0</v>
+      </c>
+      <c r="K369">
+        <v>0</v>
+      </c>
+      <c r="L369">
+        <v>0</v>
+      </c>
+      <c r="M369">
+        <v>1</v>
+      </c>
+      <c r="N369">
+        <v>1</v>
+      </c>
+      <c r="O369" t="s">
+        <v>95</v>
+      </c>
+      <c r="P369" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q369">
+        <v>2.5</v>
+      </c>
+      <c r="R369">
+        <v>2.1</v>
+      </c>
+      <c r="S369">
+        <v>4.75</v>
+      </c>
+      <c r="T369">
+        <v>1.44</v>
+      </c>
+      <c r="U369">
+        <v>2.63</v>
+      </c>
+      <c r="V369">
+        <v>3.25</v>
+      </c>
+      <c r="W369">
+        <v>1.33</v>
+      </c>
+      <c r="X369">
+        <v>9</v>
+      </c>
+      <c r="Y369">
+        <v>1.07</v>
+      </c>
+      <c r="Z369">
+        <v>1.87</v>
+      </c>
+      <c r="AA369">
+        <v>3.4</v>
+      </c>
+      <c r="AB369">
+        <v>4.2</v>
+      </c>
+      <c r="AC369">
+        <v>1.06</v>
+      </c>
+      <c r="AD369">
+        <v>10</v>
+      </c>
+      <c r="AE369">
+        <v>1.36</v>
+      </c>
+      <c r="AF369">
+        <v>3.2</v>
+      </c>
+      <c r="AG369">
+        <v>2.05</v>
+      </c>
+      <c r="AH369">
+        <v>1.7</v>
+      </c>
+      <c r="AI369">
+        <v>1.91</v>
+      </c>
+      <c r="AJ369">
+        <v>1.8</v>
+      </c>
+      <c r="AK369">
+        <v>1.22</v>
+      </c>
+      <c r="AL369">
+        <v>1.3</v>
+      </c>
+      <c r="AM369">
+        <v>1.88</v>
+      </c>
+      <c r="AN369">
+        <v>1.86</v>
+      </c>
+      <c r="AO369">
+        <v>0.93</v>
+      </c>
+      <c r="AP369">
+        <v>1.73</v>
+      </c>
+      <c r="AQ369">
+        <v>1.06</v>
+      </c>
+      <c r="AR369">
+        <v>1.47</v>
+      </c>
+      <c r="AS369">
+        <v>1.13</v>
+      </c>
+      <c r="AT369">
+        <v>2.6</v>
+      </c>
+      <c r="AU369">
+        <v>4</v>
+      </c>
+      <c r="AV369">
+        <v>6</v>
+      </c>
+      <c r="AW369">
+        <v>16</v>
+      </c>
+      <c r="AX369">
+        <v>4</v>
+      </c>
+      <c r="AY369">
+        <v>29</v>
+      </c>
+      <c r="AZ369">
+        <v>12</v>
+      </c>
+      <c r="BA369">
+        <v>11</v>
+      </c>
+      <c r="BB369">
+        <v>3</v>
+      </c>
+      <c r="BC369">
+        <v>14</v>
+      </c>
+      <c r="BD369">
+        <v>1.64</v>
+      </c>
+      <c r="BE369">
+        <v>8</v>
+      </c>
+      <c r="BF369">
+        <v>3.16</v>
+      </c>
+      <c r="BG369">
+        <v>1.2</v>
+      </c>
+      <c r="BH369">
+        <v>4.06</v>
+      </c>
+      <c r="BI369">
+        <v>1.41</v>
+      </c>
+      <c r="BJ369">
+        <v>2.79</v>
+      </c>
+      <c r="BK369">
+        <v>1.72</v>
+      </c>
+      <c r="BL369">
+        <v>2.12</v>
+      </c>
+      <c r="BM369">
+        <v>2.13</v>
+      </c>
+      <c r="BN369">
+        <v>1.71</v>
+      </c>
+      <c r="BO369">
+        <v>2.76</v>
+      </c>
+      <c r="BP369">
+        <v>1.42</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2276" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2306" uniqueCount="446">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -997,6 +997,9 @@
     <t>['24', '73']</t>
   </si>
   <si>
+    <t>['9', '17']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -1346,6 +1349,9 @@
   </si>
   <si>
     <t>['43', '46']</t>
+  </si>
+  <si>
+    <t>['20', '28', '35', '62']</t>
   </si>
 </sst>
 </file>
@@ -1707,7 +1713,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP369"/>
+  <dimension ref="A1:BP374"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1963,7 +1969,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -2169,7 +2175,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2375,7 +2381,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2787,7 +2793,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -3199,7 +3205,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3611,7 +3617,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -4229,7 +4235,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4435,7 +4441,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -4513,10 +4519,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ14">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4722,7 +4728,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ15">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4925,7 +4931,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ16">
         <v>1.29</v>
@@ -5131,7 +5137,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ17">
         <v>0.33</v>
@@ -5259,7 +5265,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5340,7 +5346,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ18">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR18">
         <v>0</v>
@@ -5543,7 +5549,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ19">
         <v>0.87</v>
@@ -5752,7 +5758,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ20">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR20">
         <v>0</v>
@@ -5877,7 +5883,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -6083,7 +6089,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6161,7 +6167,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ22">
         <v>1.07</v>
@@ -6370,7 +6376,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ23">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR23">
         <v>0</v>
@@ -6907,7 +6913,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -6988,7 +6994,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ26">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR26">
         <v>2.62</v>
@@ -7731,7 +7737,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -8015,7 +8021,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ31">
         <v>0.5</v>
@@ -8636,7 +8642,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ34">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR34">
         <v>1.56</v>
@@ -8761,7 +8767,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8967,7 +8973,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9045,7 +9051,7 @@
         <v>3</v>
       </c>
       <c r="AP36">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ36">
         <v>1.94</v>
@@ -9254,7 +9260,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ37">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR37">
         <v>1.5</v>
@@ -9379,7 +9385,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9460,7 +9466,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ38">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR38">
         <v>1.01</v>
@@ -9791,7 +9797,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -9997,7 +10003,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10075,7 +10081,7 @@
         <v>0</v>
       </c>
       <c r="AP41">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -10409,7 +10415,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -10487,7 +10493,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ43">
         <v>1.63</v>
@@ -11311,7 +11317,7 @@
         <v>1</v>
       </c>
       <c r="AP47">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ47">
         <v>1</v>
@@ -11520,7 +11526,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ48">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR48">
         <v>1.23</v>
@@ -11851,7 +11857,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -12753,10 +12759,10 @@
         <v>0.5</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ54">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR54">
         <v>1.24</v>
@@ -12959,7 +12965,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ55">
         <v>1.06</v>
@@ -13087,7 +13093,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13374,7 +13380,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ57">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR57">
         <v>1.82</v>
@@ -13911,7 +13917,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -13992,7 +13998,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ60">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR60">
         <v>1.85</v>
@@ -14117,7 +14123,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14195,7 +14201,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ61">
         <v>1.19</v>
@@ -14323,7 +14329,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14813,7 +14819,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ64">
         <v>0.8100000000000001</v>
@@ -15147,7 +15153,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15228,7 +15234,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ66">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR66">
         <v>1.23</v>
@@ -15640,7 +15646,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ68">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR68">
         <v>1.6</v>
@@ -15765,7 +15771,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -16177,7 +16183,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16255,7 +16261,7 @@
         <v>0</v>
       </c>
       <c r="AP71">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ71">
         <v>1.06</v>
@@ -16795,7 +16801,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -17082,7 +17088,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ75">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR75">
         <v>1.35</v>
@@ -17207,7 +17213,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17285,7 +17291,7 @@
         <v>1</v>
       </c>
       <c r="AP76">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ76">
         <v>1</v>
@@ -17413,7 +17419,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17825,7 +17831,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17903,7 +17909,7 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ79">
         <v>1.63</v>
@@ -18237,7 +18243,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -18318,7 +18324,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ81">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR81">
         <v>1.39</v>
@@ -18524,7 +18530,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ82">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR82">
         <v>1.37</v>
@@ -18727,7 +18733,7 @@
         <v>2.33</v>
       </c>
       <c r="AP83">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ83">
         <v>1.94</v>
@@ -19757,7 +19763,7 @@
         <v>1</v>
       </c>
       <c r="AP88">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ88">
         <v>1.07</v>
@@ -19885,7 +19891,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -19966,7 +19972,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ89">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR89">
         <v>1.26</v>
@@ -20375,10 +20381,10 @@
         <v>2.33</v>
       </c>
       <c r="AP91">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ91">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -20503,7 +20509,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -21739,7 +21745,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21820,7 +21826,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ98">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR98">
         <v>1.22</v>
@@ -22023,10 +22029,10 @@
         <v>0.25</v>
       </c>
       <c r="AP99">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ99">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR99">
         <v>1.08</v>
@@ -22229,7 +22235,7 @@
         <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ100">
         <v>1.21</v>
@@ -22438,7 +22444,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ101">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR101">
         <v>1.42</v>
@@ -22563,7 +22569,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22641,7 +22647,7 @@
         <v>0.25</v>
       </c>
       <c r="AP102">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ102">
         <v>1.33</v>
@@ -22769,7 +22775,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -23465,7 +23471,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ106">
         <v>1.29</v>
@@ -23877,10 +23883,10 @@
         <v>1.25</v>
       </c>
       <c r="AP108">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ108">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR108">
         <v>1.27</v>
@@ -24086,7 +24092,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ109">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR109">
         <v>1.56</v>
@@ -25241,7 +25247,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25447,7 +25453,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25859,7 +25865,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -26889,7 +26895,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -27095,7 +27101,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -28537,7 +28543,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -29155,7 +29161,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29233,7 +29239,7 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ134">
         <v>1.33</v>
@@ -29442,7 +29448,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ135">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR135">
         <v>1.5</v>
@@ -29567,7 +29573,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -29645,7 +29651,7 @@
         <v>0.8</v>
       </c>
       <c r="AP136">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ136">
         <v>0.33</v>
@@ -29851,7 +29857,7 @@
         <v>0.6</v>
       </c>
       <c r="AP137">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ137">
         <v>1.07</v>
@@ -30266,7 +30272,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ139">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR139">
         <v>1.36</v>
@@ -30472,7 +30478,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ140">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR140">
         <v>1.3</v>
@@ -30803,7 +30809,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -30884,7 +30890,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ142">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR142">
         <v>1.64</v>
@@ -31087,7 +31093,7 @@
         <v>1.4</v>
       </c>
       <c r="AP143">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ143">
         <v>1.21</v>
@@ -31296,7 +31302,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ144">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR144">
         <v>1.29</v>
@@ -31421,7 +31427,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31499,7 +31505,7 @@
         <v>1.2</v>
       </c>
       <c r="AP145">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ145">
         <v>1.29</v>
@@ -31627,7 +31633,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31833,7 +31839,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -32245,7 +32251,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32451,7 +32457,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32863,7 +32869,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33275,7 +33281,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33687,7 +33693,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -34099,7 +34105,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34717,7 +34723,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -35416,7 +35422,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ164">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR164">
         <v>1.43</v>
@@ -35541,7 +35547,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35747,7 +35753,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q166">
         <v>2.5</v>
@@ -35825,7 +35831,7 @@
         <v>0.29</v>
       </c>
       <c r="AP166">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ166">
         <v>0.5</v>
@@ -36034,7 +36040,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ167">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR167">
         <v>1.4</v>
@@ -36649,10 +36655,10 @@
         <v>0.33</v>
       </c>
       <c r="AP170">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ170">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR170">
         <v>1.45</v>
@@ -36983,7 +36989,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37189,7 +37195,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37476,7 +37482,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ174">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR174">
         <v>1.88</v>
@@ -37601,7 +37607,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -37885,10 +37891,10 @@
         <v>0.5</v>
       </c>
       <c r="AP176">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ176">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR176">
         <v>1.24</v>
@@ -38013,7 +38019,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38091,7 +38097,7 @@
         <v>0.14</v>
       </c>
       <c r="AP177">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ177">
         <v>0.27</v>
@@ -38297,7 +38303,7 @@
         <v>1.29</v>
       </c>
       <c r="AP178">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ178">
         <v>1</v>
@@ -38631,7 +38637,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -39043,7 +39049,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39455,7 +39461,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -39533,7 +39539,7 @@
         <v>1.75</v>
       </c>
       <c r="AP184">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ184">
         <v>1.94</v>
@@ -39742,7 +39748,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ185">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR185">
         <v>1.45</v>
@@ -40279,7 +40285,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40897,7 +40903,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41103,7 +41109,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41184,7 +41190,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ192">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR192">
         <v>1.35</v>
@@ -41387,7 +41393,7 @@
         <v>1.5</v>
       </c>
       <c r="AP193">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ193">
         <v>1</v>
@@ -41596,7 +41602,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ194">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR194">
         <v>1.32</v>
@@ -41802,7 +41808,7 @@
         <v>2.33</v>
       </c>
       <c r="AQ195">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR195">
         <v>1.46</v>
@@ -41927,7 +41933,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -42417,7 +42423,7 @@
         <v>0.25</v>
       </c>
       <c r="AP198">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ198">
         <v>0.27</v>
@@ -42957,7 +42963,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -43038,7 +43044,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ201">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR201">
         <v>1.58</v>
@@ -43447,7 +43453,7 @@
         <v>0.88</v>
       </c>
       <c r="AP203">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ203">
         <v>1.06</v>
@@ -43859,10 +43865,10 @@
         <v>1.13</v>
       </c>
       <c r="AP205">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ205">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR205">
         <v>1.43</v>
@@ -44193,7 +44199,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44480,7 +44486,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ208">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR208">
         <v>1.36</v>
@@ -44811,7 +44817,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44889,7 +44895,7 @@
         <v>0.5</v>
       </c>
       <c r="AP210">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ210">
         <v>0.33</v>
@@ -45017,7 +45023,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45095,10 +45101,10 @@
         <v>0.5</v>
       </c>
       <c r="AP211">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ211">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR211">
         <v>1.94</v>
@@ -45429,7 +45435,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45635,7 +45641,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45841,7 +45847,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -45919,7 +45925,7 @@
         <v>1.25</v>
       </c>
       <c r="AP215">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ215">
         <v>1.33</v>
@@ -46540,7 +46546,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ218">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR218">
         <v>1.44</v>
@@ -47361,7 +47367,7 @@
         <v>1.33</v>
       </c>
       <c r="AP222">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ222">
         <v>1</v>
@@ -47695,7 +47701,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47901,7 +47907,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -48597,7 +48603,7 @@
         <v>0.9</v>
       </c>
       <c r="AP228">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ228">
         <v>1</v>
@@ -48725,7 +48731,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49549,7 +49555,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49755,7 +49761,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -49836,7 +49842,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ234">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR234">
         <v>1.65</v>
@@ -50248,7 +50254,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ236">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR236">
         <v>1.67</v>
@@ -50657,7 +50663,7 @@
         <v>0.78</v>
       </c>
       <c r="AP238">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ238">
         <v>0.44</v>
@@ -50866,7 +50872,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ239">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR239">
         <v>1.26</v>
@@ -50991,7 +50997,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51069,7 +51075,7 @@
         <v>0.89</v>
       </c>
       <c r="AP240">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ240">
         <v>1.21</v>
@@ -51278,7 +51284,7 @@
         <v>1.73</v>
       </c>
       <c r="AQ241">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR241">
         <v>1.43</v>
@@ -51609,7 +51615,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51690,7 +51696,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ243">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR243">
         <v>1.27</v>
@@ -51815,7 +51821,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -52227,7 +52233,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52717,7 +52723,7 @@
         <v>1.7</v>
       </c>
       <c r="AP248">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ248">
         <v>1.19</v>
@@ -52845,7 +52851,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -52923,7 +52929,7 @@
         <v>1.8</v>
       </c>
       <c r="AP249">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ249">
         <v>2</v>
@@ -53463,7 +53469,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53747,7 +53753,7 @@
         <v>0.91</v>
       </c>
       <c r="AP253">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ253">
         <v>1.06</v>
@@ -53875,7 +53881,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54574,7 +54580,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ257">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR257">
         <v>1.86</v>
@@ -54905,7 +54911,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -55111,7 +55117,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55192,7 +55198,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ260">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR260">
         <v>1.65</v>
@@ -55523,7 +55529,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -55604,7 +55610,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ262">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR262">
         <v>1.06</v>
@@ -56013,7 +56019,7 @@
         <v>0.89</v>
       </c>
       <c r="AP264">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ264">
         <v>1.14</v>
@@ -56141,7 +56147,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56347,7 +56353,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56634,7 +56640,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ267">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR267">
         <v>1.39</v>
@@ -56965,7 +56971,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57249,7 +57255,7 @@
         <v>0.7</v>
       </c>
       <c r="AP270">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ270">
         <v>0.44</v>
@@ -57455,7 +57461,7 @@
         <v>0.18</v>
       </c>
       <c r="AP271">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ271">
         <v>0.27</v>
@@ -57583,7 +57589,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57661,7 +57667,7 @@
         <v>1.55</v>
       </c>
       <c r="AP272">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ272">
         <v>1.19</v>
@@ -57789,7 +57795,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -57870,7 +57876,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ273">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR273">
         <v>1.28</v>
@@ -58407,7 +58413,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58485,10 +58491,10 @@
         <v>1</v>
       </c>
       <c r="AP276">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ276">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR276">
         <v>1.44</v>
@@ -58613,7 +58619,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58819,7 +58825,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -58897,10 +58903,10 @@
         <v>0.55</v>
       </c>
       <c r="AP278">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ278">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR278">
         <v>1.47</v>
@@ -59721,7 +59727,7 @@
         <v>0.8</v>
       </c>
       <c r="AP282">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ282">
         <v>1.14</v>
@@ -60133,10 +60139,10 @@
         <v>1.55</v>
       </c>
       <c r="AP284">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ284">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR284">
         <v>1.42</v>
@@ -60673,7 +60679,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -60960,7 +60966,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ288">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR288">
         <v>1.32</v>
@@ -61085,7 +61091,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61166,7 +61172,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ289">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR289">
         <v>1.34</v>
@@ -61291,7 +61297,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61575,7 +61581,7 @@
         <v>1.17</v>
       </c>
       <c r="AP291">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ291">
         <v>1.06</v>
@@ -62115,7 +62121,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62733,7 +62739,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63557,7 +63563,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63763,7 +63769,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -63844,7 +63850,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ302">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR302">
         <v>1.22</v>
@@ -64047,7 +64053,7 @@
         <v>0.85</v>
       </c>
       <c r="AP303">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ303">
         <v>1.06</v>
@@ -64175,7 +64181,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64253,7 +64259,7 @@
         <v>1.69</v>
       </c>
       <c r="AP304">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ304">
         <v>1.94</v>
@@ -64381,7 +64387,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64462,7 +64468,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ305">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR305">
         <v>1.29</v>
@@ -64793,7 +64799,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -64874,7 +64880,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ307">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR307">
         <v>1.51</v>
@@ -65411,7 +65417,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -65698,7 +65704,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ311">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR311">
         <v>1.49</v>
@@ -66522,7 +66528,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ315">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR315">
         <v>1.45</v>
@@ -67471,7 +67477,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -67549,7 +67555,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP320">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ320">
         <v>0.8100000000000001</v>
@@ -67755,7 +67761,7 @@
         <v>1.08</v>
       </c>
       <c r="AP321">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ321">
         <v>1</v>
@@ -67964,7 +67970,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ322">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR322">
         <v>1.41</v>
@@ -68167,7 +68173,7 @@
         <v>1.5</v>
       </c>
       <c r="AP323">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ323">
         <v>1.29</v>
@@ -68501,7 +68507,7 @@
         <v>302</v>
       </c>
       <c r="P325" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q325">
         <v>2.5</v>
@@ -68579,10 +68585,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP325">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ325">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR325">
         <v>1.43</v>
@@ -68707,7 +68713,7 @@
         <v>303</v>
       </c>
       <c r="P326" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q326">
         <v>3</v>
@@ -69119,7 +69125,7 @@
         <v>296</v>
       </c>
       <c r="P328" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69403,7 +69409,7 @@
         <v>1.43</v>
       </c>
       <c r="AP329">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ329">
         <v>1.63</v>
@@ -69531,7 +69537,7 @@
         <v>95</v>
       </c>
       <c r="P330" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q330">
         <v>3.4</v>
@@ -69737,7 +69743,7 @@
         <v>305</v>
       </c>
       <c r="P331" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q331">
         <v>2.88</v>
@@ -69818,7 +69824,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ331">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR331">
         <v>1.31</v>
@@ -69943,7 +69949,7 @@
         <v>306</v>
       </c>
       <c r="P332" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q332">
         <v>2.63</v>
@@ -70024,7 +70030,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ332">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR332">
         <v>1.34</v>
@@ -70355,7 +70361,7 @@
         <v>308</v>
       </c>
       <c r="P334" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q334">
         <v>3.1</v>
@@ -70433,7 +70439,7 @@
         <v>0.77</v>
       </c>
       <c r="AP334">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ334">
         <v>0.87</v>
@@ -70561,7 +70567,7 @@
         <v>309</v>
       </c>
       <c r="P335" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q335">
         <v>3</v>
@@ -70767,7 +70773,7 @@
         <v>95</v>
       </c>
       <c r="P336" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q336">
         <v>5.5</v>
@@ -70973,7 +70979,7 @@
         <v>95</v>
       </c>
       <c r="P337" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q337">
         <v>2.2</v>
@@ -71179,7 +71185,7 @@
         <v>95</v>
       </c>
       <c r="P338" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q338">
         <v>2.75</v>
@@ -71466,7 +71472,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ339">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR339">
         <v>1.25</v>
@@ -71669,7 +71675,7 @@
         <v>1</v>
       </c>
       <c r="AP340">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ340">
         <v>1.06</v>
@@ -71797,7 +71803,7 @@
         <v>311</v>
       </c>
       <c r="P341" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q341">
         <v>1.83</v>
@@ -72003,7 +72009,7 @@
         <v>95</v>
       </c>
       <c r="P342" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q342">
         <v>3.2</v>
@@ -72493,7 +72499,7 @@
         <v>0.86</v>
       </c>
       <c r="AP344">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ344">
         <v>0.8100000000000001</v>
@@ -72621,7 +72627,7 @@
         <v>314</v>
       </c>
       <c r="P345" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q345">
         <v>3</v>
@@ -73320,7 +73326,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ348">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR348">
         <v>1.45</v>
@@ -73523,7 +73529,7 @@
         <v>1</v>
       </c>
       <c r="AP349">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ349">
         <v>1.14</v>
@@ -73732,7 +73738,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ350">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR350">
         <v>1.29</v>
@@ -73857,7 +73863,7 @@
         <v>95</v>
       </c>
       <c r="P351" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q351">
         <v>3.1</v>
@@ -73935,7 +73941,7 @@
         <v>0.87</v>
       </c>
       <c r="AP351">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AQ351">
         <v>1</v>
@@ -74269,7 +74275,7 @@
         <v>146</v>
       </c>
       <c r="P353" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q353">
         <v>5.5</v>
@@ -74475,7 +74481,7 @@
         <v>197</v>
       </c>
       <c r="P354" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q354">
         <v>2.75</v>
@@ -74759,7 +74765,7 @@
         <v>2.07</v>
       </c>
       <c r="AP355">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ355">
         <v>2</v>
@@ -74887,7 +74893,7 @@
         <v>95</v>
       </c>
       <c r="P356" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q356">
         <v>3.2</v>
@@ -75174,7 +75180,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ357">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR357">
         <v>1.89</v>
@@ -75299,7 +75305,7 @@
         <v>289</v>
       </c>
       <c r="P358" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q358">
         <v>2.63</v>
@@ -75505,7 +75511,7 @@
         <v>95</v>
       </c>
       <c r="P359" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q359">
         <v>4.33</v>
@@ -75583,7 +75589,7 @@
         <v>1.87</v>
       </c>
       <c r="AP359">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AQ359">
         <v>1.94</v>
@@ -75792,7 +75798,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ360">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR360">
         <v>1.33</v>
@@ -75917,7 +75923,7 @@
         <v>321</v>
       </c>
       <c r="P361" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q361">
         <v>3</v>
@@ -76204,7 +76210,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ362">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR362">
         <v>1.39</v>
@@ -76535,7 +76541,7 @@
         <v>95</v>
       </c>
       <c r="P364" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q364">
         <v>4.5</v>
@@ -76613,10 +76619,10 @@
         <v>1.57</v>
       </c>
       <c r="AP364">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="AQ364">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AR364">
         <v>1.82</v>
@@ -76947,7 +76953,7 @@
         <v>324</v>
       </c>
       <c r="P366" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q366">
         <v>2.1</v>
@@ -77231,7 +77237,7 @@
         <v>0.47</v>
       </c>
       <c r="AP367">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ367">
         <v>0.5</v>
@@ -77359,7 +77365,7 @@
         <v>326</v>
       </c>
       <c r="P368" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q368">
         <v>2.1</v>
@@ -77722,6 +77728,1036 @@
       </c>
       <c r="BP369">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="370" spans="1:68">
+      <c r="A370" s="1">
+        <v>369</v>
+      </c>
+      <c r="B370">
+        <v>7479120</v>
+      </c>
+      <c r="C370" t="s">
+        <v>68</v>
+      </c>
+      <c r="D370" t="s">
+        <v>69</v>
+      </c>
+      <c r="E370" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F370">
+        <v>32</v>
+      </c>
+      <c r="G370" t="s">
+        <v>85</v>
+      </c>
+      <c r="H370" t="s">
+        <v>78</v>
+      </c>
+      <c r="I370">
+        <v>2</v>
+      </c>
+      <c r="J370">
+        <v>1</v>
+      </c>
+      <c r="K370">
+        <v>3</v>
+      </c>
+      <c r="L370">
+        <v>2</v>
+      </c>
+      <c r="M370">
+        <v>1</v>
+      </c>
+      <c r="N370">
+        <v>3</v>
+      </c>
+      <c r="O370" t="s">
+        <v>327</v>
+      </c>
+      <c r="P370" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q370">
+        <v>3.1</v>
+      </c>
+      <c r="R370">
+        <v>2.05</v>
+      </c>
+      <c r="S370">
+        <v>3.75</v>
+      </c>
+      <c r="T370">
+        <v>1.44</v>
+      </c>
+      <c r="U370">
+        <v>2.63</v>
+      </c>
+      <c r="V370">
+        <v>3.4</v>
+      </c>
+      <c r="W370">
+        <v>1.3</v>
+      </c>
+      <c r="X370">
+        <v>10</v>
+      </c>
+      <c r="Y370">
+        <v>1.06</v>
+      </c>
+      <c r="Z370">
+        <v>2.34</v>
+      </c>
+      <c r="AA370">
+        <v>3.38</v>
+      </c>
+      <c r="AB370">
+        <v>2.88</v>
+      </c>
+      <c r="AC370">
+        <v>1.07</v>
+      </c>
+      <c r="AD370">
+        <v>10</v>
+      </c>
+      <c r="AE370">
+        <v>1.36</v>
+      </c>
+      <c r="AF370">
+        <v>3.2</v>
+      </c>
+      <c r="AG370">
+        <v>1.98</v>
+      </c>
+      <c r="AH370">
+        <v>1.77</v>
+      </c>
+      <c r="AI370">
+        <v>1.83</v>
+      </c>
+      <c r="AJ370">
+        <v>1.83</v>
+      </c>
+      <c r="AK370">
+        <v>1.36</v>
+      </c>
+      <c r="AL370">
+        <v>1.28</v>
+      </c>
+      <c r="AM370">
+        <v>1.66</v>
+      </c>
+      <c r="AN370">
+        <v>1.53</v>
+      </c>
+      <c r="AO370">
+        <v>0.73</v>
+      </c>
+      <c r="AP370">
+        <v>1.63</v>
+      </c>
+      <c r="AQ370">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR370">
+        <v>1.51</v>
+      </c>
+      <c r="AS370">
+        <v>1.11</v>
+      </c>
+      <c r="AT370">
+        <v>2.62</v>
+      </c>
+      <c r="AU370">
+        <v>7</v>
+      </c>
+      <c r="AV370">
+        <v>7</v>
+      </c>
+      <c r="AW370">
+        <v>15</v>
+      </c>
+      <c r="AX370">
+        <v>6</v>
+      </c>
+      <c r="AY370">
+        <v>30</v>
+      </c>
+      <c r="AZ370">
+        <v>15</v>
+      </c>
+      <c r="BA370">
+        <v>10</v>
+      </c>
+      <c r="BB370">
+        <v>4</v>
+      </c>
+      <c r="BC370">
+        <v>14</v>
+      </c>
+      <c r="BD370">
+        <v>1.73</v>
+      </c>
+      <c r="BE370">
+        <v>6.75</v>
+      </c>
+      <c r="BF370">
+        <v>2.32</v>
+      </c>
+      <c r="BG370">
+        <v>1.21</v>
+      </c>
+      <c r="BH370">
+        <v>3.8</v>
+      </c>
+      <c r="BI370">
+        <v>1.38</v>
+      </c>
+      <c r="BJ370">
+        <v>2.7</v>
+      </c>
+      <c r="BK370">
+        <v>1.63</v>
+      </c>
+      <c r="BL370">
+        <v>2.1</v>
+      </c>
+      <c r="BM370">
+        <v>1.98</v>
+      </c>
+      <c r="BN370">
+        <v>1.72</v>
+      </c>
+      <c r="BO370">
+        <v>2.48</v>
+      </c>
+      <c r="BP370">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="371" spans="1:68">
+      <c r="A371" s="1">
+        <v>370</v>
+      </c>
+      <c r="B371">
+        <v>7479117</v>
+      </c>
+      <c r="C371" t="s">
+        <v>68</v>
+      </c>
+      <c r="D371" t="s">
+        <v>69</v>
+      </c>
+      <c r="E371" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F371">
+        <v>32</v>
+      </c>
+      <c r="G371" t="s">
+        <v>84</v>
+      </c>
+      <c r="H371" t="s">
+        <v>73</v>
+      </c>
+      <c r="I371">
+        <v>0</v>
+      </c>
+      <c r="J371">
+        <v>0</v>
+      </c>
+      <c r="K371">
+        <v>0</v>
+      </c>
+      <c r="L371">
+        <v>0</v>
+      </c>
+      <c r="M371">
+        <v>0</v>
+      </c>
+      <c r="N371">
+        <v>0</v>
+      </c>
+      <c r="O371" t="s">
+        <v>95</v>
+      </c>
+      <c r="P371" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q371">
+        <v>2.75</v>
+      </c>
+      <c r="R371">
+        <v>2.05</v>
+      </c>
+      <c r="S371">
+        <v>4.33</v>
+      </c>
+      <c r="T371">
+        <v>1.44</v>
+      </c>
+      <c r="U371">
+        <v>2.63</v>
+      </c>
+      <c r="V371">
+        <v>3.25</v>
+      </c>
+      <c r="W371">
+        <v>1.33</v>
+      </c>
+      <c r="X371">
+        <v>10</v>
+      </c>
+      <c r="Y371">
+        <v>1.06</v>
+      </c>
+      <c r="Z371">
+        <v>1.99</v>
+      </c>
+      <c r="AA371">
+        <v>3.47</v>
+      </c>
+      <c r="AB371">
+        <v>3.57</v>
+      </c>
+      <c r="AC371">
+        <v>1.08</v>
+      </c>
+      <c r="AD371">
+        <v>8.5</v>
+      </c>
+      <c r="AE371">
+        <v>1.42</v>
+      </c>
+      <c r="AF371">
+        <v>2.9</v>
+      </c>
+      <c r="AG371">
+        <v>2.2</v>
+      </c>
+      <c r="AH371">
+        <v>1.61</v>
+      </c>
+      <c r="AI371">
+        <v>1.91</v>
+      </c>
+      <c r="AJ371">
+        <v>1.8</v>
+      </c>
+      <c r="AK371">
+        <v>1.26</v>
+      </c>
+      <c r="AL371">
+        <v>1.3</v>
+      </c>
+      <c r="AM371">
+        <v>1.78</v>
+      </c>
+      <c r="AN371">
+        <v>1.33</v>
+      </c>
+      <c r="AO371">
+        <v>0.53</v>
+      </c>
+      <c r="AP371">
+        <v>1.31</v>
+      </c>
+      <c r="AQ371">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AR371">
+        <v>1.38</v>
+      </c>
+      <c r="AS371">
+        <v>1.02</v>
+      </c>
+      <c r="AT371">
+        <v>2.4</v>
+      </c>
+      <c r="AU371">
+        <v>5</v>
+      </c>
+      <c r="AV371">
+        <v>2</v>
+      </c>
+      <c r="AW371">
+        <v>10</v>
+      </c>
+      <c r="AX371">
+        <v>5</v>
+      </c>
+      <c r="AY371">
+        <v>19</v>
+      </c>
+      <c r="AZ371">
+        <v>10</v>
+      </c>
+      <c r="BA371">
+        <v>3</v>
+      </c>
+      <c r="BB371">
+        <v>4</v>
+      </c>
+      <c r="BC371">
+        <v>7</v>
+      </c>
+      <c r="BD371">
+        <v>1.35</v>
+      </c>
+      <c r="BE371">
+        <v>7.5</v>
+      </c>
+      <c r="BF371">
+        <v>3.45</v>
+      </c>
+      <c r="BG371">
+        <v>1.18</v>
+      </c>
+      <c r="BH371">
+        <v>4.1</v>
+      </c>
+      <c r="BI371">
+        <v>1.33</v>
+      </c>
+      <c r="BJ371">
+        <v>2.95</v>
+      </c>
+      <c r="BK371">
+        <v>1.54</v>
+      </c>
+      <c r="BL371">
+        <v>2.28</v>
+      </c>
+      <c r="BM371">
+        <v>1.85</v>
+      </c>
+      <c r="BN371">
+        <v>1.83</v>
+      </c>
+      <c r="BO371">
+        <v>2.3</v>
+      </c>
+      <c r="BP371">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="372" spans="1:68">
+      <c r="A372" s="1">
+        <v>371</v>
+      </c>
+      <c r="B372">
+        <v>7479116</v>
+      </c>
+      <c r="C372" t="s">
+        <v>68</v>
+      </c>
+      <c r="D372" t="s">
+        <v>69</v>
+      </c>
+      <c r="E372" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F372">
+        <v>32</v>
+      </c>
+      <c r="G372" t="s">
+        <v>82</v>
+      </c>
+      <c r="H372" t="s">
+        <v>72</v>
+      </c>
+      <c r="I372">
+        <v>0</v>
+      </c>
+      <c r="J372">
+        <v>0</v>
+      </c>
+      <c r="K372">
+        <v>0</v>
+      </c>
+      <c r="L372">
+        <v>1</v>
+      </c>
+      <c r="M372">
+        <v>0</v>
+      </c>
+      <c r="N372">
+        <v>1</v>
+      </c>
+      <c r="O372" t="s">
+        <v>218</v>
+      </c>
+      <c r="P372" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q372">
+        <v>2.3</v>
+      </c>
+      <c r="R372">
+        <v>2.15</v>
+      </c>
+      <c r="S372">
+        <v>4.5</v>
+      </c>
+      <c r="T372">
+        <v>1.38</v>
+      </c>
+      <c r="U372">
+        <v>2.8</v>
+      </c>
+      <c r="V372">
+        <v>2.7</v>
+      </c>
+      <c r="W372">
+        <v>1.4</v>
+      </c>
+      <c r="X372">
+        <v>7</v>
+      </c>
+      <c r="Y372">
+        <v>1.08</v>
+      </c>
+      <c r="Z372">
+        <v>1.74</v>
+      </c>
+      <c r="AA372">
+        <v>3.65</v>
+      </c>
+      <c r="AB372">
+        <v>4.5</v>
+      </c>
+      <c r="AC372">
+        <v>1.05</v>
+      </c>
+      <c r="AD372">
+        <v>9.5</v>
+      </c>
+      <c r="AE372">
+        <v>1.3</v>
+      </c>
+      <c r="AF372">
+        <v>3.45</v>
+      </c>
+      <c r="AG372">
+        <v>1.91</v>
+      </c>
+      <c r="AH372">
+        <v>1.83</v>
+      </c>
+      <c r="AI372">
+        <v>1.85</v>
+      </c>
+      <c r="AJ372">
+        <v>1.83</v>
+      </c>
+      <c r="AK372">
+        <v>1.2</v>
+      </c>
+      <c r="AL372">
+        <v>1.27</v>
+      </c>
+      <c r="AM372">
+        <v>2</v>
+      </c>
+      <c r="AN372">
+        <v>1.6</v>
+      </c>
+      <c r="AO372">
+        <v>1.2</v>
+      </c>
+      <c r="AP372">
+        <v>1.69</v>
+      </c>
+      <c r="AQ372">
+        <v>1.13</v>
+      </c>
+      <c r="AR372">
+        <v>1.79</v>
+      </c>
+      <c r="AS372">
+        <v>0.9</v>
+      </c>
+      <c r="AT372">
+        <v>2.69</v>
+      </c>
+      <c r="AU372">
+        <v>7</v>
+      </c>
+      <c r="AV372">
+        <v>4</v>
+      </c>
+      <c r="AW372">
+        <v>5</v>
+      </c>
+      <c r="AX372">
+        <v>9</v>
+      </c>
+      <c r="AY372">
+        <v>12</v>
+      </c>
+      <c r="AZ372">
+        <v>14</v>
+      </c>
+      <c r="BA372">
+        <v>10</v>
+      </c>
+      <c r="BB372">
+        <v>9</v>
+      </c>
+      <c r="BC372">
+        <v>19</v>
+      </c>
+      <c r="BD372">
+        <v>1.48</v>
+      </c>
+      <c r="BE372">
+        <v>9.5</v>
+      </c>
+      <c r="BF372">
+        <v>3.2</v>
+      </c>
+      <c r="BG372">
+        <v>1.11</v>
+      </c>
+      <c r="BH372">
+        <v>4.9</v>
+      </c>
+      <c r="BI372">
+        <v>1.25</v>
+      </c>
+      <c r="BJ372">
+        <v>3.28</v>
+      </c>
+      <c r="BK372">
+        <v>1.47</v>
+      </c>
+      <c r="BL372">
+        <v>2.42</v>
+      </c>
+      <c r="BM372">
+        <v>1.82</v>
+      </c>
+      <c r="BN372">
+        <v>1.88</v>
+      </c>
+      <c r="BO372">
+        <v>2.28</v>
+      </c>
+      <c r="BP372">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="373" spans="1:68">
+      <c r="A373" s="1">
+        <v>372</v>
+      </c>
+      <c r="B373">
+        <v>7479122</v>
+      </c>
+      <c r="C373" t="s">
+        <v>68</v>
+      </c>
+      <c r="D373" t="s">
+        <v>69</v>
+      </c>
+      <c r="E373" s="2">
+        <v>45699.69791666666</v>
+      </c>
+      <c r="F373">
+        <v>32</v>
+      </c>
+      <c r="G373" t="s">
+        <v>87</v>
+      </c>
+      <c r="H373" t="s">
+        <v>76</v>
+      </c>
+      <c r="I373">
+        <v>0</v>
+      </c>
+      <c r="J373">
+        <v>3</v>
+      </c>
+      <c r="K373">
+        <v>3</v>
+      </c>
+      <c r="L373">
+        <v>0</v>
+      </c>
+      <c r="M373">
+        <v>4</v>
+      </c>
+      <c r="N373">
+        <v>4</v>
+      </c>
+      <c r="O373" t="s">
+        <v>95</v>
+      </c>
+      <c r="P373" t="s">
+        <v>445</v>
+      </c>
+      <c r="Q373">
+        <v>5.5</v>
+      </c>
+      <c r="R373">
+        <v>2.5</v>
+      </c>
+      <c r="S373">
+        <v>2</v>
+      </c>
+      <c r="T373">
+        <v>1.29</v>
+      </c>
+      <c r="U373">
+        <v>3.5</v>
+      </c>
+      <c r="V373">
+        <v>2.38</v>
+      </c>
+      <c r="W373">
+        <v>1.53</v>
+      </c>
+      <c r="X373">
+        <v>5.5</v>
+      </c>
+      <c r="Y373">
+        <v>1.14</v>
+      </c>
+      <c r="Z373">
+        <v>5.9</v>
+      </c>
+      <c r="AA373">
+        <v>4.3</v>
+      </c>
+      <c r="AB373">
+        <v>1.49</v>
+      </c>
+      <c r="AC373">
+        <v>1.03</v>
+      </c>
+      <c r="AD373">
+        <v>15</v>
+      </c>
+      <c r="AE373">
+        <v>1.24</v>
+      </c>
+      <c r="AF373">
+        <v>4.2</v>
+      </c>
+      <c r="AG373">
+        <v>1.73</v>
+      </c>
+      <c r="AH373">
+        <v>2</v>
+      </c>
+      <c r="AI373">
+        <v>1.67</v>
+      </c>
+      <c r="AJ373">
+        <v>2.1</v>
+      </c>
+      <c r="AK373">
+        <v>2.7</v>
+      </c>
+      <c r="AL373">
+        <v>1.17</v>
+      </c>
+      <c r="AM373">
+        <v>1.1</v>
+      </c>
+      <c r="AN373">
+        <v>1.93</v>
+      </c>
+      <c r="AO373">
+        <v>1.67</v>
+      </c>
+      <c r="AP373">
+        <v>1.81</v>
+      </c>
+      <c r="AQ373">
+        <v>1.75</v>
+      </c>
+      <c r="AR373">
+        <v>1.42</v>
+      </c>
+      <c r="AS373">
+        <v>1.57</v>
+      </c>
+      <c r="AT373">
+        <v>2.99</v>
+      </c>
+      <c r="AU373">
+        <v>3</v>
+      </c>
+      <c r="AV373">
+        <v>8</v>
+      </c>
+      <c r="AW373">
+        <v>4</v>
+      </c>
+      <c r="AX373">
+        <v>11</v>
+      </c>
+      <c r="AY373">
+        <v>9</v>
+      </c>
+      <c r="AZ373">
+        <v>29</v>
+      </c>
+      <c r="BA373">
+        <v>7</v>
+      </c>
+      <c r="BB373">
+        <v>7</v>
+      </c>
+      <c r="BC373">
+        <v>14</v>
+      </c>
+      <c r="BD373">
+        <v>3.05</v>
+      </c>
+      <c r="BE373">
+        <v>7</v>
+      </c>
+      <c r="BF373">
+        <v>1.45</v>
+      </c>
+      <c r="BG373">
+        <v>1.26</v>
+      </c>
+      <c r="BH373">
+        <v>3.4</v>
+      </c>
+      <c r="BI373">
+        <v>1.44</v>
+      </c>
+      <c r="BJ373">
+        <v>2.55</v>
+      </c>
+      <c r="BK373">
+        <v>1.72</v>
+      </c>
+      <c r="BL373">
+        <v>1.97</v>
+      </c>
+      <c r="BM373">
+        <v>2.15</v>
+      </c>
+      <c r="BN373">
+        <v>1.61</v>
+      </c>
+      <c r="BO373">
+        <v>2.7</v>
+      </c>
+      <c r="BP373">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="374" spans="1:68">
+      <c r="A374" s="1">
+        <v>373</v>
+      </c>
+      <c r="B374">
+        <v>7479118</v>
+      </c>
+      <c r="C374" t="s">
+        <v>68</v>
+      </c>
+      <c r="D374" t="s">
+        <v>69</v>
+      </c>
+      <c r="E374" s="2">
+        <v>45699.70833333334</v>
+      </c>
+      <c r="F374">
+        <v>32</v>
+      </c>
+      <c r="G374" t="s">
+        <v>90</v>
+      </c>
+      <c r="H374" t="s">
+        <v>71</v>
+      </c>
+      <c r="I374">
+        <v>0</v>
+      </c>
+      <c r="J374">
+        <v>1</v>
+      </c>
+      <c r="K374">
+        <v>1</v>
+      </c>
+      <c r="L374">
+        <v>0</v>
+      </c>
+      <c r="M374">
+        <v>1</v>
+      </c>
+      <c r="N374">
+        <v>1</v>
+      </c>
+      <c r="O374" t="s">
+        <v>95</v>
+      </c>
+      <c r="P374" t="s">
+        <v>417</v>
+      </c>
+      <c r="Q374">
+        <v>2.4</v>
+      </c>
+      <c r="R374">
+        <v>2.25</v>
+      </c>
+      <c r="S374">
+        <v>4.5</v>
+      </c>
+      <c r="T374">
+        <v>1.36</v>
+      </c>
+      <c r="U374">
+        <v>3</v>
+      </c>
+      <c r="V374">
+        <v>2.75</v>
+      </c>
+      <c r="W374">
+        <v>1.4</v>
+      </c>
+      <c r="X374">
+        <v>7</v>
+      </c>
+      <c r="Y374">
+        <v>1.1</v>
+      </c>
+      <c r="Z374">
+        <v>1.78</v>
+      </c>
+      <c r="AA374">
+        <v>3.55</v>
+      </c>
+      <c r="AB374">
+        <v>4.4</v>
+      </c>
+      <c r="AC374">
+        <v>1.06</v>
+      </c>
+      <c r="AD374">
+        <v>10</v>
+      </c>
+      <c r="AE374">
+        <v>1.35</v>
+      </c>
+      <c r="AF374">
+        <v>3.25</v>
+      </c>
+      <c r="AG374">
+        <v>1.77</v>
+      </c>
+      <c r="AH374">
+        <v>1.98</v>
+      </c>
+      <c r="AI374">
+        <v>1.73</v>
+      </c>
+      <c r="AJ374">
+        <v>2</v>
+      </c>
+      <c r="AK374">
+        <v>1.2</v>
+      </c>
+      <c r="AL374">
+        <v>1.24</v>
+      </c>
+      <c r="AM374">
+        <v>2.1</v>
+      </c>
+      <c r="AN374">
+        <v>1.8</v>
+      </c>
+      <c r="AO374">
+        <v>0.8</v>
+      </c>
+      <c r="AP374">
+        <v>1.69</v>
+      </c>
+      <c r="AQ374">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR374">
+        <v>1.52</v>
+      </c>
+      <c r="AS374">
+        <v>1.1</v>
+      </c>
+      <c r="AT374">
+        <v>2.62</v>
+      </c>
+      <c r="AU374">
+        <v>2</v>
+      </c>
+      <c r="AV374">
+        <v>2</v>
+      </c>
+      <c r="AW374">
+        <v>9</v>
+      </c>
+      <c r="AX374">
+        <v>7</v>
+      </c>
+      <c r="AY374">
+        <v>17</v>
+      </c>
+      <c r="AZ374">
+        <v>12</v>
+      </c>
+      <c r="BA374">
+        <v>8</v>
+      </c>
+      <c r="BB374">
+        <v>3</v>
+      </c>
+      <c r="BC374">
+        <v>11</v>
+      </c>
+      <c r="BD374">
+        <v>1.49</v>
+      </c>
+      <c r="BE374">
+        <v>6.75</v>
+      </c>
+      <c r="BF374">
+        <v>2.9</v>
+      </c>
+      <c r="BG374">
+        <v>1.29</v>
+      </c>
+      <c r="BH374">
+        <v>3.15</v>
+      </c>
+      <c r="BI374">
+        <v>1.5</v>
+      </c>
+      <c r="BJ374">
+        <v>2.38</v>
+      </c>
+      <c r="BK374">
+        <v>1.81</v>
+      </c>
+      <c r="BL374">
+        <v>1.88</v>
+      </c>
+      <c r="BM374">
+        <v>2.28</v>
+      </c>
+      <c r="BN374">
+        <v>1.54</v>
+      </c>
+      <c r="BO374">
+        <v>2.9</v>
+      </c>
+      <c r="BP374">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2348" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2354" uniqueCount="452">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -973,10 +973,10 @@
     <t>['59']</t>
   </si>
   <si>
-    <t>['6', '13', '50', '65', '67', '88', '90+5']</t>
+    <t>['1', '25']</t>
   </si>
   <si>
-    <t>['1', '25']</t>
+    <t>['6', '13', '50', '65', '67', '88', '90+5']</t>
   </si>
   <si>
     <t>['11', '59']</t>
@@ -1013,6 +1013,9 @@
   </si>
   <si>
     <t>['32', '75', '87']</t>
+  </si>
+  <si>
+    <t>['21', '35', '57', '66']</t>
   </si>
   <si>
     <t>['67', '88']</t>
@@ -1728,7 +1731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP381"/>
+  <dimension ref="A1:BP382"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1984,7 +1987,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -2065,7 +2068,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ2">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2190,7 +2193,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2396,7 +2399,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2474,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ4">
         <v>1.19</v>
@@ -2808,7 +2811,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -3220,7 +3223,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3632,7 +3635,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -4250,7 +4253,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4456,7 +4459,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -5280,7 +5283,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5898,7 +5901,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -6104,7 +6107,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6928,7 +6931,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -7418,7 +7421,7 @@
         <v>0</v>
       </c>
       <c r="AP28">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ28">
         <v>0.27</v>
@@ -7752,7 +7755,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -8039,7 +8042,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ31">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR31">
         <v>2.07</v>
@@ -8782,7 +8785,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -8988,7 +8991,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9400,7 +9403,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9812,7 +9815,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -10018,7 +10021,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10430,7 +10433,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -11872,7 +11875,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -13108,7 +13111,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13932,7 +13935,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -14138,7 +14141,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14344,7 +14347,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -15040,7 +15043,7 @@
         <v>0.5</v>
       </c>
       <c r="AP65">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ65">
         <v>1.07</v>
@@ -15168,7 +15171,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15786,7 +15789,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -16198,7 +16201,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16485,7 +16488,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ72">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR72">
         <v>1.52</v>
@@ -16816,7 +16819,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -17228,7 +17231,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17434,7 +17437,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17846,7 +17849,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -18258,7 +18261,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -19906,7 +19909,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -20193,7 +20196,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ90">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR90">
         <v>1.26</v>
@@ -20524,7 +20527,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -20602,7 +20605,7 @@
         <v>1.33</v>
       </c>
       <c r="AP92">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ92">
         <v>1.13</v>
@@ -21760,7 +21763,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -22584,7 +22587,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22790,7 +22793,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -25262,7 +25265,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25468,7 +25471,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25546,7 +25549,7 @@
         <v>0.5</v>
       </c>
       <c r="AP116">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ116">
         <v>0.44</v>
@@ -25880,7 +25883,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -26373,7 +26376,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ120">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR120">
         <v>1.42</v>
@@ -26910,7 +26913,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -27116,7 +27119,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -27815,7 +27818,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ127">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR127">
         <v>1.11</v>
@@ -28018,7 +28021,7 @@
         <v>0.4</v>
       </c>
       <c r="AP128">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ128">
         <v>1.06</v>
@@ -28558,7 +28561,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -29176,7 +29179,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29588,7 +29591,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -30824,7 +30827,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -31442,7 +31445,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31648,7 +31651,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31854,7 +31857,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -32141,7 +32144,7 @@
         <v>1.27</v>
       </c>
       <c r="AQ148">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR148">
         <v>1.41</v>
@@ -32266,7 +32269,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32472,7 +32475,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32884,7 +32887,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33168,7 +33171,7 @@
         <v>2</v>
       </c>
       <c r="AP153">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ153">
         <v>1.63</v>
@@ -33296,7 +33299,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33708,7 +33711,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -34120,7 +34123,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34198,7 +34201,7 @@
         <v>1.17</v>
       </c>
       <c r="AP158">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ158">
         <v>1.2</v>
@@ -34738,7 +34741,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -35562,7 +35565,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -35849,7 +35852,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ166">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR166">
         <v>1.94</v>
@@ -37004,7 +37007,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37210,7 +37213,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37622,7 +37625,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -38034,7 +38037,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38652,7 +38655,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -39064,7 +39067,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39476,7 +39479,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -40300,7 +40303,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40587,7 +40590,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ189">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR189">
         <v>1.2</v>
@@ -40790,7 +40793,7 @@
         <v>1</v>
       </c>
       <c r="AP190">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ190">
         <v>0.8100000000000001</v>
@@ -40918,7 +40921,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41124,7 +41127,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41948,7 +41951,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -42978,7 +42981,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -44214,7 +44217,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44832,7 +44835,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -45038,7 +45041,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45450,7 +45453,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45656,7 +45659,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45862,7 +45865,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -46355,7 +46358,7 @@
         <v>2.56</v>
       </c>
       <c r="AQ217">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR217">
         <v>1.92</v>
@@ -47588,7 +47591,7 @@
         <v>1</v>
       </c>
       <c r="AP223">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ223">
         <v>1</v>
@@ -47716,7 +47719,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47922,7 +47925,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -48746,7 +48749,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49239,7 +49242,7 @@
         <v>2</v>
       </c>
       <c r="AQ231">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR231">
         <v>1.4</v>
@@ -49570,7 +49573,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49776,7 +49779,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -50266,7 +50269,7 @@
         <v>0.25</v>
       </c>
       <c r="AP236">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ236">
         <v>0.5600000000000001</v>
@@ -51012,7 +51015,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51630,7 +51633,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51836,7 +51839,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -52248,7 +52251,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52866,7 +52869,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53153,7 +53156,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ250">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR250">
         <v>1.41</v>
@@ -53484,7 +53487,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53896,7 +53899,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54926,7 +54929,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -55132,7 +55135,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55210,7 +55213,7 @@
         <v>0.8</v>
       </c>
       <c r="AP260">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ260">
         <v>0.9399999999999999</v>
@@ -55544,7 +55547,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -56162,7 +56165,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56368,7 +56371,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56986,7 +56989,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57604,7 +57607,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57810,7 +57813,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -58428,7 +58431,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58634,7 +58637,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58840,7 +58843,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -60566,7 +60569,7 @@
         <v>0.73</v>
       </c>
       <c r="AP286">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ286">
         <v>0.8100000000000001</v>
@@ -60694,7 +60697,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -61106,7 +61109,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61312,7 +61315,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61393,7 +61396,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ290">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR290">
         <v>1.4</v>
@@ -62136,7 +62139,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62754,7 +62757,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63578,7 +63581,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63784,7 +63787,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -64196,7 +64199,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64402,7 +64405,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64689,7 +64692,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ306">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR306">
         <v>1.49</v>
@@ -64814,7 +64817,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -65304,7 +65307,7 @@
         <v>0.33</v>
       </c>
       <c r="AP309">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ309">
         <v>0.31</v>
@@ -65432,7 +65435,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -67492,7 +67495,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -68522,7 +68525,7 @@
         <v>302</v>
       </c>
       <c r="P325" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q325">
         <v>2.5</v>
@@ -68728,7 +68731,7 @@
         <v>303</v>
       </c>
       <c r="P326" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q326">
         <v>3</v>
@@ -69140,7 +69143,7 @@
         <v>296</v>
       </c>
       <c r="P328" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69552,7 +69555,7 @@
         <v>95</v>
       </c>
       <c r="P330" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q330">
         <v>3.4</v>
@@ -69758,7 +69761,7 @@
         <v>305</v>
       </c>
       <c r="P331" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q331">
         <v>2.88</v>
@@ -69964,7 +69967,7 @@
         <v>306</v>
       </c>
       <c r="P332" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q332">
         <v>2.63</v>
@@ -70376,7 +70379,7 @@
         <v>308</v>
       </c>
       <c r="P334" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q334">
         <v>3.1</v>
@@ -70582,7 +70585,7 @@
         <v>309</v>
       </c>
       <c r="P335" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q335">
         <v>3</v>
@@ -70788,7 +70791,7 @@
         <v>95</v>
       </c>
       <c r="P336" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q336">
         <v>5.5</v>
@@ -70994,7 +70997,7 @@
         <v>95</v>
       </c>
       <c r="P337" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q337">
         <v>2.2</v>
@@ -71200,7 +71203,7 @@
         <v>95</v>
       </c>
       <c r="P338" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q338">
         <v>2.75</v>
@@ -71818,7 +71821,7 @@
         <v>311</v>
       </c>
       <c r="P341" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q341">
         <v>1.83</v>
@@ -72024,7 +72027,7 @@
         <v>95</v>
       </c>
       <c r="P342" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q342">
         <v>3.2</v>
@@ -72102,7 +72105,7 @@
         <v>1.31</v>
       </c>
       <c r="AP342">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ342">
         <v>1.44</v>
@@ -72642,7 +72645,7 @@
         <v>314</v>
       </c>
       <c r="P345" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q345">
         <v>3</v>
@@ -72723,7 +72726,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ345">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR345">
         <v>1.51</v>
@@ -73878,7 +73881,7 @@
         <v>95</v>
       </c>
       <c r="P351" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q351">
         <v>3.1</v>
@@ -74290,7 +74293,7 @@
         <v>146</v>
       </c>
       <c r="P353" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q353">
         <v>5.5</v>
@@ -74454,7 +74457,7 @@
         <v>353</v>
       </c>
       <c r="B354">
-        <v>7479100</v>
+        <v>7479294</v>
       </c>
       <c r="C354" t="s">
         <v>68</v>
@@ -74469,55 +74472,55 @@
         <v>30</v>
       </c>
       <c r="G354" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H354" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I354">
         <v>0</v>
       </c>
       <c r="J354">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K354">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L354">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M354">
         <v>1</v>
       </c>
       <c r="N354">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O354" t="s">
-        <v>197</v>
+        <v>95</v>
       </c>
       <c r="P354" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="Q354">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="R354">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S354">
-        <v>4.33</v>
+        <v>2.88</v>
       </c>
       <c r="T354">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="U354">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V354">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="W354">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X354">
         <v>10</v>
@@ -74526,133 +74529,133 @@
         <v>1.06</v>
       </c>
       <c r="Z354">
+        <v>3.6</v>
+      </c>
+      <c r="AA354">
+        <v>3.1</v>
+      </c>
+      <c r="AB354">
+        <v>2.15</v>
+      </c>
+      <c r="AC354">
+        <v>1.09</v>
+      </c>
+      <c r="AD354">
+        <v>7</v>
+      </c>
+      <c r="AE354">
+        <v>1.42</v>
+      </c>
+      <c r="AF354">
+        <v>2.8</v>
+      </c>
+      <c r="AG354">
+        <v>2.3</v>
+      </c>
+      <c r="AH354">
+        <v>1.62</v>
+      </c>
+      <c r="AI354">
+        <v>1.91</v>
+      </c>
+      <c r="AJ354">
+        <v>1.8</v>
+      </c>
+      <c r="AK354">
+        <v>1.65</v>
+      </c>
+      <c r="AL354">
+        <v>1.33</v>
+      </c>
+      <c r="AM354">
+        <v>1.3</v>
+      </c>
+      <c r="AN354">
+        <v>1.43</v>
+      </c>
+      <c r="AO354">
+        <v>1.87</v>
+      </c>
+      <c r="AP354">
+        <v>1.31</v>
+      </c>
+      <c r="AQ354">
+        <v>1.94</v>
+      </c>
+      <c r="AR354">
+        <v>1.38</v>
+      </c>
+      <c r="AS354">
+        <v>1.29</v>
+      </c>
+      <c r="AT354">
+        <v>2.67</v>
+      </c>
+      <c r="AU354">
+        <v>3</v>
+      </c>
+      <c r="AV354">
+        <v>4</v>
+      </c>
+      <c r="AW354">
+        <v>9</v>
+      </c>
+      <c r="AX354">
+        <v>3</v>
+      </c>
+      <c r="AY354">
+        <v>15</v>
+      </c>
+      <c r="AZ354">
+        <v>7</v>
+      </c>
+      <c r="BA354">
+        <v>2</v>
+      </c>
+      <c r="BB354">
+        <v>2</v>
+      </c>
+      <c r="BC354">
+        <v>4</v>
+      </c>
+      <c r="BD354">
+        <v>1.98</v>
+      </c>
+      <c r="BE354">
+        <v>6.75</v>
+      </c>
+      <c r="BF354">
         <v>1.96</v>
       </c>
-      <c r="AA354">
-        <v>3.41</v>
-      </c>
-      <c r="AB354">
-        <v>3.75</v>
-      </c>
-      <c r="AC354">
-        <v>1.07</v>
-      </c>
-      <c r="AD354">
-        <v>8</v>
-      </c>
-      <c r="AE354">
-        <v>1.36</v>
-      </c>
-      <c r="AF354">
-        <v>3.1</v>
-      </c>
-      <c r="AG354">
-        <v>1.98</v>
-      </c>
-      <c r="AH354">
-        <v>1.77</v>
-      </c>
-      <c r="AI354">
-        <v>1.83</v>
-      </c>
-      <c r="AJ354">
-        <v>1.83</v>
-      </c>
-      <c r="AK354">
-        <v>1.28</v>
-      </c>
-      <c r="AL354">
-        <v>1.32</v>
-      </c>
-      <c r="AM354">
-        <v>1.72</v>
-      </c>
-      <c r="AN354">
-        <v>1.4</v>
-      </c>
-      <c r="AO354">
-        <v>0.29</v>
-      </c>
-      <c r="AP354">
-        <v>1.38</v>
-      </c>
-      <c r="AQ354">
-        <v>0.31</v>
-      </c>
-      <c r="AR354">
-        <v>1.41</v>
-      </c>
-      <c r="AS354">
-        <v>1.13</v>
-      </c>
-      <c r="AT354">
+      <c r="BG354">
+        <v>1.1</v>
+      </c>
+      <c r="BH354">
+        <v>5.45</v>
+      </c>
+      <c r="BI354">
+        <v>1.26</v>
+      </c>
+      <c r="BJ354">
+        <v>3.52</v>
+      </c>
+      <c r="BK354">
+        <v>1.5</v>
+      </c>
+      <c r="BL354">
         <v>2.54</v>
       </c>
-      <c r="AU354">
-        <v>4</v>
-      </c>
-      <c r="AV354">
-        <v>2</v>
-      </c>
-      <c r="AW354">
-        <v>15</v>
-      </c>
-      <c r="AX354">
-        <v>7</v>
-      </c>
-      <c r="AY354">
-        <v>22</v>
-      </c>
-      <c r="AZ354">
-        <v>13</v>
-      </c>
-      <c r="BA354">
-        <v>9</v>
-      </c>
-      <c r="BB354">
-        <v>5</v>
-      </c>
-      <c r="BC354">
-        <v>14</v>
-      </c>
-      <c r="BD354">
-        <v>1.5</v>
-      </c>
-      <c r="BE354">
-        <v>7</v>
-      </c>
-      <c r="BF354">
-        <v>2.8</v>
-      </c>
-      <c r="BG354">
-        <v>1.13</v>
-      </c>
-      <c r="BH354">
-        <v>4.99</v>
-      </c>
-      <c r="BI354">
-        <v>1.3</v>
-      </c>
-      <c r="BJ354">
-        <v>3.28</v>
-      </c>
-      <c r="BK354">
-        <v>1.55</v>
-      </c>
-      <c r="BL354">
-        <v>2.4</v>
-      </c>
       <c r="BM354">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="BN354">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BO354">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="BP354">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="355" spans="1:68">
@@ -74660,7 +74663,7 @@
         <v>354</v>
       </c>
       <c r="B355">
-        <v>7479099</v>
+        <v>7479100</v>
       </c>
       <c r="C355" t="s">
         <v>68</v>
@@ -74675,43 +74678,43 @@
         <v>30</v>
       </c>
       <c r="G355" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H355" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="I355">
         <v>0</v>
       </c>
       <c r="J355">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K355">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L355">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M355">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N355">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O355" t="s">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="P355" t="s">
-        <v>95</v>
+        <v>348</v>
       </c>
       <c r="Q355">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="R355">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S355">
-        <v>2.3</v>
+        <v>4.33</v>
       </c>
       <c r="T355">
         <v>1.44</v>
@@ -74720,25 +74723,25 @@
         <v>2.63</v>
       </c>
       <c r="V355">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="W355">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X355">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y355">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z355">
-        <v>5.5</v>
+        <v>1.96</v>
       </c>
       <c r="AA355">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="AB355">
-        <v>1.66</v>
+        <v>3.75</v>
       </c>
       <c r="AC355">
         <v>1.07</v>
@@ -74747,10 +74750,10 @@
         <v>8</v>
       </c>
       <c r="AE355">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AF355">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AG355">
         <v>1.98</v>
@@ -74759,106 +74762,106 @@
         <v>1.77</v>
       </c>
       <c r="AI355">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AJ355">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AK355">
-        <v>2.15</v>
+        <v>1.28</v>
       </c>
       <c r="AL355">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AM355">
-        <v>1.14</v>
+        <v>1.72</v>
       </c>
       <c r="AN355">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AO355">
-        <v>2.07</v>
+        <v>0.29</v>
       </c>
       <c r="AP355">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AQ355">
-        <v>2</v>
+        <v>0.31</v>
       </c>
       <c r="AR355">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="AS355">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="AT355">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="AU355">
         <v>4</v>
       </c>
       <c r="AV355">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AW355">
+        <v>15</v>
+      </c>
+      <c r="AX355">
+        <v>7</v>
+      </c>
+      <c r="AY355">
+        <v>22</v>
+      </c>
+      <c r="AZ355">
+        <v>13</v>
+      </c>
+      <c r="BA355">
+        <v>9</v>
+      </c>
+      <c r="BB355">
+        <v>5</v>
+      </c>
+      <c r="BC355">
         <v>14</v>
       </c>
-      <c r="AX355">
-        <v>9</v>
-      </c>
-      <c r="AY355">
-        <v>19</v>
-      </c>
-      <c r="AZ355">
-        <v>15</v>
-      </c>
-      <c r="BA355">
-        <v>3</v>
-      </c>
-      <c r="BB355">
-        <v>3</v>
-      </c>
-      <c r="BC355">
-        <v>6</v>
-      </c>
       <c r="BD355">
-        <v>2.43</v>
+        <v>1.5</v>
       </c>
       <c r="BE355">
         <v>7</v>
       </c>
       <c r="BF355">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="BG355">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BH355">
-        <v>4.78</v>
+        <v>4.99</v>
       </c>
       <c r="BI355">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BJ355">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="BK355">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="BL355">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="BM355">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="BN355">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="BO355">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="BP355">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="356" spans="1:68">
@@ -74908,7 +74911,7 @@
         <v>95</v>
       </c>
       <c r="P356" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q356">
         <v>3.2</v>
@@ -75072,7 +75075,7 @@
         <v>356</v>
       </c>
       <c r="B357">
-        <v>7479094</v>
+        <v>7479096</v>
       </c>
       <c r="C357" t="s">
         <v>68</v>
@@ -75087,190 +75090,190 @@
         <v>30</v>
       </c>
       <c r="G357" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H357" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="I357">
         <v>2</v>
       </c>
       <c r="J357">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K357">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L357">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M357">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N357">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O357" t="s">
         <v>319</v>
       </c>
       <c r="P357" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="Q357">
+        <v>3.1</v>
+      </c>
+      <c r="R357">
+        <v>1.95</v>
+      </c>
+      <c r="S357">
+        <v>4</v>
+      </c>
+      <c r="T357">
+        <v>1.53</v>
+      </c>
+      <c r="U357">
+        <v>2.38</v>
+      </c>
+      <c r="V357">
+        <v>3.75</v>
+      </c>
+      <c r="W357">
+        <v>1.25</v>
+      </c>
+      <c r="X357">
+        <v>11</v>
+      </c>
+      <c r="Y357">
+        <v>1.05</v>
+      </c>
+      <c r="Z357">
+        <v>2.3</v>
+      </c>
+      <c r="AA357">
+        <v>3</v>
+      </c>
+      <c r="AB357">
+        <v>3.3</v>
+      </c>
+      <c r="AC357">
+        <v>1.1</v>
+      </c>
+      <c r="AD357">
+        <v>6.5</v>
+      </c>
+      <c r="AE357">
+        <v>1.53</v>
+      </c>
+      <c r="AF357">
+        <v>2.38</v>
+      </c>
+      <c r="AG357">
+        <v>2.37</v>
+      </c>
+      <c r="AH357">
+        <v>1.53</v>
+      </c>
+      <c r="AI357">
+        <v>2</v>
+      </c>
+      <c r="AJ357">
         <v>1.73</v>
       </c>
-      <c r="R357">
-        <v>2.5</v>
-      </c>
-      <c r="S357">
-        <v>10</v>
-      </c>
-      <c r="T357">
+      <c r="AK357">
         <v>1.33</v>
       </c>
-      <c r="U357">
-        <v>3.25</v>
-      </c>
-      <c r="V357">
-        <v>2.5</v>
-      </c>
-      <c r="W357">
+      <c r="AL357">
+        <v>1.33</v>
+      </c>
+      <c r="AM357">
+        <v>1.57</v>
+      </c>
+      <c r="AN357">
+        <v>1.4</v>
+      </c>
+      <c r="AO357">
+        <v>1.29</v>
+      </c>
+      <c r="AP357">
         <v>1.5</v>
       </c>
-      <c r="X357">
-        <v>6.5</v>
-      </c>
-      <c r="Y357">
-        <v>1.11</v>
-      </c>
-      <c r="Z357">
-        <v>1.22</v>
-      </c>
-      <c r="AA357">
-        <v>5.9</v>
-      </c>
-      <c r="AB357">
+      <c r="AQ357">
+        <v>1.13</v>
+      </c>
+      <c r="AR357">
+        <v>1.33</v>
+      </c>
+      <c r="AS357">
+        <v>0.85</v>
+      </c>
+      <c r="AT357">
+        <v>2.18</v>
+      </c>
+      <c r="AU357">
+        <v>5</v>
+      </c>
+      <c r="AV357">
+        <v>6</v>
+      </c>
+      <c r="AW357">
+        <v>2</v>
+      </c>
+      <c r="AX357">
+        <v>8</v>
+      </c>
+      <c r="AY357">
+        <v>9</v>
+      </c>
+      <c r="AZ357">
+        <v>15</v>
+      </c>
+      <c r="BA357">
+        <v>2</v>
+      </c>
+      <c r="BB357">
+        <v>11</v>
+      </c>
+      <c r="BC357">
         <v>13</v>
       </c>
-      <c r="AC357">
-        <v>1.04</v>
-      </c>
-      <c r="AD357">
-        <v>10</v>
-      </c>
-      <c r="AE357">
-        <v>1.22</v>
-      </c>
-      <c r="AF357">
-        <v>4.2</v>
-      </c>
-      <c r="AG357">
-        <v>1.75</v>
-      </c>
-      <c r="AH357">
-        <v>2</v>
-      </c>
-      <c r="AI357">
-        <v>2.38</v>
-      </c>
-      <c r="AJ357">
-        <v>1.53</v>
-      </c>
-      <c r="AK357">
-        <v>1.05</v>
-      </c>
-      <c r="AL357">
+      <c r="BD357">
+        <v>1.78</v>
+      </c>
+      <c r="BE357">
+        <v>6.75</v>
+      </c>
+      <c r="BF357">
+        <v>2.2</v>
+      </c>
+      <c r="BG357">
         <v>1.13</v>
       </c>
-      <c r="AM357">
-        <v>3.7</v>
-      </c>
-      <c r="AN357">
-        <v>2.53</v>
-      </c>
-      <c r="AO357">
-        <v>0.79</v>
-      </c>
-      <c r="AP357">
-        <v>2.56</v>
-      </c>
-      <c r="AQ357">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AR357">
-        <v>1.89</v>
-      </c>
-      <c r="AS357">
-        <v>1.15</v>
-      </c>
-      <c r="AT357">
-        <v>3.04</v>
-      </c>
-      <c r="AU357">
-        <v>14</v>
-      </c>
-      <c r="AV357">
-        <v>3</v>
-      </c>
-      <c r="AW357">
-        <v>17</v>
-      </c>
-      <c r="AX357">
-        <v>0</v>
-      </c>
-      <c r="AY357">
-        <v>35</v>
-      </c>
-      <c r="AZ357">
-        <v>3</v>
-      </c>
-      <c r="BA357">
-        <v>14</v>
-      </c>
-      <c r="BB357">
-        <v>1</v>
-      </c>
-      <c r="BC357">
-        <v>15</v>
-      </c>
-      <c r="BD357">
-        <v>1.15</v>
-      </c>
-      <c r="BE357">
-        <v>9.5</v>
-      </c>
-      <c r="BF357">
-        <v>5.6</v>
-      </c>
-      <c r="BG357">
-        <v>1.19</v>
-      </c>
       <c r="BH357">
-        <v>4.09</v>
+        <v>4.88</v>
       </c>
       <c r="BI357">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="BJ357">
-        <v>2.8</v>
+        <v>3.22</v>
       </c>
       <c r="BK357">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="BL357">
-        <v>2.13</v>
+        <v>2.37</v>
       </c>
       <c r="BM357">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="BN357">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="BO357">
-        <v>2.75</v>
+        <v>2.42</v>
       </c>
       <c r="BP357">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="358" spans="1:68">
@@ -75278,7 +75281,7 @@
         <v>357</v>
       </c>
       <c r="B358">
-        <v>7479093</v>
+        <v>7479094</v>
       </c>
       <c r="C358" t="s">
         <v>68</v>
@@ -75293,190 +75296,190 @@
         <v>30</v>
       </c>
       <c r="G358" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H358" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="I358">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J358">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K358">
         <v>2</v>
       </c>
       <c r="L358">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M358">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N358">
+        <v>7</v>
+      </c>
+      <c r="O358" t="s">
+        <v>320</v>
+      </c>
+      <c r="P358" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q358">
+        <v>1.73</v>
+      </c>
+      <c r="R358">
+        <v>2.5</v>
+      </c>
+      <c r="S358">
+        <v>10</v>
+      </c>
+      <c r="T358">
+        <v>1.33</v>
+      </c>
+      <c r="U358">
+        <v>3.25</v>
+      </c>
+      <c r="V358">
+        <v>2.5</v>
+      </c>
+      <c r="W358">
+        <v>1.5</v>
+      </c>
+      <c r="X358">
+        <v>6.5</v>
+      </c>
+      <c r="Y358">
+        <v>1.11</v>
+      </c>
+      <c r="Z358">
+        <v>1.22</v>
+      </c>
+      <c r="AA358">
+        <v>5.9</v>
+      </c>
+      <c r="AB358">
+        <v>13</v>
+      </c>
+      <c r="AC358">
+        <v>1.04</v>
+      </c>
+      <c r="AD358">
+        <v>10</v>
+      </c>
+      <c r="AE358">
+        <v>1.22</v>
+      </c>
+      <c r="AF358">
+        <v>4.2</v>
+      </c>
+      <c r="AG358">
+        <v>1.75</v>
+      </c>
+      <c r="AH358">
+        <v>2</v>
+      </c>
+      <c r="AI358">
+        <v>2.38</v>
+      </c>
+      <c r="AJ358">
+        <v>1.53</v>
+      </c>
+      <c r="AK358">
+        <v>1.05</v>
+      </c>
+      <c r="AL358">
+        <v>1.13</v>
+      </c>
+      <c r="AM358">
+        <v>3.7</v>
+      </c>
+      <c r="AN358">
+        <v>2.53</v>
+      </c>
+      <c r="AO358">
+        <v>0.79</v>
+      </c>
+      <c r="AP358">
+        <v>2.56</v>
+      </c>
+      <c r="AQ358">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR358">
+        <v>1.89</v>
+      </c>
+      <c r="AS358">
+        <v>1.15</v>
+      </c>
+      <c r="AT358">
+        <v>3.04</v>
+      </c>
+      <c r="AU358">
+        <v>14</v>
+      </c>
+      <c r="AV358">
         <v>3</v>
       </c>
-      <c r="O358" t="s">
-        <v>289</v>
-      </c>
-      <c r="P358" t="s">
-        <v>445</v>
-      </c>
-      <c r="Q358">
-        <v>2.63</v>
-      </c>
-      <c r="R358">
-        <v>2.1</v>
-      </c>
-      <c r="S358">
-        <v>4.33</v>
-      </c>
-      <c r="T358">
-        <v>1.44</v>
-      </c>
-      <c r="U358">
-        <v>2.63</v>
-      </c>
-      <c r="V358">
+      <c r="AW358">
+        <v>17</v>
+      </c>
+      <c r="AX358">
+        <v>0</v>
+      </c>
+      <c r="AY358">
+        <v>35</v>
+      </c>
+      <c r="AZ358">
         <v>3</v>
       </c>
-      <c r="W358">
-        <v>1.36</v>
-      </c>
-      <c r="X358">
-        <v>9</v>
-      </c>
-      <c r="Y358">
-        <v>1.07</v>
-      </c>
-      <c r="Z358">
-        <v>2</v>
-      </c>
-      <c r="AA358">
-        <v>3.38</v>
-      </c>
-      <c r="AB358">
-        <v>3.66</v>
-      </c>
-      <c r="AC358">
-        <v>1.06</v>
-      </c>
-      <c r="AD358">
-        <v>8.5</v>
-      </c>
-      <c r="AE358">
-        <v>1.33</v>
-      </c>
-      <c r="AF358">
-        <v>3.2</v>
-      </c>
-      <c r="AG358">
-        <v>1.94</v>
-      </c>
-      <c r="AH358">
-        <v>1.8</v>
-      </c>
-      <c r="AI358">
-        <v>1.83</v>
-      </c>
-      <c r="AJ358">
-        <v>1.83</v>
-      </c>
-      <c r="AK358">
-        <v>1.25</v>
-      </c>
-      <c r="AL358">
-        <v>1.3</v>
-      </c>
-      <c r="AM358">
-        <v>1.8</v>
-      </c>
-      <c r="AN358">
-        <v>0.8</v>
-      </c>
-      <c r="AO358">
-        <v>0.71</v>
-      </c>
-      <c r="AP358">
-        <v>0.75</v>
-      </c>
-      <c r="AQ358">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AR358">
-        <v>1.32</v>
-      </c>
-      <c r="AS358">
-        <v>1.12</v>
-      </c>
-      <c r="AT358">
-        <v>2.44</v>
-      </c>
-      <c r="AU358">
-        <v>10</v>
-      </c>
-      <c r="AV358">
-        <v>5</v>
-      </c>
-      <c r="AW358">
-        <v>13</v>
-      </c>
-      <c r="AX358">
-        <v>7</v>
-      </c>
-      <c r="AY358">
-        <v>25</v>
-      </c>
-      <c r="AZ358">
-        <v>13</v>
-      </c>
       <c r="BA358">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BB358">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BC358">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BD358">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="BE358">
-        <v>6.75</v>
+        <v>9.5</v>
       </c>
       <c r="BF358">
-        <v>2.88</v>
+        <v>5.6</v>
       </c>
       <c r="BG358">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BH358">
-        <v>4.58</v>
+        <v>4.09</v>
       </c>
       <c r="BI358">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="BJ358">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="BK358">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="BL358">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="BM358">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="BN358">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="BO358">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="BP358">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="359" spans="1:68">
@@ -75484,7 +75487,7 @@
         <v>358</v>
       </c>
       <c r="B359">
-        <v>7479294</v>
+        <v>7479093</v>
       </c>
       <c r="C359" t="s">
         <v>68</v>
@@ -75499,190 +75502,190 @@
         <v>30</v>
       </c>
       <c r="G359" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H359" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I359">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J359">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K359">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L359">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M359">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N359">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O359" t="s">
-        <v>95</v>
+        <v>289</v>
       </c>
       <c r="P359" t="s">
-        <v>350</v>
+        <v>446</v>
       </c>
       <c r="Q359">
+        <v>2.63</v>
+      </c>
+      <c r="R359">
+        <v>2.1</v>
+      </c>
+      <c r="S359">
         <v>4.33</v>
       </c>
-      <c r="R359">
-        <v>2</v>
-      </c>
-      <c r="S359">
-        <v>2.88</v>
-      </c>
       <c r="T359">
+        <v>1.44</v>
+      </c>
+      <c r="U359">
+        <v>2.63</v>
+      </c>
+      <c r="V359">
+        <v>3</v>
+      </c>
+      <c r="W359">
+        <v>1.36</v>
+      </c>
+      <c r="X359">
+        <v>9</v>
+      </c>
+      <c r="Y359">
+        <v>1.07</v>
+      </c>
+      <c r="Z359">
+        <v>2</v>
+      </c>
+      <c r="AA359">
+        <v>3.38</v>
+      </c>
+      <c r="AB359">
+        <v>3.66</v>
+      </c>
+      <c r="AC359">
+        <v>1.06</v>
+      </c>
+      <c r="AD359">
+        <v>8.5</v>
+      </c>
+      <c r="AE359">
+        <v>1.33</v>
+      </c>
+      <c r="AF359">
+        <v>3.2</v>
+      </c>
+      <c r="AG359">
+        <v>1.94</v>
+      </c>
+      <c r="AH359">
+        <v>1.8</v>
+      </c>
+      <c r="AI359">
+        <v>1.83</v>
+      </c>
+      <c r="AJ359">
+        <v>1.83</v>
+      </c>
+      <c r="AK359">
+        <v>1.25</v>
+      </c>
+      <c r="AL359">
+        <v>1.3</v>
+      </c>
+      <c r="AM359">
+        <v>1.8</v>
+      </c>
+      <c r="AN359">
+        <v>0.8</v>
+      </c>
+      <c r="AO359">
+        <v>0.71</v>
+      </c>
+      <c r="AP359">
+        <v>0.75</v>
+      </c>
+      <c r="AQ359">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AR359">
+        <v>1.32</v>
+      </c>
+      <c r="AS359">
+        <v>1.12</v>
+      </c>
+      <c r="AT359">
+        <v>2.44</v>
+      </c>
+      <c r="AU359">
+        <v>10</v>
+      </c>
+      <c r="AV359">
+        <v>5</v>
+      </c>
+      <c r="AW359">
+        <v>13</v>
+      </c>
+      <c r="AX359">
+        <v>7</v>
+      </c>
+      <c r="AY359">
+        <v>25</v>
+      </c>
+      <c r="AZ359">
+        <v>13</v>
+      </c>
+      <c r="BA359">
+        <v>8</v>
+      </c>
+      <c r="BB359">
+        <v>4</v>
+      </c>
+      <c r="BC359">
+        <v>12</v>
+      </c>
+      <c r="BD359">
         <v>1.5</v>
-      </c>
-      <c r="U359">
-        <v>2.5</v>
-      </c>
-      <c r="V359">
-        <v>3.4</v>
-      </c>
-      <c r="W359">
-        <v>1.3</v>
-      </c>
-      <c r="X359">
-        <v>10</v>
-      </c>
-      <c r="Y359">
-        <v>1.06</v>
-      </c>
-      <c r="Z359">
-        <v>3.6</v>
-      </c>
-      <c r="AA359">
-        <v>3.1</v>
-      </c>
-      <c r="AB359">
-        <v>2.15</v>
-      </c>
-      <c r="AC359">
-        <v>1.09</v>
-      </c>
-      <c r="AD359">
-        <v>7</v>
-      </c>
-      <c r="AE359">
-        <v>1.42</v>
-      </c>
-      <c r="AF359">
-        <v>2.8</v>
-      </c>
-      <c r="AG359">
-        <v>2.3</v>
-      </c>
-      <c r="AH359">
-        <v>1.62</v>
-      </c>
-      <c r="AI359">
-        <v>1.91</v>
-      </c>
-      <c r="AJ359">
-        <v>1.8</v>
-      </c>
-      <c r="AK359">
-        <v>1.65</v>
-      </c>
-      <c r="AL359">
-        <v>1.33</v>
-      </c>
-      <c r="AM359">
-        <v>1.3</v>
-      </c>
-      <c r="AN359">
-        <v>1.43</v>
-      </c>
-      <c r="AO359">
-        <v>1.87</v>
-      </c>
-      <c r="AP359">
-        <v>1.31</v>
-      </c>
-      <c r="AQ359">
-        <v>1.94</v>
-      </c>
-      <c r="AR359">
-        <v>1.38</v>
-      </c>
-      <c r="AS359">
-        <v>1.29</v>
-      </c>
-      <c r="AT359">
-        <v>2.67</v>
-      </c>
-      <c r="AU359">
-        <v>3</v>
-      </c>
-      <c r="AV359">
-        <v>4</v>
-      </c>
-      <c r="AW359">
-        <v>9</v>
-      </c>
-      <c r="AX359">
-        <v>3</v>
-      </c>
-      <c r="AY359">
-        <v>15</v>
-      </c>
-      <c r="AZ359">
-        <v>7</v>
-      </c>
-      <c r="BA359">
-        <v>2</v>
-      </c>
-      <c r="BB359">
-        <v>2</v>
-      </c>
-      <c r="BC359">
-        <v>4</v>
-      </c>
-      <c r="BD359">
-        <v>1.98</v>
       </c>
       <c r="BE359">
         <v>6.75</v>
       </c>
       <c r="BF359">
-        <v>1.96</v>
+        <v>2.88</v>
       </c>
       <c r="BG359">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="BH359">
-        <v>5.45</v>
+        <v>4.58</v>
       </c>
       <c r="BI359">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="BJ359">
-        <v>3.52</v>
+        <v>3.06</v>
       </c>
       <c r="BK359">
+        <v>1.62</v>
+      </c>
+      <c r="BL359">
+        <v>2.28</v>
+      </c>
+      <c r="BM359">
+        <v>2</v>
+      </c>
+      <c r="BN359">
+        <v>1.8</v>
+      </c>
+      <c r="BO359">
+        <v>2.52</v>
+      </c>
+      <c r="BP359">
         <v>1.5</v>
-      </c>
-      <c r="BL359">
-        <v>2.54</v>
-      </c>
-      <c r="BM359">
-        <v>1.8</v>
-      </c>
-      <c r="BN359">
-        <v>2</v>
-      </c>
-      <c r="BO359">
-        <v>2.26</v>
-      </c>
-      <c r="BP359">
-        <v>1.63</v>
       </c>
     </row>
     <row r="360" spans="1:68">
@@ -75690,7 +75693,7 @@
         <v>359</v>
       </c>
       <c r="B360">
-        <v>7479096</v>
+        <v>7479099</v>
       </c>
       <c r="C360" t="s">
         <v>68</v>
@@ -75705,190 +75708,190 @@
         <v>30</v>
       </c>
       <c r="G360" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="H360" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="I360">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J360">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K360">
+        <v>0</v>
+      </c>
+      <c r="L360">
+        <v>0</v>
+      </c>
+      <c r="M360">
+        <v>0</v>
+      </c>
+      <c r="N360">
+        <v>0</v>
+      </c>
+      <c r="O360" t="s">
+        <v>95</v>
+      </c>
+      <c r="P360" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q360">
+        <v>5.5</v>
+      </c>
+      <c r="R360">
+        <v>2.2</v>
+      </c>
+      <c r="S360">
+        <v>2.3</v>
+      </c>
+      <c r="T360">
+        <v>1.44</v>
+      </c>
+      <c r="U360">
+        <v>2.63</v>
+      </c>
+      <c r="V360">
         <v>3</v>
       </c>
-      <c r="L360">
-        <v>2</v>
-      </c>
-      <c r="M360">
-        <v>1</v>
-      </c>
-      <c r="N360">
-        <v>3</v>
-      </c>
-      <c r="O360" t="s">
-        <v>320</v>
-      </c>
-      <c r="P360" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q360">
-        <v>3.1</v>
-      </c>
-      <c r="R360">
-        <v>1.95</v>
-      </c>
-      <c r="S360">
+      <c r="W360">
+        <v>1.36</v>
+      </c>
+      <c r="X360">
+        <v>9</v>
+      </c>
+      <c r="Y360">
+        <v>1.07</v>
+      </c>
+      <c r="Z360">
+        <v>5.5</v>
+      </c>
+      <c r="AA360">
+        <v>3.5</v>
+      </c>
+      <c r="AB360">
+        <v>1.66</v>
+      </c>
+      <c r="AC360">
+        <v>1.07</v>
+      </c>
+      <c r="AD360">
+        <v>8</v>
+      </c>
+      <c r="AE360">
+        <v>1.33</v>
+      </c>
+      <c r="AF360">
+        <v>3.25</v>
+      </c>
+      <c r="AG360">
+        <v>1.98</v>
+      </c>
+      <c r="AH360">
+        <v>1.77</v>
+      </c>
+      <c r="AI360">
+        <v>1.91</v>
+      </c>
+      <c r="AJ360">
+        <v>1.8</v>
+      </c>
+      <c r="AK360">
+        <v>2.15</v>
+      </c>
+      <c r="AL360">
+        <v>1.25</v>
+      </c>
+      <c r="AM360">
+        <v>1.14</v>
+      </c>
+      <c r="AN360">
+        <v>1.57</v>
+      </c>
+      <c r="AO360">
+        <v>2.07</v>
+      </c>
+      <c r="AP360">
+        <v>1.63</v>
+      </c>
+      <c r="AQ360">
+        <v>2</v>
+      </c>
+      <c r="AR360">
+        <v>1.49</v>
+      </c>
+      <c r="AS360">
+        <v>1.25</v>
+      </c>
+      <c r="AT360">
+        <v>2.74</v>
+      </c>
+      <c r="AU360">
         <v>4</v>
-      </c>
-      <c r="T360">
-        <v>1.53</v>
-      </c>
-      <c r="U360">
-        <v>2.38</v>
-      </c>
-      <c r="V360">
-        <v>3.75</v>
-      </c>
-      <c r="W360">
-        <v>1.25</v>
-      </c>
-      <c r="X360">
-        <v>11</v>
-      </c>
-      <c r="Y360">
-        <v>1.05</v>
-      </c>
-      <c r="Z360">
-        <v>2.3</v>
-      </c>
-      <c r="AA360">
-        <v>3</v>
-      </c>
-      <c r="AB360">
-        <v>3.3</v>
-      </c>
-      <c r="AC360">
-        <v>1.1</v>
-      </c>
-      <c r="AD360">
-        <v>6.5</v>
-      </c>
-      <c r="AE360">
-        <v>1.53</v>
-      </c>
-      <c r="AF360">
-        <v>2.38</v>
-      </c>
-      <c r="AG360">
-        <v>2.37</v>
-      </c>
-      <c r="AH360">
-        <v>1.53</v>
-      </c>
-      <c r="AI360">
-        <v>2</v>
-      </c>
-      <c r="AJ360">
-        <v>1.73</v>
-      </c>
-      <c r="AK360">
-        <v>1.33</v>
-      </c>
-      <c r="AL360">
-        <v>1.33</v>
-      </c>
-      <c r="AM360">
-        <v>1.57</v>
-      </c>
-      <c r="AN360">
-        <v>1.4</v>
-      </c>
-      <c r="AO360">
-        <v>1.29</v>
-      </c>
-      <c r="AP360">
-        <v>1.5</v>
-      </c>
-      <c r="AQ360">
-        <v>1.13</v>
-      </c>
-      <c r="AR360">
-        <v>1.33</v>
-      </c>
-      <c r="AS360">
-        <v>0.85</v>
-      </c>
-      <c r="AT360">
-        <v>2.18</v>
-      </c>
-      <c r="AU360">
-        <v>5</v>
       </c>
       <c r="AV360">
         <v>6</v>
       </c>
       <c r="AW360">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AX360">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY360">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AZ360">
         <v>15</v>
       </c>
       <c r="BA360">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB360">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BC360">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="BD360">
-        <v>1.78</v>
+        <v>2.43</v>
       </c>
       <c r="BE360">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BF360">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="BG360">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BH360">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="BI360">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="BJ360">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="BK360">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BL360">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="BM360">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="BN360">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="BO360">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="BP360">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="361" spans="1:68">
@@ -75938,7 +75941,7 @@
         <v>321</v>
       </c>
       <c r="P361" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q361">
         <v>3</v>
@@ -76428,7 +76431,7 @@
         <v>1.14</v>
       </c>
       <c r="AP363">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AQ363">
         <v>1.19</v>
@@ -76556,7 +76559,7 @@
         <v>95</v>
       </c>
       <c r="P364" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q364">
         <v>4.5</v>
@@ -76968,7 +76971,7 @@
         <v>324</v>
       </c>
       <c r="P366" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q366">
         <v>2.1</v>
@@ -77255,7 +77258,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ367">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="AR367">
         <v>1.55</v>
@@ -77380,7 +77383,7 @@
         <v>326</v>
       </c>
       <c r="P368" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q368">
         <v>2.1</v>
@@ -78410,7 +78413,7 @@
         <v>95</v>
       </c>
       <c r="P373" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q373">
         <v>5.5</v>
@@ -78616,7 +78619,7 @@
         <v>95</v>
       </c>
       <c r="P374" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q374">
         <v>2.4</v>
@@ -80058,7 +80061,7 @@
         <v>95</v>
       </c>
       <c r="P381" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q381">
         <v>2.5</v>
@@ -80215,6 +80218,212 @@
       </c>
       <c r="BP381">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="382" spans="1:68">
+      <c r="A382" s="1">
+        <v>381</v>
+      </c>
+      <c r="B382">
+        <v>7479136</v>
+      </c>
+      <c r="C382" t="s">
+        <v>68</v>
+      </c>
+      <c r="D382" t="s">
+        <v>69</v>
+      </c>
+      <c r="E382" s="2">
+        <v>45702.70833333334</v>
+      </c>
+      <c r="F382">
+        <v>33</v>
+      </c>
+      <c r="G382" t="s">
+        <v>72</v>
+      </c>
+      <c r="H382" t="s">
+        <v>84</v>
+      </c>
+      <c r="I382">
+        <v>2</v>
+      </c>
+      <c r="J382">
+        <v>0</v>
+      </c>
+      <c r="K382">
+        <v>2</v>
+      </c>
+      <c r="L382">
+        <v>4</v>
+      </c>
+      <c r="M382">
+        <v>0</v>
+      </c>
+      <c r="N382">
+        <v>4</v>
+      </c>
+      <c r="O382" t="s">
+        <v>333</v>
+      </c>
+      <c r="P382" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q382">
+        <v>3</v>
+      </c>
+      <c r="R382">
+        <v>2.05</v>
+      </c>
+      <c r="S382">
+        <v>3.75</v>
+      </c>
+      <c r="T382">
+        <v>1.44</v>
+      </c>
+      <c r="U382">
+        <v>2.63</v>
+      </c>
+      <c r="V382">
+        <v>3.25</v>
+      </c>
+      <c r="W382">
+        <v>1.33</v>
+      </c>
+      <c r="X382">
+        <v>10</v>
+      </c>
+      <c r="Y382">
+        <v>1.06</v>
+      </c>
+      <c r="Z382">
+        <v>2.24</v>
+      </c>
+      <c r="AA382">
+        <v>3.47</v>
+      </c>
+      <c r="AB382">
+        <v>2.98</v>
+      </c>
+      <c r="AC382">
+        <v>1.06</v>
+      </c>
+      <c r="AD382">
+        <v>8.5</v>
+      </c>
+      <c r="AE382">
+        <v>1.35</v>
+      </c>
+      <c r="AF382">
+        <v>3.1</v>
+      </c>
+      <c r="AG382">
+        <v>2.05</v>
+      </c>
+      <c r="AH382">
+        <v>1.7</v>
+      </c>
+      <c r="AI382">
+        <v>1.83</v>
+      </c>
+      <c r="AJ382">
+        <v>1.83</v>
+      </c>
+      <c r="AK382">
+        <v>1.37</v>
+      </c>
+      <c r="AL382">
+        <v>1.31</v>
+      </c>
+      <c r="AM382">
+        <v>1.58</v>
+      </c>
+      <c r="AN382">
+        <v>1.44</v>
+      </c>
+      <c r="AO382">
+        <v>0.5</v>
+      </c>
+      <c r="AP382">
+        <v>1.53</v>
+      </c>
+      <c r="AQ382">
+        <v>0.47</v>
+      </c>
+      <c r="AR382">
+        <v>1.63</v>
+      </c>
+      <c r="AS382">
+        <v>1.06</v>
+      </c>
+      <c r="AT382">
+        <v>2.69</v>
+      </c>
+      <c r="AU382">
+        <v>6</v>
+      </c>
+      <c r="AV382">
+        <v>2</v>
+      </c>
+      <c r="AW382">
+        <v>7</v>
+      </c>
+      <c r="AX382">
+        <v>6</v>
+      </c>
+      <c r="AY382">
+        <v>17</v>
+      </c>
+      <c r="AZ382">
+        <v>11</v>
+      </c>
+      <c r="BA382">
+        <v>2</v>
+      </c>
+      <c r="BB382">
+        <v>3</v>
+      </c>
+      <c r="BC382">
+        <v>5</v>
+      </c>
+      <c r="BD382">
+        <v>1.65</v>
+      </c>
+      <c r="BE382">
+        <v>6.2</v>
+      </c>
+      <c r="BF382">
+        <v>2.75</v>
+      </c>
+      <c r="BG382">
+        <v>1.07</v>
+      </c>
+      <c r="BH382">
+        <v>6.4</v>
+      </c>
+      <c r="BI382">
+        <v>1.2</v>
+      </c>
+      <c r="BJ382">
+        <v>4.03</v>
+      </c>
+      <c r="BK382">
+        <v>1.4</v>
+      </c>
+      <c r="BL382">
+        <v>2.82</v>
+      </c>
+      <c r="BM382">
+        <v>1.69</v>
+      </c>
+      <c r="BN382">
+        <v>2.16</v>
+      </c>
+      <c r="BO382">
+        <v>2.07</v>
+      </c>
+      <c r="BP382">
+        <v>1.76</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2420" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="457">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1746,7 +1746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP393"/>
+  <dimension ref="A1:BP395"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2286,7 +2286,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ3">
         <v>2</v>
@@ -4143,7 +4143,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ12">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4346,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ13">
         <v>1.94</v>
@@ -5997,7 +5997,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ21">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR21">
         <v>0</v>
@@ -7233,7 +7233,7 @@
         <v>0.76</v>
       </c>
       <c r="AQ27">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR27">
         <v>1.22</v>
@@ -7439,7 +7439,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ28">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR28">
         <v>1.52</v>
@@ -8466,7 +8466,7 @@
         <v>1</v>
       </c>
       <c r="AP33">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ33">
         <v>0.31</v>
@@ -9496,7 +9496,7 @@
         <v>1</v>
       </c>
       <c r="AP38">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ38">
         <v>1.13</v>
@@ -15061,7 +15061,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ65">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR65">
         <v>2.07</v>
@@ -15473,7 +15473,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ67">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR67">
         <v>1.29</v>
@@ -16088,7 +16088,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ70">
         <v>1.44</v>
@@ -16706,7 +16706,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ73">
         <v>1.19</v>
@@ -19387,7 +19387,7 @@
         <v>2</v>
       </c>
       <c r="AQ86">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR86">
         <v>1.43</v>
@@ -19593,7 +19593,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ87">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR87">
         <v>1.02</v>
@@ -20002,7 +20002,7 @@
         <v>0</v>
       </c>
       <c r="AP89">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ89">
         <v>0.5600000000000001</v>
@@ -21238,7 +21238,7 @@
         <v>1</v>
       </c>
       <c r="AP95">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ95">
         <v>0.9399999999999999</v>
@@ -23713,7 +23713,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ107">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR107">
         <v>1.37</v>
@@ -24537,7 +24537,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ111">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR111">
         <v>1.11</v>
@@ -24740,7 +24740,7 @@
         <v>0.75</v>
       </c>
       <c r="AP112">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ112">
         <v>0.9399999999999999</v>
@@ -24946,7 +24946,7 @@
         <v>0.5</v>
       </c>
       <c r="AP113">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ113">
         <v>1.18</v>
@@ -27006,7 +27006,7 @@
         <v>1.4</v>
       </c>
       <c r="AP123">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ123">
         <v>1</v>
@@ -28654,7 +28654,7 @@
         <v>1.8</v>
       </c>
       <c r="AP131">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ131">
         <v>1.53</v>
@@ -28863,7 +28863,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ132">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR132">
         <v>1.45</v>
@@ -30099,7 +30099,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ138">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR138">
         <v>1.35</v>
@@ -31744,7 +31744,7 @@
         <v>1.83</v>
       </c>
       <c r="AP146">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ146">
         <v>1.18</v>
@@ -32980,7 +32980,7 @@
         <v>1</v>
       </c>
       <c r="AP152">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ152">
         <v>1</v>
@@ -33601,7 +33601,7 @@
         <v>2.59</v>
       </c>
       <c r="AQ155">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR155">
         <v>1.82</v>
@@ -36070,7 +36070,7 @@
         <v>0.5</v>
       </c>
       <c r="AP167">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ167">
         <v>0.6899999999999999</v>
@@ -36276,7 +36276,7 @@
         <v>1.86</v>
       </c>
       <c r="AP168">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ168">
         <v>1.53</v>
@@ -37103,7 +37103,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ172">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR172">
         <v>1.36</v>
@@ -38133,7 +38133,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ177">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR177">
         <v>1.3</v>
@@ -39984,7 +39984,7 @@
         <v>1.14</v>
       </c>
       <c r="AP186">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ186">
         <v>1.13</v>
@@ -40602,7 +40602,7 @@
         <v>0.63</v>
       </c>
       <c r="AP189">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ189">
         <v>0.47</v>
@@ -42459,7 +42459,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ198">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR198">
         <v>1.39</v>
@@ -44107,7 +44107,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ206">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR206">
         <v>1.07</v>
@@ -44722,7 +44722,7 @@
         <v>1.78</v>
       </c>
       <c r="AP209">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ209">
         <v>1.18</v>
@@ -45343,7 +45343,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ212">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR212">
         <v>1.27</v>
@@ -47812,7 +47812,7 @@
         <v>1.11</v>
       </c>
       <c r="AP224">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ224">
         <v>1</v>
@@ -49048,7 +49048,7 @@
         <v>0.89</v>
       </c>
       <c r="AP230">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ230">
         <v>0.8100000000000001</v>
@@ -50902,7 +50902,7 @@
         <v>1.44</v>
       </c>
       <c r="AP239">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ239">
         <v>1.75</v>
@@ -51523,7 +51523,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ242">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR242">
         <v>1.65</v>
@@ -52141,7 +52141,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ245">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR245">
         <v>1.5</v>
@@ -53168,7 +53168,7 @@
         <v>0.64</v>
       </c>
       <c r="AP250">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ250">
         <v>0.47</v>
@@ -55846,7 +55846,7 @@
         <v>0.8</v>
       </c>
       <c r="AP263">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ263">
         <v>1.13</v>
@@ -56055,7 +56055,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ264">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR264">
         <v>1.47</v>
@@ -57497,7 +57497,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ271">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR271">
         <v>1.9</v>
@@ -58318,7 +58318,7 @@
         <v>1.55</v>
       </c>
       <c r="AP275">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ275">
         <v>1.44</v>
@@ -59351,7 +59351,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ280">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR280">
         <v>1.09</v>
@@ -59763,7 +59763,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ282">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR282">
         <v>1.92</v>
@@ -61820,7 +61820,7 @@
         <v>0.83</v>
       </c>
       <c r="AP292">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ292">
         <v>1</v>
@@ -63059,7 +63059,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ298">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR298">
         <v>1.23</v>
@@ -63677,7 +63677,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ301">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR301">
         <v>1.41</v>
@@ -63880,7 +63880,7 @@
         <v>0.45</v>
       </c>
       <c r="AP302">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ302">
         <v>0.5600000000000001</v>
@@ -68000,7 +68000,7 @@
         <v>0.67</v>
       </c>
       <c r="AP322">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ322">
         <v>0.9399999999999999</v>
@@ -71296,10 +71296,10 @@
         <v>0.83</v>
       </c>
       <c r="AP338">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ338">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR338">
         <v>1.41</v>
@@ -71917,7 +71917,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ341">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR341">
         <v>1.59</v>
@@ -73150,7 +73150,7 @@
         <v>1.38</v>
       </c>
       <c r="AP347">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="AQ347">
         <v>1.2</v>
@@ -73565,7 +73565,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ349">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR349">
         <v>1.47</v>
@@ -78921,7 +78921,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ375">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AR375">
         <v>1.33</v>
@@ -80446,7 +80446,7 @@
         <v>382</v>
       </c>
       <c r="B383">
-        <v>7479128</v>
+        <v>7479134</v>
       </c>
       <c r="C383" t="s">
         <v>68</v>
@@ -80461,10 +80461,10 @@
         <v>33</v>
       </c>
       <c r="G383" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="H383" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I383">
         <v>0</v>
@@ -80476,28 +80476,28 @@
         <v>0</v>
       </c>
       <c r="L383">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M383">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N383">
         <v>2</v>
       </c>
       <c r="O383" t="s">
-        <v>302</v>
+        <v>95</v>
       </c>
       <c r="P383" t="s">
-        <v>197</v>
+        <v>455</v>
       </c>
       <c r="Q383">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R383">
         <v>2.1</v>
       </c>
       <c r="S383">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T383">
         <v>1.4</v>
@@ -80518,13 +80518,13 @@
         <v>1.08</v>
       </c>
       <c r="Z383">
-        <v>2.58</v>
+        <v>2.49</v>
       </c>
       <c r="AA383">
-        <v>3.47</v>
+        <v>3.29</v>
       </c>
       <c r="AB383">
-        <v>2.53</v>
+        <v>2.74</v>
       </c>
       <c r="AC383">
         <v>1.05</v>
@@ -80533,16 +80533,16 @@
         <v>11</v>
       </c>
       <c r="AE383">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AF383">
         <v>3.4</v>
       </c>
       <c r="AG383">
+        <v>1.77</v>
+      </c>
+      <c r="AH383">
         <v>1.98</v>
-      </c>
-      <c r="AH383">
-        <v>1.77</v>
       </c>
       <c r="AI383">
         <v>1.73</v>
@@ -80551,52 +80551,52 @@
         <v>2</v>
       </c>
       <c r="AK383">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AL383">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AM383">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AN383">
-        <v>1.33</v>
+        <v>1.81</v>
       </c>
       <c r="AO383">
-        <v>1</v>
+        <v>0.44</v>
       </c>
       <c r="AP383">
-        <v>1.31</v>
+        <v>1.71</v>
       </c>
       <c r="AQ383">
-        <v>1</v>
+        <v>0.59</v>
       </c>
       <c r="AR383">
-        <v>1.53</v>
+        <v>1.24</v>
       </c>
       <c r="AS383">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
       <c r="AT383">
-        <v>2.78</v>
+        <v>2.29</v>
       </c>
       <c r="AU383">
+        <v>2</v>
+      </c>
+      <c r="AV383">
         <v>6</v>
-      </c>
-      <c r="AV383">
-        <v>4</v>
       </c>
       <c r="AW383">
         <v>9</v>
       </c>
       <c r="AX383">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY383">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ383">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA383">
         <v>4</v>
@@ -80608,43 +80608,43 @@
         <v>9</v>
       </c>
       <c r="BD383">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="BE383">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="BF383">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="BG383">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="BH383">
-        <v>3.18</v>
+        <v>4.99</v>
       </c>
       <c r="BI383">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="BJ383">
-        <v>2.31</v>
+        <v>3.28</v>
       </c>
       <c r="BK383">
-        <v>2</v>
+        <v>1.55</v>
       </c>
       <c r="BL383">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="BM383">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="BN383">
-        <v>1.49</v>
+        <v>1.9</v>
       </c>
       <c r="BO383">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="BP383">
-        <v>1.26</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="384" spans="1:68">
@@ -80652,7 +80652,7 @@
         <v>383</v>
       </c>
       <c r="B384">
-        <v>7479135</v>
+        <v>7479128</v>
       </c>
       <c r="C384" t="s">
         <v>68</v>
@@ -80667,10 +80667,10 @@
         <v>33</v>
       </c>
       <c r="G384" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H384" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I384">
         <v>0</v>
@@ -80682,175 +80682,175 @@
         <v>0</v>
       </c>
       <c r="L384">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M384">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N384">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O384" t="s">
-        <v>95</v>
+        <v>302</v>
       </c>
       <c r="P384" t="s">
-        <v>95</v>
+        <v>197</v>
       </c>
       <c r="Q384">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="R384">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="S384">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="T384">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="U384">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="V384">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="W384">
+        <v>1.36</v>
+      </c>
+      <c r="X384">
+        <v>8</v>
+      </c>
+      <c r="Y384">
+        <v>1.08</v>
+      </c>
+      <c r="Z384">
+        <v>2.58</v>
+      </c>
+      <c r="AA384">
+        <v>3.47</v>
+      </c>
+      <c r="AB384">
+        <v>2.53</v>
+      </c>
+      <c r="AC384">
+        <v>1.05</v>
+      </c>
+      <c r="AD384">
+        <v>11</v>
+      </c>
+      <c r="AE384">
+        <v>1.33</v>
+      </c>
+      <c r="AF384">
+        <v>3.4</v>
+      </c>
+      <c r="AG384">
+        <v>1.98</v>
+      </c>
+      <c r="AH384">
+        <v>1.77</v>
+      </c>
+      <c r="AI384">
+        <v>1.73</v>
+      </c>
+      <c r="AJ384">
+        <v>2</v>
+      </c>
+      <c r="AK384">
+        <v>1.49</v>
+      </c>
+      <c r="AL384">
+        <v>1.29</v>
+      </c>
+      <c r="AM384">
+        <v>1.47</v>
+      </c>
+      <c r="AN384">
+        <v>1.33</v>
+      </c>
+      <c r="AO384">
+        <v>1</v>
+      </c>
+      <c r="AP384">
+        <v>1.31</v>
+      </c>
+      <c r="AQ384">
+        <v>1</v>
+      </c>
+      <c r="AR384">
+        <v>1.53</v>
+      </c>
+      <c r="AS384">
         <v>1.25</v>
       </c>
-      <c r="X384">
-        <v>13</v>
-      </c>
-      <c r="Y384">
-        <v>1.04</v>
-      </c>
-      <c r="Z384">
-        <v>3.57</v>
-      </c>
-      <c r="AA384">
-        <v>3.23</v>
-      </c>
-      <c r="AB384">
-        <v>2.09</v>
-      </c>
-      <c r="AC384">
-        <v>1.1</v>
-      </c>
-      <c r="AD384">
-        <v>7.5</v>
-      </c>
-      <c r="AE384">
-        <v>1.5</v>
-      </c>
-      <c r="AF384">
-        <v>2.4</v>
-      </c>
-      <c r="AG384">
-        <v>2.86</v>
-      </c>
-      <c r="AH384">
-        <v>1.39</v>
-      </c>
-      <c r="AI384">
-        <v>2.2</v>
-      </c>
-      <c r="AJ384">
-        <v>1.62</v>
-      </c>
-      <c r="AK384">
-        <v>1.68</v>
-      </c>
-      <c r="AL384">
-        <v>1.33</v>
-      </c>
-      <c r="AM384">
-        <v>1.29</v>
-      </c>
-      <c r="AN384">
-        <v>1.67</v>
-      </c>
-      <c r="AO384">
-        <v>2</v>
-      </c>
-      <c r="AP384">
-        <v>1.63</v>
-      </c>
-      <c r="AQ384">
-        <v>1.94</v>
-      </c>
-      <c r="AR384">
+      <c r="AT384">
+        <v>2.78</v>
+      </c>
+      <c r="AU384">
+        <v>6</v>
+      </c>
+      <c r="AV384">
+        <v>4</v>
+      </c>
+      <c r="AW384">
+        <v>9</v>
+      </c>
+      <c r="AX384">
+        <v>8</v>
+      </c>
+      <c r="AY384">
+        <v>18</v>
+      </c>
+      <c r="AZ384">
+        <v>16</v>
+      </c>
+      <c r="BA384">
+        <v>4</v>
+      </c>
+      <c r="BB384">
+        <v>5</v>
+      </c>
+      <c r="BC384">
+        <v>9</v>
+      </c>
+      <c r="BD384">
+        <v>1.83</v>
+      </c>
+      <c r="BE384">
+        <v>6.4</v>
+      </c>
+      <c r="BF384">
+        <v>2.17</v>
+      </c>
+      <c r="BG384">
+        <v>1.32</v>
+      </c>
+      <c r="BH384">
+        <v>3.18</v>
+      </c>
+      <c r="BI384">
+        <v>1.6</v>
+      </c>
+      <c r="BJ384">
+        <v>2.31</v>
+      </c>
+      <c r="BK384">
+        <v>2</v>
+      </c>
+      <c r="BL384">
+        <v>1.8</v>
+      </c>
+      <c r="BM384">
+        <v>2.56</v>
+      </c>
+      <c r="BN384">
+        <v>1.49</v>
+      </c>
+      <c r="BO384">
+        <v>3.5</v>
+      </c>
+      <c r="BP384">
         <v>1.26</v>
-      </c>
-      <c r="AS384">
-        <v>1.27</v>
-      </c>
-      <c r="AT384">
-        <v>2.53</v>
-      </c>
-      <c r="AU384">
-        <v>2</v>
-      </c>
-      <c r="AV384">
-        <v>3</v>
-      </c>
-      <c r="AW384">
-        <v>4</v>
-      </c>
-      <c r="AX384">
-        <v>9</v>
-      </c>
-      <c r="AY384">
-        <v>7</v>
-      </c>
-      <c r="AZ384">
-        <v>14</v>
-      </c>
-      <c r="BA384">
-        <v>2</v>
-      </c>
-      <c r="BB384">
-        <v>6</v>
-      </c>
-      <c r="BC384">
-        <v>8</v>
-      </c>
-      <c r="BD384">
-        <v>2.1</v>
-      </c>
-      <c r="BE384">
-        <v>8</v>
-      </c>
-      <c r="BF384">
-        <v>1.91</v>
-      </c>
-      <c r="BG384">
-        <v>1.57</v>
-      </c>
-      <c r="BH384">
-        <v>2.38</v>
-      </c>
-      <c r="BI384">
-        <v>1.98</v>
-      </c>
-      <c r="BJ384">
-        <v>1.82</v>
-      </c>
-      <c r="BK384">
-        <v>2.56</v>
-      </c>
-      <c r="BL384">
-        <v>1.49</v>
-      </c>
-      <c r="BM384">
-        <v>3.56</v>
-      </c>
-      <c r="BN384">
-        <v>1.25</v>
-      </c>
-      <c r="BO384">
-        <v>5.36</v>
-      </c>
-      <c r="BP384">
-        <v>1.11</v>
       </c>
     </row>
     <row r="385" spans="1:68">
@@ -80858,7 +80858,7 @@
         <v>384</v>
       </c>
       <c r="B385">
-        <v>7479134</v>
+        <v>7479135</v>
       </c>
       <c r="C385" t="s">
         <v>68</v>
@@ -80873,10 +80873,10 @@
         <v>33</v>
       </c>
       <c r="G385" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H385" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I385">
         <v>0</v>
@@ -80891,172 +80891,172 @@
         <v>0</v>
       </c>
       <c r="M385">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N385">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O385" t="s">
         <v>95</v>
       </c>
       <c r="P385" t="s">
-        <v>455</v>
+        <v>95</v>
       </c>
       <c r="Q385">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="R385">
+        <v>1.91</v>
+      </c>
+      <c r="S385">
+        <v>2.88</v>
+      </c>
+      <c r="T385">
+        <v>1.57</v>
+      </c>
+      <c r="U385">
+        <v>2.25</v>
+      </c>
+      <c r="V385">
+        <v>3.75</v>
+      </c>
+      <c r="W385">
+        <v>1.25</v>
+      </c>
+      <c r="X385">
+        <v>13</v>
+      </c>
+      <c r="Y385">
+        <v>1.04</v>
+      </c>
+      <c r="Z385">
+        <v>3.57</v>
+      </c>
+      <c r="AA385">
+        <v>3.23</v>
+      </c>
+      <c r="AB385">
+        <v>2.09</v>
+      </c>
+      <c r="AC385">
+        <v>1.1</v>
+      </c>
+      <c r="AD385">
+        <v>7.5</v>
+      </c>
+      <c r="AE385">
+        <v>1.5</v>
+      </c>
+      <c r="AF385">
+        <v>2.4</v>
+      </c>
+      <c r="AG385">
+        <v>2.86</v>
+      </c>
+      <c r="AH385">
+        <v>1.39</v>
+      </c>
+      <c r="AI385">
+        <v>2.2</v>
+      </c>
+      <c r="AJ385">
+        <v>1.62</v>
+      </c>
+      <c r="AK385">
+        <v>1.68</v>
+      </c>
+      <c r="AL385">
+        <v>1.33</v>
+      </c>
+      <c r="AM385">
+        <v>1.29</v>
+      </c>
+      <c r="AN385">
+        <v>1.67</v>
+      </c>
+      <c r="AO385">
+        <v>2</v>
+      </c>
+      <c r="AP385">
+        <v>1.59</v>
+      </c>
+      <c r="AQ385">
+        <v>1.94</v>
+      </c>
+      <c r="AR385">
+        <v>1.26</v>
+      </c>
+      <c r="AS385">
+        <v>1.27</v>
+      </c>
+      <c r="AT385">
+        <v>2.53</v>
+      </c>
+      <c r="AU385">
+        <v>2</v>
+      </c>
+      <c r="AV385">
+        <v>3</v>
+      </c>
+      <c r="AW385">
+        <v>4</v>
+      </c>
+      <c r="AX385">
+        <v>9</v>
+      </c>
+      <c r="AY385">
+        <v>7</v>
+      </c>
+      <c r="AZ385">
+        <v>14</v>
+      </c>
+      <c r="BA385">
+        <v>2</v>
+      </c>
+      <c r="BB385">
+        <v>6</v>
+      </c>
+      <c r="BC385">
+        <v>8</v>
+      </c>
+      <c r="BD385">
         <v>2.1</v>
       </c>
-      <c r="S385">
-        <v>3.4</v>
-      </c>
-      <c r="T385">
-        <v>1.4</v>
-      </c>
-      <c r="U385">
-        <v>2.75</v>
-      </c>
-      <c r="V385">
-        <v>3</v>
-      </c>
-      <c r="W385">
-        <v>1.36</v>
-      </c>
-      <c r="X385">
+      <c r="BE385">
         <v>8</v>
       </c>
-      <c r="Y385">
-        <v>1.08</v>
-      </c>
-      <c r="Z385">
-        <v>2.49</v>
-      </c>
-      <c r="AA385">
-        <v>3.29</v>
-      </c>
-      <c r="AB385">
-        <v>2.74</v>
-      </c>
-      <c r="AC385">
-        <v>1.05</v>
-      </c>
-      <c r="AD385">
-        <v>11</v>
-      </c>
-      <c r="AE385">
-        <v>1.32</v>
-      </c>
-      <c r="AF385">
-        <v>3.4</v>
-      </c>
-      <c r="AG385">
-        <v>1.77</v>
-      </c>
-      <c r="AH385">
+      <c r="BF385">
+        <v>1.91</v>
+      </c>
+      <c r="BG385">
+        <v>1.57</v>
+      </c>
+      <c r="BH385">
+        <v>2.38</v>
+      </c>
+      <c r="BI385">
         <v>1.98</v>
       </c>
-      <c r="AI385">
-        <v>1.73</v>
-      </c>
-      <c r="AJ385">
-        <v>2</v>
-      </c>
-      <c r="AK385">
-        <v>1.47</v>
-      </c>
-      <c r="AL385">
-        <v>1.28</v>
-      </c>
-      <c r="AM385">
-        <v>1.55</v>
-      </c>
-      <c r="AN385">
-        <v>1.81</v>
-      </c>
-      <c r="AO385">
-        <v>0.44</v>
-      </c>
-      <c r="AP385">
-        <v>1.71</v>
-      </c>
-      <c r="AQ385">
-        <v>0.59</v>
-      </c>
-      <c r="AR385">
-        <v>1.24</v>
-      </c>
-      <c r="AS385">
-        <v>1.05</v>
-      </c>
-      <c r="AT385">
-        <v>2.29</v>
-      </c>
-      <c r="AU385">
-        <v>2</v>
-      </c>
-      <c r="AV385">
-        <v>6</v>
-      </c>
-      <c r="AW385">
-        <v>9</v>
-      </c>
-      <c r="AX385">
-        <v>6</v>
-      </c>
-      <c r="AY385">
-        <v>15</v>
-      </c>
-      <c r="AZ385">
-        <v>13</v>
-      </c>
-      <c r="BA385">
-        <v>4</v>
-      </c>
-      <c r="BB385">
-        <v>5</v>
-      </c>
-      <c r="BC385">
-        <v>9</v>
-      </c>
-      <c r="BD385">
-        <v>2.12</v>
-      </c>
-      <c r="BE385">
-        <v>6.5</v>
-      </c>
-      <c r="BF385">
-        <v>1.86</v>
-      </c>
-      <c r="BG385">
-        <v>1.13</v>
-      </c>
-      <c r="BH385">
-        <v>4.99</v>
-      </c>
-      <c r="BI385">
-        <v>1.3</v>
-      </c>
       <c r="BJ385">
-        <v>3.28</v>
+        <v>1.82</v>
       </c>
       <c r="BK385">
-        <v>1.55</v>
+        <v>2.56</v>
       </c>
       <c r="BL385">
-        <v>2.4</v>
+        <v>1.49</v>
       </c>
       <c r="BM385">
-        <v>1.9</v>
+        <v>3.56</v>
       </c>
       <c r="BN385">
-        <v>1.9</v>
+        <v>1.25</v>
       </c>
       <c r="BO385">
-        <v>2.38</v>
+        <v>5.36</v>
       </c>
       <c r="BP385">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="386" spans="1:68">
@@ -81064,7 +81064,7 @@
         <v>385</v>
       </c>
       <c r="B386">
-        <v>7479137</v>
+        <v>7479138</v>
       </c>
       <c r="C386" t="s">
         <v>68</v>
@@ -81079,190 +81079,190 @@
         <v>33</v>
       </c>
       <c r="G386" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H386" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I386">
         <v>0</v>
       </c>
       <c r="J386">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K386">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L386">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M386">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N386">
+        <v>4</v>
+      </c>
+      <c r="O386" t="s">
+        <v>334</v>
+      </c>
+      <c r="P386" t="s">
+        <v>444</v>
+      </c>
+      <c r="Q386">
         <v>3</v>
       </c>
-      <c r="O386" t="s">
-        <v>143</v>
-      </c>
-      <c r="P386" t="s">
-        <v>456</v>
-      </c>
-      <c r="Q386">
-        <v>3.1</v>
-      </c>
       <c r="R386">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S386">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="T386">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="U386">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V386">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="W386">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="X386">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y386">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z386">
-        <v>2.62</v>
+        <v>2.29</v>
       </c>
       <c r="AA386">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="AB386">
-        <v>2.6</v>
+        <v>2.98</v>
       </c>
       <c r="AC386">
         <v>1.06</v>
       </c>
       <c r="AD386">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AE386">
         <v>1.33</v>
       </c>
       <c r="AF386">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AG386">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="AH386">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="AI386">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AJ386">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AK386">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL386">
         <v>1.31</v>
       </c>
       <c r="AM386">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AN386">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="AO386">
         <v>1.06</v>
       </c>
       <c r="AP386">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AQ386">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="AR386">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AS386">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AT386">
-        <v>2.56</v>
+        <v>2.37</v>
       </c>
       <c r="AU386">
+        <v>6</v>
+      </c>
+      <c r="AV386">
+        <v>3</v>
+      </c>
+      <c r="AW386">
+        <v>3</v>
+      </c>
+      <c r="AX386">
+        <v>7</v>
+      </c>
+      <c r="AY386">
         <v>9</v>
       </c>
-      <c r="AV386">
-        <v>5</v>
-      </c>
-      <c r="AW386">
-        <v>15</v>
-      </c>
-      <c r="AX386">
-        <v>5</v>
-      </c>
-      <c r="AY386">
-        <v>31</v>
-      </c>
       <c r="AZ386">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA386">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="BB386">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BC386">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BD386">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="BE386">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF386">
-        <v>2.48</v>
+        <v>2.17</v>
       </c>
       <c r="BG386">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="BH386">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="BI386">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="BJ386">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
       <c r="BK386">
-        <v>1.38</v>
+        <v>1.58</v>
       </c>
       <c r="BL386">
-        <v>2.7</v>
+        <v>2.18</v>
       </c>
       <c r="BM386">
-        <v>1.61</v>
+        <v>1.95</v>
       </c>
       <c r="BN386">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="BO386">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="BP386">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="387" spans="1:68">
@@ -81270,7 +81270,7 @@
         <v>386</v>
       </c>
       <c r="B387">
-        <v>7479138</v>
+        <v>7479133</v>
       </c>
       <c r="C387" t="s">
         <v>68</v>
@@ -81285,43 +81285,43 @@
         <v>33</v>
       </c>
       <c r="G387" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H387" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I387">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J387">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K387">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L387">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M387">
         <v>1</v>
       </c>
       <c r="N387">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O387" t="s">
-        <v>334</v>
+        <v>295</v>
       </c>
       <c r="P387" t="s">
-        <v>444</v>
+        <v>119</v>
       </c>
       <c r="Q387">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R387">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S387">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T387">
         <v>1.44</v>
@@ -81330,43 +81330,43 @@
         <v>2.63</v>
       </c>
       <c r="V387">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="W387">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X387">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y387">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Z387">
-        <v>2.29</v>
+        <v>2.49</v>
       </c>
       <c r="AA387">
-        <v>3.37</v>
+        <v>3.29</v>
       </c>
       <c r="AB387">
-        <v>2.98</v>
+        <v>2.74</v>
       </c>
       <c r="AC387">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AD387">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="AE387">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="AF387">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AG387">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AH387">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="AI387">
         <v>1.83</v>
@@ -81375,64 +81375,64 @@
         <v>1.83</v>
       </c>
       <c r="AK387">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL387">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AM387">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="AN387">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AO387">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="AP387">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AQ387">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AR387">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AS387">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AT387">
-        <v>2.37</v>
+        <v>2.52</v>
       </c>
       <c r="AU387">
+        <v>8</v>
+      </c>
+      <c r="AV387">
+        <v>5</v>
+      </c>
+      <c r="AW387">
         <v>6</v>
       </c>
-      <c r="AV387">
-        <v>3</v>
-      </c>
-      <c r="AW387">
-        <v>3</v>
-      </c>
       <c r="AX387">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY387">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AZ387">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA387">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BB387">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BC387">
         <v>7</v>
       </c>
       <c r="BD387">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="BE387">
         <v>6.75</v>
@@ -81441,34 +81441,34 @@
         <v>2.17</v>
       </c>
       <c r="BG387">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="BH387">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="BI387">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="BJ387">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="BK387">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="BL387">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="BM387">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="BN387">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="BO387">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="BP387">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="388" spans="1:68">
@@ -81682,7 +81682,7 @@
         <v>388</v>
       </c>
       <c r="B389">
-        <v>7479133</v>
+        <v>7479137</v>
       </c>
       <c r="C389" t="s">
         <v>68</v>
@@ -81697,190 +81697,190 @@
         <v>33</v>
       </c>
       <c r="G389" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H389" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I389">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J389">
         <v>1</v>
       </c>
       <c r="K389">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L389">
         <v>1</v>
       </c>
       <c r="M389">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N389">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O389" t="s">
-        <v>295</v>
+        <v>143</v>
       </c>
       <c r="P389" t="s">
-        <v>119</v>
+        <v>456</v>
       </c>
       <c r="Q389">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="R389">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S389">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T389">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="U389">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="V389">
+        <v>2.75</v>
+      </c>
+      <c r="W389">
+        <v>1.4</v>
+      </c>
+      <c r="X389">
+        <v>7</v>
+      </c>
+      <c r="Y389">
+        <v>1.1</v>
+      </c>
+      <c r="Z389">
+        <v>2.62</v>
+      </c>
+      <c r="AA389">
+        <v>3.3</v>
+      </c>
+      <c r="AB389">
+        <v>2.6</v>
+      </c>
+      <c r="AC389">
+        <v>1.06</v>
+      </c>
+      <c r="AD389">
+        <v>10</v>
+      </c>
+      <c r="AE389">
+        <v>1.33</v>
+      </c>
+      <c r="AF389">
         <v>3.4</v>
       </c>
-      <c r="W389">
-        <v>1.3</v>
-      </c>
-      <c r="X389">
-        <v>10</v>
-      </c>
-      <c r="Y389">
-        <v>1.06</v>
-      </c>
-      <c r="Z389">
-        <v>2.49</v>
-      </c>
-      <c r="AA389">
-        <v>3.29</v>
-      </c>
-      <c r="AB389">
-        <v>2.74</v>
-      </c>
-      <c r="AC389">
-        <v>1.09</v>
-      </c>
-      <c r="AD389">
-        <v>8</v>
-      </c>
-      <c r="AE389">
-        <v>1.42</v>
-      </c>
-      <c r="AF389">
-        <v>2.9</v>
-      </c>
       <c r="AG389">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AH389">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AI389">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AJ389">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AK389">
         <v>1.42</v>
       </c>
       <c r="AL389">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AM389">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AN389">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AO389">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="AP389">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AQ389">
         <v>1.18</v>
       </c>
       <c r="AR389">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AS389">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AT389">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AU389">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV389">
         <v>5</v>
       </c>
       <c r="AW389">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AX389">
         <v>5</v>
       </c>
       <c r="AY389">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="AZ389">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA389">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BB389">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC389">
+        <v>11</v>
+      </c>
+      <c r="BD389">
+        <v>1.63</v>
+      </c>
+      <c r="BE389">
         <v>7</v>
       </c>
-      <c r="BD389">
-        <v>1.82</v>
-      </c>
-      <c r="BE389">
-        <v>6.75</v>
-      </c>
       <c r="BF389">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="BG389">
-        <v>1.23</v>
+        <v>1.11</v>
       </c>
       <c r="BH389">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="BI389">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="BJ389">
-        <v>2.65</v>
+        <v>3.8</v>
       </c>
       <c r="BK389">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="BL389">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="BM389">
-        <v>2.04</v>
+        <v>1.61</v>
       </c>
       <c r="BN389">
-        <v>1.68</v>
+        <v>2.15</v>
       </c>
       <c r="BO389">
-        <v>2.55</v>
+        <v>1.95</v>
       </c>
       <c r="BP389">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="390" spans="1:68">
@@ -82217,7 +82217,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ391">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="AR391">
         <v>1.29</v>
@@ -82420,7 +82420,7 @@
         <v>1.94</v>
       </c>
       <c r="AP392">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AQ392">
         <v>2</v>
@@ -82705,6 +82705,418 @@
       </c>
       <c r="BP393">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="394" spans="1:68">
+      <c r="A394" s="1">
+        <v>393</v>
+      </c>
+      <c r="B394">
+        <v>7479109</v>
+      </c>
+      <c r="C394" t="s">
+        <v>68</v>
+      </c>
+      <c r="D394" t="s">
+        <v>69</v>
+      </c>
+      <c r="E394" s="2">
+        <v>45706.69791666666</v>
+      </c>
+      <c r="F394">
+        <v>31</v>
+      </c>
+      <c r="G394" t="s">
+        <v>71</v>
+      </c>
+      <c r="H394" t="s">
+        <v>74</v>
+      </c>
+      <c r="I394">
+        <v>0</v>
+      </c>
+      <c r="J394">
+        <v>1</v>
+      </c>
+      <c r="K394">
+        <v>1</v>
+      </c>
+      <c r="L394">
+        <v>1</v>
+      </c>
+      <c r="M394">
+        <v>1</v>
+      </c>
+      <c r="N394">
+        <v>2</v>
+      </c>
+      <c r="O394" t="s">
+        <v>273</v>
+      </c>
+      <c r="P394" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q394">
+        <v>2.88</v>
+      </c>
+      <c r="R394">
+        <v>2</v>
+      </c>
+      <c r="S394">
+        <v>4</v>
+      </c>
+      <c r="T394">
+        <v>1.5</v>
+      </c>
+      <c r="U394">
+        <v>2.5</v>
+      </c>
+      <c r="V394">
+        <v>3.4</v>
+      </c>
+      <c r="W394">
+        <v>1.3</v>
+      </c>
+      <c r="X394">
+        <v>10</v>
+      </c>
+      <c r="Y394">
+        <v>1.06</v>
+      </c>
+      <c r="Z394">
+        <v>2.08</v>
+      </c>
+      <c r="AA394">
+        <v>3.27</v>
+      </c>
+      <c r="AB394">
+        <v>3.53</v>
+      </c>
+      <c r="AC394">
+        <v>1.12</v>
+      </c>
+      <c r="AD394">
+        <v>7</v>
+      </c>
+      <c r="AE394">
+        <v>1.5</v>
+      </c>
+      <c r="AF394">
+        <v>2.45</v>
+      </c>
+      <c r="AG394">
+        <v>2.35</v>
+      </c>
+      <c r="AH394">
+        <v>1.59</v>
+      </c>
+      <c r="AI394">
+        <v>1.91</v>
+      </c>
+      <c r="AJ394">
+        <v>1.8</v>
+      </c>
+      <c r="AK394">
+        <v>1.33</v>
+      </c>
+      <c r="AL394">
+        <v>1.33</v>
+      </c>
+      <c r="AM394">
+        <v>1.63</v>
+      </c>
+      <c r="AN394">
+        <v>1.63</v>
+      </c>
+      <c r="AO394">
+        <v>1.07</v>
+      </c>
+      <c r="AP394">
+        <v>1.59</v>
+      </c>
+      <c r="AQ394">
+        <v>1.06</v>
+      </c>
+      <c r="AR394">
+        <v>1.22</v>
+      </c>
+      <c r="AS394">
+        <v>1.19</v>
+      </c>
+      <c r="AT394">
+        <v>2.41</v>
+      </c>
+      <c r="AU394">
+        <v>4</v>
+      </c>
+      <c r="AV394">
+        <v>4</v>
+      </c>
+      <c r="AW394">
+        <v>12</v>
+      </c>
+      <c r="AX394">
+        <v>6</v>
+      </c>
+      <c r="AY394">
+        <v>17</v>
+      </c>
+      <c r="AZ394">
+        <v>13</v>
+      </c>
+      <c r="BA394">
+        <v>7</v>
+      </c>
+      <c r="BB394">
+        <v>4</v>
+      </c>
+      <c r="BC394">
+        <v>11</v>
+      </c>
+      <c r="BD394">
+        <v>1.61</v>
+      </c>
+      <c r="BE394">
+        <v>6.5</v>
+      </c>
+      <c r="BF394">
+        <v>2.55</v>
+      </c>
+      <c r="BG394">
+        <v>1.32</v>
+      </c>
+      <c r="BH394">
+        <v>3</v>
+      </c>
+      <c r="BI394">
+        <v>1.56</v>
+      </c>
+      <c r="BJ394">
+        <v>2.23</v>
+      </c>
+      <c r="BK394">
+        <v>1.91</v>
+      </c>
+      <c r="BL394">
+        <v>1.77</v>
+      </c>
+      <c r="BM394">
+        <v>2.43</v>
+      </c>
+      <c r="BN394">
+        <v>1.48</v>
+      </c>
+      <c r="BO394">
+        <v>3.15</v>
+      </c>
+      <c r="BP394">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="395" spans="1:68">
+      <c r="A395" s="1">
+        <v>394</v>
+      </c>
+      <c r="B395">
+        <v>7479107</v>
+      </c>
+      <c r="C395" t="s">
+        <v>68</v>
+      </c>
+      <c r="D395" t="s">
+        <v>69</v>
+      </c>
+      <c r="E395" s="2">
+        <v>45707.69791666666</v>
+      </c>
+      <c r="F395">
+        <v>31</v>
+      </c>
+      <c r="G395" t="s">
+        <v>81</v>
+      </c>
+      <c r="H395" t="s">
+        <v>92</v>
+      </c>
+      <c r="I395">
+        <v>0</v>
+      </c>
+      <c r="J395">
+        <v>0</v>
+      </c>
+      <c r="K395">
+        <v>0</v>
+      </c>
+      <c r="L395">
+        <v>1</v>
+      </c>
+      <c r="M395">
+        <v>1</v>
+      </c>
+      <c r="N395">
+        <v>2</v>
+      </c>
+      <c r="O395" t="s">
+        <v>104</v>
+      </c>
+      <c r="P395" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q395">
+        <v>2.38</v>
+      </c>
+      <c r="R395">
+        <v>2.2</v>
+      </c>
+      <c r="S395">
+        <v>5</v>
+      </c>
+      <c r="T395">
+        <v>1.4</v>
+      </c>
+      <c r="U395">
+        <v>2.75</v>
+      </c>
+      <c r="V395">
+        <v>3</v>
+      </c>
+      <c r="W395">
+        <v>1.36</v>
+      </c>
+      <c r="X395">
+        <v>8</v>
+      </c>
+      <c r="Y395">
+        <v>1.08</v>
+      </c>
+      <c r="Z395">
+        <v>1.67</v>
+      </c>
+      <c r="AA395">
+        <v>3.69</v>
+      </c>
+      <c r="AB395">
+        <v>5</v>
+      </c>
+      <c r="AC395">
+        <v>1.07</v>
+      </c>
+      <c r="AD395">
+        <v>9.5</v>
+      </c>
+      <c r="AE395">
+        <v>1.35</v>
+      </c>
+      <c r="AF395">
+        <v>3.25</v>
+      </c>
+      <c r="AG395">
+        <v>1.98</v>
+      </c>
+      <c r="AH395">
+        <v>1.77</v>
+      </c>
+      <c r="AI395">
+        <v>1.91</v>
+      </c>
+      <c r="AJ395">
+        <v>1.8</v>
+      </c>
+      <c r="AK395">
+        <v>1.2</v>
+      </c>
+      <c r="AL395">
+        <v>1.26</v>
+      </c>
+      <c r="AM395">
+        <v>2</v>
+      </c>
+      <c r="AN395">
+        <v>1.38</v>
+      </c>
+      <c r="AO395">
+        <v>0.25</v>
+      </c>
+      <c r="AP395">
+        <v>1.35</v>
+      </c>
+      <c r="AQ395">
+        <v>0.29</v>
+      </c>
+      <c r="AR395">
+        <v>1.44</v>
+      </c>
+      <c r="AS395">
+        <v>0.77</v>
+      </c>
+      <c r="AT395">
+        <v>2.21</v>
+      </c>
+      <c r="AU395">
+        <v>3</v>
+      </c>
+      <c r="AV395">
+        <v>4</v>
+      </c>
+      <c r="AW395">
+        <v>16</v>
+      </c>
+      <c r="AX395">
+        <v>1</v>
+      </c>
+      <c r="AY395">
+        <v>27</v>
+      </c>
+      <c r="AZ395">
+        <v>5</v>
+      </c>
+      <c r="BA395">
+        <v>10</v>
+      </c>
+      <c r="BB395">
+        <v>2</v>
+      </c>
+      <c r="BC395">
+        <v>12</v>
+      </c>
+      <c r="BD395">
+        <v>1.26</v>
+      </c>
+      <c r="BE395">
+        <v>8</v>
+      </c>
+      <c r="BF395">
+        <v>4.1</v>
+      </c>
+      <c r="BG395">
+        <v>1.19</v>
+      </c>
+      <c r="BH395">
+        <v>4.1</v>
+      </c>
+      <c r="BI395">
+        <v>1.33</v>
+      </c>
+      <c r="BJ395">
+        <v>2.95</v>
+      </c>
+      <c r="BK395">
+        <v>1.55</v>
+      </c>
+      <c r="BL395">
+        <v>2.28</v>
+      </c>
+      <c r="BM395">
+        <v>1.88</v>
+      </c>
+      <c r="BN395">
+        <v>1.8</v>
+      </c>
+      <c r="BO395">
+        <v>2.33</v>
+      </c>
+      <c r="BP395">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2432" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="459">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1027,6 +1027,12 @@
     <t>['78', '90+5']</t>
   </si>
   <si>
+    <t>['72', '82']</t>
+  </si>
+  <si>
+    <t>['43', '62', '70', '90+5']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -1746,7 +1752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP395"/>
+  <dimension ref="A1:BP397"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2002,7 +2008,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -2208,7 +2214,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2414,7 +2420,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2826,7 +2832,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -3238,7 +3244,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3650,7 +3656,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -4268,7 +4274,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4474,7 +4480,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -4967,7 +4973,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ16">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -5298,7 +5304,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5916,7 +5922,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -5994,7 +6000,7 @@
         <v>0</v>
       </c>
       <c r="AP21">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ21">
         <v>1.06</v>
@@ -6122,7 +6128,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6406,7 +6412,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ23">
         <v>0.6899999999999999</v>
@@ -6821,7 +6827,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ25">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR25">
         <v>0</v>
@@ -6946,7 +6952,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -7642,7 +7648,7 @@
         <v>0</v>
       </c>
       <c r="AP29">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ29">
         <v>1.18</v>
@@ -7770,7 +7776,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -8800,7 +8806,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9006,7 +9012,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9418,7 +9424,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9702,7 +9708,7 @@
         <v>1</v>
       </c>
       <c r="AP39">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ39">
         <v>1.19</v>
@@ -9830,7 +9836,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -9911,7 +9917,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ40">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR40">
         <v>1.28</v>
@@ -10036,7 +10042,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10448,7 +10454,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -10941,7 +10947,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ45">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR45">
         <v>1.47</v>
@@ -11890,7 +11896,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -13126,7 +13132,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13950,7 +13956,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -14156,7 +14162,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14362,7 +14368,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -14649,7 +14655,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ63">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR63">
         <v>1.34</v>
@@ -15186,7 +15192,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15676,7 +15682,7 @@
         <v>0</v>
       </c>
       <c r="AP68">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ68">
         <v>0.5600000000000001</v>
@@ -15804,7 +15810,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -15882,7 +15888,7 @@
         <v>1</v>
       </c>
       <c r="AP69">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ69">
         <v>0.59</v>
@@ -16091,7 +16097,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ70">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR70">
         <v>1.2</v>
@@ -16216,7 +16222,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16834,7 +16840,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -17246,7 +17252,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17452,7 +17458,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17864,7 +17870,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -18276,7 +18282,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -19384,7 +19390,7 @@
         <v>0.33</v>
       </c>
       <c r="AP86">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ86">
         <v>0.29</v>
@@ -19924,7 +19930,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -20542,7 +20548,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -20829,7 +20835,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ93">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR93">
         <v>1.4</v>
@@ -21650,10 +21656,10 @@
         <v>0</v>
       </c>
       <c r="AP97">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ97">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR97">
         <v>1.65</v>
@@ -21778,7 +21784,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -22474,7 +22480,7 @@
         <v>0.25</v>
       </c>
       <c r="AP101">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ101">
         <v>0.9399999999999999</v>
@@ -22602,7 +22608,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22683,7 +22689,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ102">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR102">
         <v>2.01</v>
@@ -22808,7 +22814,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -23507,7 +23513,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ106">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR106">
         <v>1.67</v>
@@ -24122,7 +24128,7 @@
         <v>0.25</v>
       </c>
       <c r="AP109">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ109">
         <v>0.6899999999999999</v>
@@ -25280,7 +25286,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25486,7 +25492,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25898,7 +25904,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -26928,7 +26934,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -27134,7 +27140,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -28576,7 +28582,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -29194,7 +29200,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29275,7 +29281,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ134">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR134">
         <v>1.28</v>
@@ -29478,7 +29484,7 @@
         <v>1.8</v>
       </c>
       <c r="AP135">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ135">
         <v>1.75</v>
@@ -29606,7 +29612,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -30842,7 +30848,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -31332,7 +31338,7 @@
         <v>1</v>
       </c>
       <c r="AP144">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ144">
         <v>1.13</v>
@@ -31460,7 +31466,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31541,7 +31547,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ145">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR145">
         <v>1.49</v>
@@ -31666,7 +31672,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31872,7 +31878,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -32284,7 +32290,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32490,7 +32496,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32902,7 +32908,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33314,7 +33320,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33726,7 +33732,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -34138,7 +34144,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34219,7 +34225,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ158">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR158">
         <v>1.74</v>
@@ -34756,7 +34762,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -34834,7 +34840,7 @@
         <v>1.57</v>
       </c>
       <c r="AP161">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ161">
         <v>2</v>
@@ -35580,7 +35586,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -37022,7 +37028,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37228,7 +37234,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37640,7 +37646,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -38052,7 +38058,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38545,7 +38551,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ179">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR179">
         <v>1.59</v>
@@ -38670,7 +38676,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -38954,7 +38960,7 @@
         <v>1</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ181">
         <v>1</v>
@@ -39082,7 +39088,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39366,7 +39372,7 @@
         <v>1.5</v>
       </c>
       <c r="AP183">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ183">
         <v>1.94</v>
@@ -39494,7 +39500,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -40318,7 +40324,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40399,7 +40405,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ188">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR188">
         <v>1.01</v>
@@ -40936,7 +40942,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41142,7 +41148,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41966,7 +41972,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -42047,7 +42053,7 @@
         <v>0.76</v>
       </c>
       <c r="AQ196">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR196">
         <v>1.31</v>
@@ -42250,7 +42256,7 @@
         <v>0.88</v>
       </c>
       <c r="AP197">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ197">
         <v>1.18</v>
@@ -42996,7 +43002,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -44232,7 +44238,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44850,7 +44856,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -45056,7 +45062,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45340,7 +45346,7 @@
         <v>0.22</v>
       </c>
       <c r="AP212">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ212">
         <v>0.29</v>
@@ -45468,7 +45474,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45674,7 +45680,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45880,7 +45886,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -45961,7 +45967,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ215">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR215">
         <v>1.4</v>
@@ -46164,10 +46170,10 @@
         <v>1.63</v>
       </c>
       <c r="AP216">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ216">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR216">
         <v>1.41</v>
@@ -47734,7 +47740,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47940,7 +47946,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -48764,7 +48770,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49254,7 +49260,7 @@
         <v>0.6</v>
       </c>
       <c r="AP231">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ231">
         <v>0.47</v>
@@ -49463,7 +49469,7 @@
         <v>2.59</v>
       </c>
       <c r="AQ232">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR232">
         <v>1.9</v>
@@ -49588,7 +49594,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49794,7 +49800,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -51030,7 +51036,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51314,7 +51320,7 @@
         <v>1.11</v>
       </c>
       <c r="AP241">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ241">
         <v>1.13</v>
@@ -51648,7 +51654,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51854,7 +51860,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -52266,7 +52272,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52347,7 +52353,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ246">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR246">
         <v>1.05</v>
@@ -52884,7 +52890,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53502,7 +53508,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53914,7 +53920,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54198,7 +54204,7 @@
         <v>0.8</v>
       </c>
       <c r="AP255">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ255">
         <v>0.9399999999999999</v>
@@ -54944,7 +54950,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -55025,7 +55031,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ259">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR259">
         <v>1.48</v>
@@ -55150,7 +55156,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55562,7 +55568,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -56180,7 +56186,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56386,7 +56392,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56467,7 +56473,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ266">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR266">
         <v>1.6</v>
@@ -56876,7 +56882,7 @@
         <v>0.4</v>
       </c>
       <c r="AP268">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ268">
         <v>0.31</v>
@@ -57004,7 +57010,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57622,7 +57628,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57828,7 +57834,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -58321,7 +58327,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ275">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR275">
         <v>1.19</v>
@@ -58446,7 +58452,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58652,7 +58658,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58858,7 +58864,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -59966,7 +59972,7 @@
         <v>0.64</v>
       </c>
       <c r="AP283">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ283">
         <v>0.59</v>
@@ -60712,7 +60718,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -61124,7 +61130,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61330,7 +61336,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -62154,7 +62160,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62438,7 +62444,7 @@
         <v>0.73</v>
       </c>
       <c r="AP295">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ295">
         <v>0.8100000000000001</v>
@@ -62647,7 +62653,7 @@
         <v>0.76</v>
       </c>
       <c r="AQ296">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR296">
         <v>1.35</v>
@@ -62772,7 +62778,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63596,7 +63602,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63802,7 +63808,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -64214,7 +64220,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64420,7 +64426,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64704,7 +64710,7 @@
         <v>0.54</v>
       </c>
       <c r="AP306">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ306">
         <v>0.47</v>
@@ -64832,7 +64838,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -65450,7 +65456,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -66146,7 +66152,7 @@
         <v>1.46</v>
       </c>
       <c r="AP313">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ313">
         <v>1.53</v>
@@ -67510,7 +67516,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -68209,7 +68215,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ323">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR323">
         <v>1.4</v>
@@ -68415,7 +68421,7 @@
         <v>2.59</v>
       </c>
       <c r="AQ324">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR324">
         <v>1.89</v>
@@ -68540,7 +68546,7 @@
         <v>302</v>
       </c>
       <c r="P325" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Q325">
         <v>2.5</v>
@@ -68746,7 +68752,7 @@
         <v>303</v>
       </c>
       <c r="P326" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q326">
         <v>3</v>
@@ -69158,7 +69164,7 @@
         <v>296</v>
       </c>
       <c r="P328" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69570,7 +69576,7 @@
         <v>95</v>
       </c>
       <c r="P330" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q330">
         <v>3.4</v>
@@ -69776,7 +69782,7 @@
         <v>305</v>
       </c>
       <c r="P331" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="Q331">
         <v>2.88</v>
@@ -69982,7 +69988,7 @@
         <v>306</v>
       </c>
       <c r="P332" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Q332">
         <v>2.63</v>
@@ -70394,7 +70400,7 @@
         <v>308</v>
       </c>
       <c r="P334" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="Q334">
         <v>3.1</v>
@@ -70600,7 +70606,7 @@
         <v>309</v>
       </c>
       <c r="P335" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="Q335">
         <v>3</v>
@@ -70806,7 +70812,7 @@
         <v>95</v>
       </c>
       <c r="P336" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="Q336">
         <v>5.5</v>
@@ -71012,7 +71018,7 @@
         <v>95</v>
       </c>
       <c r="P337" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="Q337">
         <v>2.2</v>
@@ -71218,7 +71224,7 @@
         <v>95</v>
       </c>
       <c r="P338" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Q338">
         <v>2.75</v>
@@ -71836,7 +71842,7 @@
         <v>311</v>
       </c>
       <c r="P341" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Q341">
         <v>1.83</v>
@@ -72042,7 +72048,7 @@
         <v>95</v>
       </c>
       <c r="P342" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="Q342">
         <v>3.2</v>
@@ -72123,7 +72129,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ342">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR342">
         <v>1.61</v>
@@ -72660,7 +72666,7 @@
         <v>314</v>
       </c>
       <c r="P345" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q345">
         <v>3</v>
@@ -72944,7 +72950,7 @@
         <v>1.23</v>
       </c>
       <c r="AP346">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ346">
         <v>1.19</v>
@@ -73153,7 +73159,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ347">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR347">
         <v>1.26</v>
@@ -73356,7 +73362,7 @@
         <v>1.62</v>
       </c>
       <c r="AP348">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ348">
         <v>1.75</v>
@@ -73896,7 +73902,7 @@
         <v>95</v>
       </c>
       <c r="P351" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q351">
         <v>3.1</v>
@@ -74308,7 +74314,7 @@
         <v>146</v>
       </c>
       <c r="P353" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q353">
         <v>5.5</v>
@@ -74514,7 +74520,7 @@
         <v>95</v>
       </c>
       <c r="P354" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q354">
         <v>4.33</v>
@@ -74720,7 +74726,7 @@
         <v>197</v>
       </c>
       <c r="P355" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q355">
         <v>2.75</v>
@@ -74926,7 +74932,7 @@
         <v>95</v>
       </c>
       <c r="P356" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="Q356">
         <v>3.2</v>
@@ -75544,7 +75550,7 @@
         <v>289</v>
       </c>
       <c r="P359" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="Q359">
         <v>2.63</v>
@@ -75956,7 +75962,7 @@
         <v>321</v>
       </c>
       <c r="P361" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="Q361">
         <v>3</v>
@@ -76240,7 +76246,7 @@
         <v>0.57</v>
       </c>
       <c r="AP362">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ362">
         <v>0.5600000000000001</v>
@@ -76574,7 +76580,7 @@
         <v>95</v>
       </c>
       <c r="P364" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="Q364">
         <v>4.5</v>
@@ -76861,7 +76867,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ365">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR365">
         <v>1.47</v>
@@ -76986,7 +76992,7 @@
         <v>324</v>
       </c>
       <c r="P366" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="Q366">
         <v>2.1</v>
@@ -77398,7 +77404,7 @@
         <v>326</v>
       </c>
       <c r="P368" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="Q368">
         <v>2.1</v>
@@ -77682,7 +77688,7 @@
         <v>0.93</v>
       </c>
       <c r="AP369">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ369">
         <v>1</v>
@@ -78428,7 +78434,7 @@
         <v>95</v>
       </c>
       <c r="P373" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Q373">
         <v>5.5</v>
@@ -78634,7 +78640,7 @@
         <v>95</v>
       </c>
       <c r="P374" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q374">
         <v>2.4</v>
@@ -79127,7 +79133,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ376">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AR376">
         <v>1.42</v>
@@ -79330,7 +79336,7 @@
         <v>0.87</v>
       </c>
       <c r="AP377">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ377">
         <v>0.8100000000000001</v>
@@ -79536,7 +79542,7 @@
         <v>1.21</v>
       </c>
       <c r="AP378">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AQ378">
         <v>1.13</v>
@@ -79951,7 +79957,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ380">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AR380">
         <v>1.49</v>
@@ -80076,7 +80082,7 @@
         <v>95</v>
       </c>
       <c r="P381" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="Q381">
         <v>2.5</v>
@@ -80488,7 +80494,7 @@
         <v>95</v>
       </c>
       <c r="P383" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="Q383">
         <v>3.2</v>
@@ -81106,7 +81112,7 @@
         <v>334</v>
       </c>
       <c r="P386" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Q386">
         <v>3</v>
@@ -81724,7 +81730,7 @@
         <v>143</v>
       </c>
       <c r="P389" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="Q389">
         <v>3.1</v>
@@ -82548,7 +82554,7 @@
         <v>336</v>
       </c>
       <c r="P393" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Q393">
         <v>2.05</v>
@@ -82960,7 +82966,7 @@
         <v>104</v>
       </c>
       <c r="P395" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Q395">
         <v>2.38</v>
@@ -83117,6 +83123,418 @@
       </c>
       <c r="BP395">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="396" spans="1:68">
+      <c r="A396" s="1">
+        <v>395</v>
+      </c>
+      <c r="B396">
+        <v>7479139</v>
+      </c>
+      <c r="C396" t="s">
+        <v>68</v>
+      </c>
+      <c r="D396" t="s">
+        <v>69</v>
+      </c>
+      <c r="E396" s="2">
+        <v>45709.69791666666</v>
+      </c>
+      <c r="F396">
+        <v>34</v>
+      </c>
+      <c r="G396" t="s">
+        <v>89</v>
+      </c>
+      <c r="H396" t="s">
+        <v>79</v>
+      </c>
+      <c r="I396">
+        <v>0</v>
+      </c>
+      <c r="J396">
+        <v>1</v>
+      </c>
+      <c r="K396">
+        <v>1</v>
+      </c>
+      <c r="L396">
+        <v>2</v>
+      </c>
+      <c r="M396">
+        <v>1</v>
+      </c>
+      <c r="N396">
+        <v>3</v>
+      </c>
+      <c r="O396" t="s">
+        <v>337</v>
+      </c>
+      <c r="P396" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q396">
+        <v>2.88</v>
+      </c>
+      <c r="R396">
+        <v>2.2</v>
+      </c>
+      <c r="S396">
+        <v>3.6</v>
+      </c>
+      <c r="T396">
+        <v>1.4</v>
+      </c>
+      <c r="U396">
+        <v>2.75</v>
+      </c>
+      <c r="V396">
+        <v>2.75</v>
+      </c>
+      <c r="W396">
+        <v>1.4</v>
+      </c>
+      <c r="X396">
+        <v>8</v>
+      </c>
+      <c r="Y396">
+        <v>1.08</v>
+      </c>
+      <c r="Z396">
+        <v>2.03</v>
+      </c>
+      <c r="AA396">
+        <v>3.53</v>
+      </c>
+      <c r="AB396">
+        <v>3.39</v>
+      </c>
+      <c r="AC396">
+        <v>1.05</v>
+      </c>
+      <c r="AD396">
+        <v>12</v>
+      </c>
+      <c r="AE396">
+        <v>1.3</v>
+      </c>
+      <c r="AF396">
+        <v>3.6</v>
+      </c>
+      <c r="AG396">
+        <v>1.83</v>
+      </c>
+      <c r="AH396">
+        <v>1.91</v>
+      </c>
+      <c r="AI396">
+        <v>1.67</v>
+      </c>
+      <c r="AJ396">
+        <v>2.1</v>
+      </c>
+      <c r="AK396">
+        <v>1.35</v>
+      </c>
+      <c r="AL396">
+        <v>1.3</v>
+      </c>
+      <c r="AM396">
+        <v>1.62</v>
+      </c>
+      <c r="AN396">
+        <v>1.81</v>
+      </c>
+      <c r="AO396">
+        <v>1.2</v>
+      </c>
+      <c r="AP396">
+        <v>1.88</v>
+      </c>
+      <c r="AQ396">
+        <v>1.13</v>
+      </c>
+      <c r="AR396">
+        <v>1.51</v>
+      </c>
+      <c r="AS396">
+        <v>1.56</v>
+      </c>
+      <c r="AT396">
+        <v>3.07</v>
+      </c>
+      <c r="AU396">
+        <v>8</v>
+      </c>
+      <c r="AV396">
+        <v>4</v>
+      </c>
+      <c r="AW396">
+        <v>12</v>
+      </c>
+      <c r="AX396">
+        <v>7</v>
+      </c>
+      <c r="AY396">
+        <v>22</v>
+      </c>
+      <c r="AZ396">
+        <v>17</v>
+      </c>
+      <c r="BA396">
+        <v>4</v>
+      </c>
+      <c r="BB396">
+        <v>1</v>
+      </c>
+      <c r="BC396">
+        <v>5</v>
+      </c>
+      <c r="BD396">
+        <v>1.58</v>
+      </c>
+      <c r="BE396">
+        <v>6.75</v>
+      </c>
+      <c r="BF396">
+        <v>2.65</v>
+      </c>
+      <c r="BG396">
+        <v>1.23</v>
+      </c>
+      <c r="BH396">
+        <v>3.65</v>
+      </c>
+      <c r="BI396">
+        <v>1.41</v>
+      </c>
+      <c r="BJ396">
+        <v>2.65</v>
+      </c>
+      <c r="BK396">
+        <v>1.66</v>
+      </c>
+      <c r="BL396">
+        <v>2.06</v>
+      </c>
+      <c r="BM396">
+        <v>2.04</v>
+      </c>
+      <c r="BN396">
+        <v>1.67</v>
+      </c>
+      <c r="BO396">
+        <v>2.55</v>
+      </c>
+      <c r="BP396">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="397" spans="1:68">
+      <c r="A397" s="1">
+        <v>396</v>
+      </c>
+      <c r="B397">
+        <v>7479140</v>
+      </c>
+      <c r="C397" t="s">
+        <v>68</v>
+      </c>
+      <c r="D397" t="s">
+        <v>69</v>
+      </c>
+      <c r="E397" s="2">
+        <v>45709.70833333334</v>
+      </c>
+      <c r="F397">
+        <v>34</v>
+      </c>
+      <c r="G397" t="s">
+        <v>91</v>
+      </c>
+      <c r="H397" t="s">
+        <v>80</v>
+      </c>
+      <c r="I397">
+        <v>1</v>
+      </c>
+      <c r="J397">
+        <v>0</v>
+      </c>
+      <c r="K397">
+        <v>1</v>
+      </c>
+      <c r="L397">
+        <v>4</v>
+      </c>
+      <c r="M397">
+        <v>0</v>
+      </c>
+      <c r="N397">
+        <v>4</v>
+      </c>
+      <c r="O397" t="s">
+        <v>338</v>
+      </c>
+      <c r="P397" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q397">
+        <v>2.5</v>
+      </c>
+      <c r="R397">
+        <v>2</v>
+      </c>
+      <c r="S397">
+        <v>5.5</v>
+      </c>
+      <c r="T397">
+        <v>1.53</v>
+      </c>
+      <c r="U397">
+        <v>2.38</v>
+      </c>
+      <c r="V397">
+        <v>3.5</v>
+      </c>
+      <c r="W397">
+        <v>1.29</v>
+      </c>
+      <c r="X397">
+        <v>11</v>
+      </c>
+      <c r="Y397">
+        <v>1.05</v>
+      </c>
+      <c r="Z397">
+        <v>1.44</v>
+      </c>
+      <c r="AA397">
+        <v>3.98</v>
+      </c>
+      <c r="AB397">
+        <v>8</v>
+      </c>
+      <c r="AC397">
+        <v>1.1</v>
+      </c>
+      <c r="AD397">
+        <v>7.5</v>
+      </c>
+      <c r="AE397">
+        <v>1.48</v>
+      </c>
+      <c r="AF397">
+        <v>2.7</v>
+      </c>
+      <c r="AG397">
+        <v>2.13</v>
+      </c>
+      <c r="AH397">
+        <v>1.65</v>
+      </c>
+      <c r="AI397">
+        <v>2.25</v>
+      </c>
+      <c r="AJ397">
+        <v>1.57</v>
+      </c>
+      <c r="AK397">
+        <v>1.17</v>
+      </c>
+      <c r="AL397">
+        <v>1.3</v>
+      </c>
+      <c r="AM397">
+        <v>2</v>
+      </c>
+      <c r="AN397">
+        <v>2</v>
+      </c>
+      <c r="AO397">
+        <v>1.44</v>
+      </c>
+      <c r="AP397">
+        <v>2.06</v>
+      </c>
+      <c r="AQ397">
+        <v>1.35</v>
+      </c>
+      <c r="AR397">
+        <v>1.46</v>
+      </c>
+      <c r="AS397">
+        <v>1.25</v>
+      </c>
+      <c r="AT397">
+        <v>2.71</v>
+      </c>
+      <c r="AU397">
+        <v>5</v>
+      </c>
+      <c r="AV397">
+        <v>3</v>
+      </c>
+      <c r="AW397">
+        <v>3</v>
+      </c>
+      <c r="AX397">
+        <v>9</v>
+      </c>
+      <c r="AY397">
+        <v>9</v>
+      </c>
+      <c r="AZ397">
+        <v>14</v>
+      </c>
+      <c r="BA397">
+        <v>3</v>
+      </c>
+      <c r="BB397">
+        <v>9</v>
+      </c>
+      <c r="BC397">
+        <v>12</v>
+      </c>
+      <c r="BD397">
+        <v>1.45</v>
+      </c>
+      <c r="BE397">
+        <v>7</v>
+      </c>
+      <c r="BF397">
+        <v>3.05</v>
+      </c>
+      <c r="BG397">
+        <v>1.24</v>
+      </c>
+      <c r="BH397">
+        <v>3.55</v>
+      </c>
+      <c r="BI397">
+        <v>1.41</v>
+      </c>
+      <c r="BJ397">
+        <v>2.65</v>
+      </c>
+      <c r="BK397">
+        <v>1.68</v>
+      </c>
+      <c r="BL397">
+        <v>2.04</v>
+      </c>
+      <c r="BM397">
+        <v>2.04</v>
+      </c>
+      <c r="BN397">
+        <v>1.67</v>
+      </c>
+      <c r="BO397">
+        <v>2.55</v>
+      </c>
+      <c r="BP397">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2492" uniqueCount="466">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2498" uniqueCount="467">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1048,6 +1048,9 @@
     <t>['32', '48', '71', '78']</t>
   </si>
   <si>
+    <t>['11', '23']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -1773,7 +1776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP405"/>
+  <dimension ref="A1:BP406"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2029,7 +2032,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -2235,7 +2238,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2441,7 +2444,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2853,7 +2856,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -3265,7 +3268,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3677,7 +3680,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -4295,7 +4298,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4501,7 +4504,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -5200,7 +5203,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ17">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5325,7 +5328,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5609,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="AP19">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ19">
         <v>0.76</v>
@@ -5943,7 +5946,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -6149,7 +6152,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -6973,7 +6976,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -7797,7 +7800,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -8081,7 +8084,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ31">
         <v>0.47</v>
@@ -8496,7 +8499,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ33">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR33">
         <v>0</v>
@@ -8827,7 +8830,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9033,7 +9036,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9445,7 +9448,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9857,7 +9860,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -10063,7 +10066,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10475,7 +10478,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -11917,7 +11920,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -12410,7 +12413,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ52">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR52">
         <v>1.45</v>
@@ -13025,7 +13028,7 @@
         <v>0.5</v>
       </c>
       <c r="AP55">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ55">
         <v>1.18</v>
@@ -13153,7 +13156,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -13977,7 +13980,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -14183,7 +14186,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14389,7 +14392,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -15213,7 +15216,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15831,7 +15834,7 @@
         <v>145</v>
       </c>
       <c r="P69" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q69">
         <v>2.05</v>
@@ -16243,7 +16246,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16861,7 +16864,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -16942,7 +16945,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ74">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR74">
         <v>1.58</v>
@@ -17273,7 +17276,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17479,7 +17482,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17891,7 +17894,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -17969,7 +17972,7 @@
         <v>2</v>
       </c>
       <c r="AP79">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ79">
         <v>1.53</v>
@@ -18303,7 +18306,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -19951,7 +19954,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -20569,7 +20572,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -21805,7 +21808,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -22629,7 +22632,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22835,7 +22838,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -23122,7 +23125,7 @@
         <v>2.38</v>
       </c>
       <c r="AQ104">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR104">
         <v>1.55</v>
@@ -23531,7 +23534,7 @@
         <v>1.5</v>
       </c>
       <c r="AP106">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ106">
         <v>1.13</v>
@@ -25307,7 +25310,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25513,7 +25516,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25925,7 +25928,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -26955,7 +26958,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -27161,7 +27164,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -28603,7 +28606,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -29221,7 +29224,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29633,7 +29636,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -29714,7 +29717,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ136">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR136">
         <v>1.84</v>
@@ -29917,7 +29920,7 @@
         <v>0.6</v>
       </c>
       <c r="AP137">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ137">
         <v>1.12</v>
@@ -30869,7 +30872,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -31487,7 +31490,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31693,7 +31696,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31899,7 +31902,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -32311,7 +32314,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32517,7 +32520,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32929,7 +32932,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33341,7 +33344,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33753,7 +33756,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -34165,7 +34168,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34783,7 +34786,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -35607,7 +35610,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -36715,7 +36718,7 @@
         <v>0.33</v>
       </c>
       <c r="AP170">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ170">
         <v>0.53</v>
@@ -36924,7 +36927,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ171">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR171">
         <v>1.68</v>
@@ -37049,7 +37052,7 @@
         <v>197</v>
       </c>
       <c r="P172" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q172">
         <v>3.25</v>
@@ -37255,7 +37258,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37667,7 +37670,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -38079,7 +38082,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38697,7 +38700,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -39109,7 +39112,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39521,7 +39524,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -40345,7 +40348,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -40963,7 +40966,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41169,7 +41172,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41453,7 +41456,7 @@
         <v>1.5</v>
       </c>
       <c r="AP193">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ193">
         <v>1</v>
@@ -41993,7 +41996,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -42898,7 +42901,7 @@
         <v>2.59</v>
       </c>
       <c r="AQ200">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR200">
         <v>1.86</v>
@@ -43023,7 +43026,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -43925,7 +43928,7 @@
         <v>1.13</v>
       </c>
       <c r="AP205">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ205">
         <v>1.06</v>
@@ -44259,7 +44262,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44877,7 +44880,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -44958,7 +44961,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ210">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR210">
         <v>1.48</v>
@@ -45083,7 +45086,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45495,7 +45498,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45701,7 +45704,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45907,7 +45910,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -47761,7 +47764,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -47967,7 +47970,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -48791,7 +48794,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49615,7 +49618,7 @@
         <v>95</v>
       </c>
       <c r="P233" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q233">
         <v>3.5</v>
@@ -49821,7 +49824,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -51057,7 +51060,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51675,7 +51678,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51881,7 +51884,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -52293,7 +52296,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52580,7 +52583,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ247">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR247">
         <v>1.31</v>
@@ -52783,7 +52786,7 @@
         <v>1.7</v>
       </c>
       <c r="AP248">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ248">
         <v>1.18</v>
@@ -52911,7 +52914,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53529,7 +53532,7 @@
         <v>260</v>
       </c>
       <c r="P252" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q252">
         <v>3.2</v>
@@ -53941,7 +53944,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -54971,7 +54974,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -55177,7 +55180,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55589,7 +55592,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -56207,7 +56210,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56413,7 +56416,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -56906,7 +56909,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ268">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR268">
         <v>1.48</v>
@@ -57031,7 +57034,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57315,7 +57318,7 @@
         <v>0.7</v>
       </c>
       <c r="AP270">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ270">
         <v>0.59</v>
@@ -57649,7 +57652,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57855,7 +57858,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -58473,7 +58476,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58679,7 +58682,7 @@
         <v>280</v>
       </c>
       <c r="P277" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q277">
         <v>3.2</v>
@@ -58760,7 +58763,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ277">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR277">
         <v>1.4</v>
@@ -58885,7 +58888,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -58963,7 +58966,7 @@
         <v>0.55</v>
       </c>
       <c r="AP278">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ278">
         <v>0.71</v>
@@ -60739,7 +60742,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -61151,7 +61154,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61357,7 +61360,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -62181,7 +62184,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62799,7 +62802,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63623,7 +63626,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63829,7 +63832,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -64241,7 +64244,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64319,7 +64322,7 @@
         <v>1.69</v>
       </c>
       <c r="AP304">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ304">
         <v>2</v>
@@ -64447,7 +64450,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64859,7 +64862,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -65352,7 +65355,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ309">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR309">
         <v>1.61</v>
@@ -65477,7 +65480,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -67537,7 +67540,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -68567,7 +68570,7 @@
         <v>302</v>
       </c>
       <c r="P325" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q325">
         <v>2.5</v>
@@ -68645,7 +68648,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AP325">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ325">
         <v>0.88</v>
@@ -68773,7 +68776,7 @@
         <v>303</v>
       </c>
       <c r="P326" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q326">
         <v>3</v>
@@ -68854,7 +68857,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ326">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR326">
         <v>1.16</v>
@@ -69185,7 +69188,7 @@
         <v>296</v>
       </c>
       <c r="P328" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69597,7 +69600,7 @@
         <v>95</v>
       </c>
       <c r="P330" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q330">
         <v>3.4</v>
@@ -69803,7 +69806,7 @@
         <v>305</v>
       </c>
       <c r="P331" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q331">
         <v>2.88</v>
@@ -70009,7 +70012,7 @@
         <v>306</v>
       </c>
       <c r="P332" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q332">
         <v>2.63</v>
@@ -70421,7 +70424,7 @@
         <v>308</v>
       </c>
       <c r="P334" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q334">
         <v>3.1</v>
@@ -70627,7 +70630,7 @@
         <v>309</v>
       </c>
       <c r="P335" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q335">
         <v>3</v>
@@ -70833,7 +70836,7 @@
         <v>95</v>
       </c>
       <c r="P336" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q336">
         <v>5.5</v>
@@ -71039,7 +71042,7 @@
         <v>95</v>
       </c>
       <c r="P337" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q337">
         <v>2.2</v>
@@ -71245,7 +71248,7 @@
         <v>95</v>
       </c>
       <c r="P338" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q338">
         <v>2.75</v>
@@ -71863,7 +71866,7 @@
         <v>311</v>
       </c>
       <c r="P341" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q341">
         <v>1.83</v>
@@ -72069,7 +72072,7 @@
         <v>95</v>
       </c>
       <c r="P342" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q342">
         <v>3.2</v>
@@ -72687,7 +72690,7 @@
         <v>314</v>
       </c>
       <c r="P345" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q345">
         <v>3</v>
@@ -73923,7 +73926,7 @@
         <v>95</v>
       </c>
       <c r="P351" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q351">
         <v>3.1</v>
@@ -74001,7 +74004,7 @@
         <v>0.87</v>
       </c>
       <c r="AP351">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ351">
         <v>1</v>
@@ -74335,7 +74338,7 @@
         <v>146</v>
       </c>
       <c r="P353" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q353">
         <v>5.5</v>
@@ -74541,7 +74544,7 @@
         <v>95</v>
       </c>
       <c r="P354" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q354">
         <v>4.33</v>
@@ -74747,7 +74750,7 @@
         <v>197</v>
       </c>
       <c r="P355" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q355">
         <v>2.75</v>
@@ -74828,7 +74831,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ355">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR355">
         <v>1.41</v>
@@ -74953,7 +74956,7 @@
         <v>95</v>
       </c>
       <c r="P356" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q356">
         <v>3.2</v>
@@ -75571,7 +75574,7 @@
         <v>289</v>
       </c>
       <c r="P359" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q359">
         <v>2.63</v>
@@ -75983,7 +75986,7 @@
         <v>321</v>
       </c>
       <c r="P361" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q361">
         <v>3</v>
@@ -76601,7 +76604,7 @@
         <v>95</v>
       </c>
       <c r="P364" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q364">
         <v>4.5</v>
@@ -77013,7 +77016,7 @@
         <v>324</v>
       </c>
       <c r="P366" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q366">
         <v>2.1</v>
@@ -77425,7 +77428,7 @@
         <v>326</v>
       </c>
       <c r="P368" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q368">
         <v>2.1</v>
@@ -78455,7 +78458,7 @@
         <v>95</v>
       </c>
       <c r="P373" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q373">
         <v>5.5</v>
@@ -78533,7 +78536,7 @@
         <v>1.67</v>
       </c>
       <c r="AP373">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="AQ373">
         <v>1.75</v>
@@ -78661,7 +78664,7 @@
         <v>95</v>
       </c>
       <c r="P374" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q374">
         <v>2.4</v>
@@ -79772,7 +79775,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ379">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AR379">
         <v>1.61</v>
@@ -80103,7 +80106,7 @@
         <v>95</v>
       </c>
       <c r="P381" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Q381">
         <v>2.5</v>
@@ -80515,7 +80518,7 @@
         <v>95</v>
       </c>
       <c r="P383" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Q383">
         <v>3.2</v>
@@ -81133,7 +81136,7 @@
         <v>334</v>
       </c>
       <c r="P386" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q386">
         <v>3</v>
@@ -81751,7 +81754,7 @@
         <v>143</v>
       </c>
       <c r="P389" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Q389">
         <v>3.1</v>
@@ -82575,7 +82578,7 @@
         <v>336</v>
       </c>
       <c r="P393" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q393">
         <v>2.05</v>
@@ -82987,7 +82990,7 @@
         <v>104</v>
       </c>
       <c r="P395" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q395">
         <v>2.38</v>
@@ -84017,7 +84020,7 @@
         <v>95</v>
       </c>
       <c r="P400" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q400">
         <v>3.5</v>
@@ -84429,7 +84432,7 @@
         <v>340</v>
       </c>
       <c r="P402" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q402">
         <v>3.1</v>
@@ -84746,13 +84749,13 @@
         <v>8</v>
       </c>
       <c r="BA403">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB403">
         <v>2</v>
       </c>
       <c r="BC403">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD403">
         <v>1.25</v>
@@ -85047,7 +85050,7 @@
         <v>343</v>
       </c>
       <c r="P405" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Q405">
         <v>2.2</v>
@@ -85204,6 +85207,212 @@
       </c>
       <c r="BP405">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="406" spans="1:68">
+      <c r="A406" s="1">
+        <v>405</v>
+      </c>
+      <c r="B406">
+        <v>7479149</v>
+      </c>
+      <c r="C406" t="s">
+        <v>68</v>
+      </c>
+      <c r="D406" t="s">
+        <v>69</v>
+      </c>
+      <c r="E406" s="2">
+        <v>45711.375</v>
+      </c>
+      <c r="F406">
+        <v>34</v>
+      </c>
+      <c r="G406" t="s">
+        <v>87</v>
+      </c>
+      <c r="H406" t="s">
+        <v>81</v>
+      </c>
+      <c r="I406">
+        <v>2</v>
+      </c>
+      <c r="J406">
+        <v>0</v>
+      </c>
+      <c r="K406">
+        <v>2</v>
+      </c>
+      <c r="L406">
+        <v>2</v>
+      </c>
+      <c r="M406">
+        <v>0</v>
+      </c>
+      <c r="N406">
+        <v>2</v>
+      </c>
+      <c r="O406" t="s">
+        <v>344</v>
+      </c>
+      <c r="P406" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q406">
+        <v>3</v>
+      </c>
+      <c r="R406">
+        <v>2.1</v>
+      </c>
+      <c r="S406">
+        <v>3.6</v>
+      </c>
+      <c r="T406">
+        <v>1.44</v>
+      </c>
+      <c r="U406">
+        <v>2.63</v>
+      </c>
+      <c r="V406">
+        <v>3</v>
+      </c>
+      <c r="W406">
+        <v>1.36</v>
+      </c>
+      <c r="X406">
+        <v>9</v>
+      </c>
+      <c r="Y406">
+        <v>1.07</v>
+      </c>
+      <c r="Z406">
+        <v>2.31</v>
+      </c>
+      <c r="AA406">
+        <v>3.53</v>
+      </c>
+      <c r="AB406">
+        <v>2.82</v>
+      </c>
+      <c r="AC406">
+        <v>1.05</v>
+      </c>
+      <c r="AD406">
+        <v>11</v>
+      </c>
+      <c r="AE406">
+        <v>1.33</v>
+      </c>
+      <c r="AF406">
+        <v>3.3</v>
+      </c>
+      <c r="AG406">
+        <v>1.98</v>
+      </c>
+      <c r="AH406">
+        <v>1.77</v>
+      </c>
+      <c r="AI406">
+        <v>1.8</v>
+      </c>
+      <c r="AJ406">
+        <v>1.91</v>
+      </c>
+      <c r="AK406">
+        <v>1.4</v>
+      </c>
+      <c r="AL406">
+        <v>1.3</v>
+      </c>
+      <c r="AM406">
+        <v>1.57</v>
+      </c>
+      <c r="AN406">
+        <v>1.81</v>
+      </c>
+      <c r="AO406">
+        <v>0.31</v>
+      </c>
+      <c r="AP406">
+        <v>1.88</v>
+      </c>
+      <c r="AQ406">
+        <v>0.29</v>
+      </c>
+      <c r="AR406">
+        <v>1.39</v>
+      </c>
+      <c r="AS406">
+        <v>1.09</v>
+      </c>
+      <c r="AT406">
+        <v>2.48</v>
+      </c>
+      <c r="AU406">
+        <v>6</v>
+      </c>
+      <c r="AV406">
+        <v>3</v>
+      </c>
+      <c r="AW406">
+        <v>6</v>
+      </c>
+      <c r="AX406">
+        <v>8</v>
+      </c>
+      <c r="AY406">
+        <v>13</v>
+      </c>
+      <c r="AZ406">
+        <v>13</v>
+      </c>
+      <c r="BA406">
+        <v>4</v>
+      </c>
+      <c r="BB406">
+        <v>6</v>
+      </c>
+      <c r="BC406">
+        <v>10</v>
+      </c>
+      <c r="BD406">
+        <v>1.77</v>
+      </c>
+      <c r="BE406">
+        <v>6.75</v>
+      </c>
+      <c r="BF406">
+        <v>2.23</v>
+      </c>
+      <c r="BG406">
+        <v>1.2</v>
+      </c>
+      <c r="BH406">
+        <v>3.9</v>
+      </c>
+      <c r="BI406">
+        <v>1.36</v>
+      </c>
+      <c r="BJ406">
+        <v>2.8</v>
+      </c>
+      <c r="BK406">
+        <v>1.6</v>
+      </c>
+      <c r="BL406">
+        <v>2.17</v>
+      </c>
+      <c r="BM406">
+        <v>1.95</v>
+      </c>
+      <c r="BN406">
+        <v>1.74</v>
+      </c>
+      <c r="BO406">
+        <v>2.43</v>
+      </c>
+      <c r="BP406">
+        <v>1.48</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2498" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="468">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1416,6 +1416,9 @@
   <si>
     <t>['45+2', '90+7']</t>
   </si>
+  <si>
+    <t>['72', '89', '90']</t>
+  </si>
 </sst>
 </file>
 
@@ -1776,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP406"/>
+  <dimension ref="A1:BP407"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4791,7 +4794,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ15">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5406,7 +5409,7 @@
         <v>0</v>
       </c>
       <c r="AP18">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ18">
         <v>1.06</v>
@@ -7057,7 +7060,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ26">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR26">
         <v>2.62</v>
@@ -11792,7 +11795,7 @@
         <v>3</v>
       </c>
       <c r="AP49">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ49">
         <v>0.9399999999999999</v>
@@ -15297,7 +15300,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ66">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR66">
         <v>1.23</v>
@@ -16530,7 +16533,7 @@
         <v>0</v>
       </c>
       <c r="AP72">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ72">
         <v>0.47</v>
@@ -20447,7 +20450,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ91">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -21062,7 +21065,7 @@
         <v>1</v>
       </c>
       <c r="AP94">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ94">
         <v>1</v>
@@ -21889,7 +21892,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ98">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR98">
         <v>1.22</v>
@@ -23122,7 +23125,7 @@
         <v>1</v>
       </c>
       <c r="AP104">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ104">
         <v>0.29</v>
@@ -29511,7 +29514,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ135">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR135">
         <v>1.5</v>
@@ -30744,7 +30747,7 @@
         <v>0.8</v>
       </c>
       <c r="AP141">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ141">
         <v>0.76</v>
@@ -35485,7 +35488,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ164">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR164">
         <v>1.43</v>
@@ -38572,7 +38575,7 @@
         <v>1.17</v>
       </c>
       <c r="AP179">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ179">
         <v>1.35</v>
@@ -41253,7 +41256,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ192">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR192">
         <v>1.35</v>
@@ -41868,7 +41871,7 @@
         <v>0.29</v>
       </c>
       <c r="AP195">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ195">
         <v>0.53</v>
@@ -43722,7 +43725,7 @@
         <v>1.67</v>
       </c>
       <c r="AP204">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ204">
         <v>1.53</v>
@@ -44549,7 +44552,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ208">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR208">
         <v>1.36</v>
@@ -50935,7 +50938,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ239">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR239">
         <v>1.26</v>
@@ -52168,7 +52171,7 @@
         <v>0.2</v>
       </c>
       <c r="AP245">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ245">
         <v>0.29</v>
@@ -56288,7 +56291,7 @@
         <v>1.91</v>
       </c>
       <c r="AP265">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ265">
         <v>1.94</v>
@@ -57939,7 +57942,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ273">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR273">
         <v>1.28</v>
@@ -58142,7 +58145,7 @@
         <v>1.42</v>
       </c>
       <c r="AP274">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ274">
         <v>1.18</v>
@@ -60205,7 +60208,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ284">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR284">
         <v>1.42</v>
@@ -64531,7 +64534,7 @@
         <v>0.76</v>
       </c>
       <c r="AQ305">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR305">
         <v>1.29</v>
@@ -67412,7 +67415,7 @@
         <v>1</v>
       </c>
       <c r="AP319">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ319">
         <v>1</v>
@@ -71120,7 +71123,7 @@
         <v>1.08</v>
       </c>
       <c r="AP337">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ337">
         <v>1.25</v>
@@ -73389,7 +73392,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ348">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR348">
         <v>1.45</v>
@@ -76685,7 +76688,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ364">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR364">
         <v>1.82</v>
@@ -77506,7 +77509,7 @@
         <v>0.47</v>
       </c>
       <c r="AP368">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ368">
         <v>0.59</v>
@@ -78539,7 +78542,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ373">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AR373">
         <v>1.42</v>
@@ -79978,7 +79981,7 @@
         <v>1.29</v>
       </c>
       <c r="AP380">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AQ380">
         <v>1.13</v>
@@ -85413,6 +85416,212 @@
       </c>
       <c r="BP406">
         <v>1.48</v>
+      </c>
+    </row>
+    <row r="407" spans="1:68">
+      <c r="A407" s="1">
+        <v>406</v>
+      </c>
+      <c r="B407">
+        <v>7479146</v>
+      </c>
+      <c r="C407" t="s">
+        <v>68</v>
+      </c>
+      <c r="D407" t="s">
+        <v>69</v>
+      </c>
+      <c r="E407" s="2">
+        <v>45712.70833333334</v>
+      </c>
+      <c r="F407">
+        <v>34</v>
+      </c>
+      <c r="G407" t="s">
+        <v>86</v>
+      </c>
+      <c r="H407" t="s">
+        <v>76</v>
+      </c>
+      <c r="I407">
+        <v>1</v>
+      </c>
+      <c r="J407">
+        <v>0</v>
+      </c>
+      <c r="K407">
+        <v>1</v>
+      </c>
+      <c r="L407">
+        <v>1</v>
+      </c>
+      <c r="M407">
+        <v>3</v>
+      </c>
+      <c r="N407">
+        <v>4</v>
+      </c>
+      <c r="O407" t="s">
+        <v>106</v>
+      </c>
+      <c r="P407" t="s">
+        <v>467</v>
+      </c>
+      <c r="Q407">
+        <v>4.75</v>
+      </c>
+      <c r="R407">
+        <v>2.1</v>
+      </c>
+      <c r="S407">
+        <v>2.5</v>
+      </c>
+      <c r="T407">
+        <v>1.4</v>
+      </c>
+      <c r="U407">
+        <v>2.75</v>
+      </c>
+      <c r="V407">
+        <v>3</v>
+      </c>
+      <c r="W407">
+        <v>1.36</v>
+      </c>
+      <c r="X407">
+        <v>8</v>
+      </c>
+      <c r="Y407">
+        <v>1.08</v>
+      </c>
+      <c r="Z407">
+        <v>3.9</v>
+      </c>
+      <c r="AA407">
+        <v>3.7</v>
+      </c>
+      <c r="AB407">
+        <v>1.85</v>
+      </c>
+      <c r="AC407">
+        <v>1.06</v>
+      </c>
+      <c r="AD407">
+        <v>10</v>
+      </c>
+      <c r="AE407">
+        <v>1.35</v>
+      </c>
+      <c r="AF407">
+        <v>3.25</v>
+      </c>
+      <c r="AG407">
+        <v>2</v>
+      </c>
+      <c r="AH407">
+        <v>1.8</v>
+      </c>
+      <c r="AI407">
+        <v>1.83</v>
+      </c>
+      <c r="AJ407">
+        <v>1.83</v>
+      </c>
+      <c r="AK407">
+        <v>1.87</v>
+      </c>
+      <c r="AL407">
+        <v>1.29</v>
+      </c>
+      <c r="AM407">
+        <v>1.23</v>
+      </c>
+      <c r="AN407">
+        <v>2.38</v>
+      </c>
+      <c r="AO407">
+        <v>1.75</v>
+      </c>
+      <c r="AP407">
+        <v>2.24</v>
+      </c>
+      <c r="AQ407">
+        <v>1.82</v>
+      </c>
+      <c r="AR407">
+        <v>1.54</v>
+      </c>
+      <c r="AS407">
+        <v>1.6</v>
+      </c>
+      <c r="AT407">
+        <v>3.14</v>
+      </c>
+      <c r="AU407">
+        <v>5</v>
+      </c>
+      <c r="AV407">
+        <v>9</v>
+      </c>
+      <c r="AW407">
+        <v>6</v>
+      </c>
+      <c r="AX407">
+        <v>10</v>
+      </c>
+      <c r="AY407">
+        <v>15</v>
+      </c>
+      <c r="AZ407">
+        <v>24</v>
+      </c>
+      <c r="BA407">
+        <v>3</v>
+      </c>
+      <c r="BB407">
+        <v>5</v>
+      </c>
+      <c r="BC407">
+        <v>8</v>
+      </c>
+      <c r="BD407">
+        <v>2.48</v>
+      </c>
+      <c r="BE407">
+        <v>6.75</v>
+      </c>
+      <c r="BF407">
+        <v>1.66</v>
+      </c>
+      <c r="BG407">
+        <v>1.22</v>
+      </c>
+      <c r="BH407">
+        <v>3.7</v>
+      </c>
+      <c r="BI407">
+        <v>1.38</v>
+      </c>
+      <c r="BJ407">
+        <v>2.7</v>
+      </c>
+      <c r="BK407">
+        <v>1.63</v>
+      </c>
+      <c r="BL407">
+        <v>2.1</v>
+      </c>
+      <c r="BM407">
+        <v>1.98</v>
+      </c>
+      <c r="BN407">
+        <v>1.72</v>
+      </c>
+      <c r="BO407">
+        <v>2.5</v>
+      </c>
+      <c r="BP407">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2516" uniqueCount="469">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1419,6 +1419,9 @@
   <si>
     <t>['72', '89', '90']</t>
   </si>
+  <si>
+    <t>['20', '52', '73']</t>
+  </si>
 </sst>
 </file>
 
@@ -1779,7 +1782,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP407"/>
+  <dimension ref="A1:BP409"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3143,7 +3146,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ7">
         <v>1.18</v>
@@ -3761,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ10">
         <v>1.53</v>
@@ -5000,7 +5003,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ16">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -6648,7 +6651,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ24">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR24">
         <v>0</v>
@@ -8911,7 +8914,7 @@
         <v>3</v>
       </c>
       <c r="AP35">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ35">
         <v>1.18</v>
@@ -9941,10 +9944,10 @@
         <v>0</v>
       </c>
       <c r="AP40">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ40">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR40">
         <v>1.28</v>
@@ -11180,7 +11183,7 @@
         <v>2.59</v>
       </c>
       <c r="AQ46">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR46">
         <v>2.31</v>
@@ -14473,10 +14476,10 @@
         <v>0.5</v>
       </c>
       <c r="AP62">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ62">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR62">
         <v>0.99</v>
@@ -14682,7 +14685,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ63">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR63">
         <v>1.34</v>
@@ -15297,7 +15300,7 @@
         <v>2</v>
       </c>
       <c r="AP66">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ66">
         <v>1.82</v>
@@ -19623,7 +19626,7 @@
         <v>0.67</v>
       </c>
       <c r="AP87">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ87">
         <v>1.18</v>
@@ -20656,7 +20659,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ92">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR92">
         <v>1.63</v>
@@ -20862,7 +20865,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ93">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR93">
         <v>1.4</v>
@@ -21477,7 +21480,7 @@
         <v>0.67</v>
       </c>
       <c r="AP96">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ96">
         <v>0.59</v>
@@ -22304,7 +22307,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ100">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR100">
         <v>1.37</v>
@@ -23540,7 +23543,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ106">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR106">
         <v>1.67</v>
@@ -24567,7 +24570,7 @@
         <v>0.25</v>
       </c>
       <c r="AP111">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ111">
         <v>0.29</v>
@@ -25803,7 +25806,7 @@
         <v>1.5</v>
       </c>
       <c r="AP117">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ117">
         <v>1</v>
@@ -27245,7 +27248,7 @@
         <v>1</v>
       </c>
       <c r="AP124">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -27657,7 +27660,7 @@
         <v>1</v>
       </c>
       <c r="AP126">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ126">
         <v>0.59</v>
@@ -31162,7 +31165,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ143">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR143">
         <v>1.28</v>
@@ -31574,7 +31577,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ145">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR145">
         <v>1.49</v>
@@ -32189,7 +32192,7 @@
         <v>0.33</v>
       </c>
       <c r="AP148">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ148">
         <v>0.47</v>
@@ -32807,7 +32810,7 @@
         <v>1.33</v>
       </c>
       <c r="AP151">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ151">
         <v>1</v>
@@ -34252,7 +34255,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ158">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR158">
         <v>1.74</v>
@@ -34664,7 +34667,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ160">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR160">
         <v>1.05</v>
@@ -37133,7 +37136,7 @@
         <v>1</v>
       </c>
       <c r="AP172">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ172">
         <v>1.18</v>
@@ -37339,7 +37342,7 @@
         <v>0.5</v>
       </c>
       <c r="AP173">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ173">
         <v>1.12</v>
@@ -40020,7 +40023,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ186">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR186">
         <v>1.39</v>
@@ -40432,7 +40435,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ188">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR188">
         <v>1.01</v>
@@ -41665,7 +41668,7 @@
         <v>0.43</v>
       </c>
       <c r="AP194">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ194">
         <v>0.88</v>
@@ -43107,7 +43110,7 @@
         <v>0.86</v>
       </c>
       <c r="AP201">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ201">
         <v>1.06</v>
@@ -44346,7 +44349,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ207">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR207">
         <v>1.61</v>
@@ -45785,7 +45788,7 @@
         <v>1.67</v>
       </c>
       <c r="AP214">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ214">
         <v>1.94</v>
@@ -46200,7 +46203,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ216">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR216">
         <v>1.41</v>
@@ -49496,7 +49499,7 @@
         <v>2.59</v>
       </c>
       <c r="AQ232">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR232">
         <v>1.9</v>
@@ -49905,7 +49908,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP234">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ234">
         <v>0.88</v>
@@ -51144,7 +51147,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ240">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR240">
         <v>1.9</v>
@@ -51759,7 +51762,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP243">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ243">
         <v>0.71</v>
@@ -54437,7 +54440,7 @@
         <v>1.73</v>
       </c>
       <c r="AP256">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ256">
         <v>2</v>
@@ -55058,7 +55061,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ259">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR259">
         <v>1.48</v>
@@ -55882,7 +55885,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ263">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR263">
         <v>1.21</v>
@@ -57939,7 +57942,7 @@
         <v>1.4</v>
       </c>
       <c r="AP273">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ273">
         <v>1.82</v>
@@ -59175,7 +59178,7 @@
         <v>1.58</v>
       </c>
       <c r="AP279">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ279">
         <v>1.53</v>
@@ -59590,7 +59593,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ281">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR281">
         <v>1.28</v>
@@ -62265,7 +62268,7 @@
         <v>0.83</v>
       </c>
       <c r="AP294">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ294">
         <v>1.18</v>
@@ -62680,7 +62683,7 @@
         <v>0.76</v>
       </c>
       <c r="AQ296">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR296">
         <v>1.35</v>
@@ -63089,7 +63092,7 @@
         <v>0.15</v>
       </c>
       <c r="AP298">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ298">
         <v>0.29</v>
@@ -65561,7 +65564,7 @@
         <v>0.67</v>
       </c>
       <c r="AP310">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ310">
         <v>0.9399999999999999</v>
@@ -66385,7 +66388,7 @@
         <v>1.08</v>
       </c>
       <c r="AP314">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ314">
         <v>1</v>
@@ -66800,7 +66803,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ316">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR316">
         <v>1.34</v>
@@ -68242,7 +68245,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ323">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR323">
         <v>1.4</v>
@@ -71126,7 +71129,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ337">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR337">
         <v>1.48</v>
@@ -71535,7 +71538,7 @@
         <v>0.54</v>
       </c>
       <c r="AP339">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ339">
         <v>0.53</v>
@@ -72771,7 +72774,7 @@
         <v>0.5</v>
       </c>
       <c r="AP345">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ345">
         <v>0.47</v>
@@ -73186,7 +73189,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ347">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR347">
         <v>1.26</v>
@@ -79572,7 +79575,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ378">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR378">
         <v>1.43</v>
@@ -79984,7 +79987,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ380">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR380">
         <v>1.49</v>
@@ -80805,7 +80808,7 @@
         <v>1</v>
       </c>
       <c r="AP384">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AQ384">
         <v>1</v>
@@ -81217,7 +81220,7 @@
         <v>1.06</v>
       </c>
       <c r="AP386">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="AQ386">
         <v>1</v>
@@ -83280,7 +83283,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ396">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AR396">
         <v>1.51</v>
@@ -83692,7 +83695,7 @@
         <v>2.12</v>
       </c>
       <c r="AQ398">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AR398">
         <v>1.61</v>
@@ -85622,6 +85625,418 @@
       </c>
       <c r="BP407">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="408" spans="1:68">
+      <c r="A408" s="1">
+        <v>407</v>
+      </c>
+      <c r="B408">
+        <v>7479105</v>
+      </c>
+      <c r="C408" t="s">
+        <v>68</v>
+      </c>
+      <c r="D408" t="s">
+        <v>69</v>
+      </c>
+      <c r="E408" s="2">
+        <v>45713.69791666666</v>
+      </c>
+      <c r="F408">
+        <v>31</v>
+      </c>
+      <c r="G408" t="s">
+        <v>78</v>
+      </c>
+      <c r="H408" t="s">
+        <v>77</v>
+      </c>
+      <c r="I408">
+        <v>0</v>
+      </c>
+      <c r="J408">
+        <v>0</v>
+      </c>
+      <c r="K408">
+        <v>0</v>
+      </c>
+      <c r="L408">
+        <v>1</v>
+      </c>
+      <c r="M408">
+        <v>0</v>
+      </c>
+      <c r="N408">
+        <v>1</v>
+      </c>
+      <c r="O408" t="s">
+        <v>113</v>
+      </c>
+      <c r="P408" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q408">
+        <v>3.1</v>
+      </c>
+      <c r="R408">
+        <v>2.1</v>
+      </c>
+      <c r="S408">
+        <v>3.6</v>
+      </c>
+      <c r="T408">
+        <v>1.45</v>
+      </c>
+      <c r="U408">
+        <v>2.8</v>
+      </c>
+      <c r="V408">
+        <v>3</v>
+      </c>
+      <c r="W408">
+        <v>1.38</v>
+      </c>
+      <c r="X408">
+        <v>7.5</v>
+      </c>
+      <c r="Y408">
+        <v>1.08</v>
+      </c>
+      <c r="Z408">
+        <v>2.49</v>
+      </c>
+      <c r="AA408">
+        <v>3.29</v>
+      </c>
+      <c r="AB408">
+        <v>2.74</v>
+      </c>
+      <c r="AC408">
+        <v>1.07</v>
+      </c>
+      <c r="AD408">
+        <v>10</v>
+      </c>
+      <c r="AE408">
+        <v>1.33</v>
+      </c>
+      <c r="AF408">
+        <v>3.3</v>
+      </c>
+      <c r="AG408">
+        <v>1.77</v>
+      </c>
+      <c r="AH408">
+        <v>1.98</v>
+      </c>
+      <c r="AI408">
+        <v>1.78</v>
+      </c>
+      <c r="AJ408">
+        <v>2</v>
+      </c>
+      <c r="AK408">
+        <v>1.44</v>
+      </c>
+      <c r="AL408">
+        <v>1.3</v>
+      </c>
+      <c r="AM408">
+        <v>1.58</v>
+      </c>
+      <c r="AN408">
+        <v>1.31</v>
+      </c>
+      <c r="AO408">
+        <v>1.25</v>
+      </c>
+      <c r="AP408">
+        <v>1.41</v>
+      </c>
+      <c r="AQ408">
+        <v>1.18</v>
+      </c>
+      <c r="AR408">
+        <v>1.55</v>
+      </c>
+      <c r="AS408">
+        <v>1.26</v>
+      </c>
+      <c r="AT408">
+        <v>2.81</v>
+      </c>
+      <c r="AU408">
+        <v>6</v>
+      </c>
+      <c r="AV408">
+        <v>2</v>
+      </c>
+      <c r="AW408">
+        <v>3</v>
+      </c>
+      <c r="AX408">
+        <v>3</v>
+      </c>
+      <c r="AY408">
+        <v>10</v>
+      </c>
+      <c r="AZ408">
+        <v>7</v>
+      </c>
+      <c r="BA408">
+        <v>5</v>
+      </c>
+      <c r="BB408">
+        <v>3</v>
+      </c>
+      <c r="BC408">
+        <v>8</v>
+      </c>
+      <c r="BD408">
+        <v>1.75</v>
+      </c>
+      <c r="BE408">
+        <v>6.4</v>
+      </c>
+      <c r="BF408">
+        <v>2.3</v>
+      </c>
+      <c r="BG408">
+        <v>1.25</v>
+      </c>
+      <c r="BH408">
+        <v>3.4</v>
+      </c>
+      <c r="BI408">
+        <v>1.43</v>
+      </c>
+      <c r="BJ408">
+        <v>2.55</v>
+      </c>
+      <c r="BK408">
+        <v>1.72</v>
+      </c>
+      <c r="BL408">
+        <v>1.98</v>
+      </c>
+      <c r="BM408">
+        <v>2.12</v>
+      </c>
+      <c r="BN408">
+        <v>1.63</v>
+      </c>
+      <c r="BO408">
+        <v>2.65</v>
+      </c>
+      <c r="BP408">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="409" spans="1:68">
+      <c r="A409" s="1">
+        <v>408</v>
+      </c>
+      <c r="B409">
+        <v>7479112</v>
+      </c>
+      <c r="C409" t="s">
+        <v>68</v>
+      </c>
+      <c r="D409" t="s">
+        <v>69</v>
+      </c>
+      <c r="E409" s="2">
+        <v>45713.69791666666</v>
+      </c>
+      <c r="F409">
+        <v>31</v>
+      </c>
+      <c r="G409" t="s">
+        <v>75</v>
+      </c>
+      <c r="H409" t="s">
+        <v>79</v>
+      </c>
+      <c r="I409">
+        <v>1</v>
+      </c>
+      <c r="J409">
+        <v>1</v>
+      </c>
+      <c r="K409">
+        <v>2</v>
+      </c>
+      <c r="L409">
+        <v>1</v>
+      </c>
+      <c r="M409">
+        <v>3</v>
+      </c>
+      <c r="N409">
+        <v>4</v>
+      </c>
+      <c r="O409" t="s">
+        <v>188</v>
+      </c>
+      <c r="P409" t="s">
+        <v>468</v>
+      </c>
+      <c r="Q409">
+        <v>3.54</v>
+      </c>
+      <c r="R409">
+        <v>2.09</v>
+      </c>
+      <c r="S409">
+        <v>3.02</v>
+      </c>
+      <c r="T409">
+        <v>1.38</v>
+      </c>
+      <c r="U409">
+        <v>2.76</v>
+      </c>
+      <c r="V409">
+        <v>2.88</v>
+      </c>
+      <c r="W409">
+        <v>1.35</v>
+      </c>
+      <c r="X409">
+        <v>7.6</v>
+      </c>
+      <c r="Y409">
+        <v>1.03</v>
+      </c>
+      <c r="Z409">
+        <v>2.86</v>
+      </c>
+      <c r="AA409">
+        <v>3.32</v>
+      </c>
+      <c r="AB409">
+        <v>2.38</v>
+      </c>
+      <c r="AC409">
+        <v>1.01</v>
+      </c>
+      <c r="AD409">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AE409">
+        <v>1.28</v>
+      </c>
+      <c r="AF409">
+        <v>3.2</v>
+      </c>
+      <c r="AG409">
+        <v>1.98</v>
+      </c>
+      <c r="AH409">
+        <v>1.77</v>
+      </c>
+      <c r="AI409">
+        <v>1.76</v>
+      </c>
+      <c r="AJ409">
+        <v>1.95</v>
+      </c>
+      <c r="AK409">
+        <v>1.57</v>
+      </c>
+      <c r="AL409">
+        <v>1.32</v>
+      </c>
+      <c r="AM409">
+        <v>1.42</v>
+      </c>
+      <c r="AN409">
+        <v>1.38</v>
+      </c>
+      <c r="AO409">
+        <v>1.13</v>
+      </c>
+      <c r="AP409">
+        <v>1.29</v>
+      </c>
+      <c r="AQ409">
+        <v>1.24</v>
+      </c>
+      <c r="AR409">
+        <v>1.25</v>
+      </c>
+      <c r="AS409">
+        <v>1.53</v>
+      </c>
+      <c r="AT409">
+        <v>2.78</v>
+      </c>
+      <c r="AU409">
+        <v>4</v>
+      </c>
+      <c r="AV409">
+        <v>7</v>
+      </c>
+      <c r="AW409">
+        <v>8</v>
+      </c>
+      <c r="AX409">
+        <v>9</v>
+      </c>
+      <c r="AY409">
+        <v>14</v>
+      </c>
+      <c r="AZ409">
+        <v>18</v>
+      </c>
+      <c r="BA409">
+        <v>5</v>
+      </c>
+      <c r="BB409">
+        <v>1</v>
+      </c>
+      <c r="BC409">
+        <v>6</v>
+      </c>
+      <c r="BD409">
+        <v>1.98</v>
+      </c>
+      <c r="BE409">
+        <v>6.5</v>
+      </c>
+      <c r="BF409">
+        <v>1.98</v>
+      </c>
+      <c r="BG409">
+        <v>1.24</v>
+      </c>
+      <c r="BH409">
+        <v>3.55</v>
+      </c>
+      <c r="BI409">
+        <v>1.43</v>
+      </c>
+      <c r="BJ409">
+        <v>2.6</v>
+      </c>
+      <c r="BK409">
+        <v>1.7</v>
+      </c>
+      <c r="BL409">
+        <v>2.02</v>
+      </c>
+      <c r="BM409">
+        <v>2.08</v>
+      </c>
+      <c r="BN409">
+        <v>1.65</v>
+      </c>
+      <c r="BO409">
+        <v>2.65</v>
+      </c>
+      <c r="BP409">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -85567,16 +85567,16 @@
         <v>9</v>
       </c>
       <c r="AW407">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AX407">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AY407">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ407">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BA407">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2516" uniqueCount="469">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2522" uniqueCount="470">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1422,6 +1422,9 @@
   <si>
     <t>['20', '52', '73']</t>
   </si>
+  <si>
+    <t>['34', '71']</t>
+  </si>
 </sst>
 </file>
 
@@ -1782,7 +1785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP409"/>
+  <dimension ref="A1:BP410"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3767,7 +3770,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ10">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -4176,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ12">
         <v>0.29</v>
@@ -7060,7 +7063,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ26">
         <v>1.82</v>
@@ -10565,7 +10568,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ43">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR43">
         <v>1.59</v>
@@ -13243,7 +13246,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ56">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR56">
         <v>1.63</v>
@@ -13446,7 +13449,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ57">
         <v>1.06</v>
@@ -17566,7 +17569,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ77">
         <v>1.18</v>
@@ -17981,7 +17984,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ79">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR79">
         <v>1.74</v>
@@ -25394,7 +25397,7 @@
         <v>1.75</v>
       </c>
       <c r="AP115">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ115">
         <v>1.94</v>
@@ -26633,7 +26636,7 @@
         <v>0.76</v>
       </c>
       <c r="AQ121">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR121">
         <v>1.53</v>
@@ -26836,7 +26839,7 @@
         <v>0.6</v>
       </c>
       <c r="AP122">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ122">
         <v>1</v>
@@ -28693,7 +28696,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ131">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR131">
         <v>1.3</v>
@@ -33225,7 +33228,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ153">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR153">
         <v>1.73</v>
@@ -33428,7 +33431,7 @@
         <v>0.5</v>
       </c>
       <c r="AP154">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ154">
         <v>0.9399999999999999</v>
@@ -34458,7 +34461,7 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ159">
         <v>1</v>
@@ -36315,7 +36318,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ168">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR168">
         <v>1.18</v>
@@ -39814,7 +39817,7 @@
         <v>0.43</v>
       </c>
       <c r="AP185">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ185">
         <v>0.71</v>
@@ -40229,7 +40232,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ187">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR187">
         <v>1.36</v>
@@ -43731,7 +43734,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ204">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR204">
         <v>1.53</v>
@@ -46612,7 +46615,7 @@
         <v>0.5</v>
       </c>
       <c r="AP218">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ218">
         <v>0.88</v>
@@ -48466,7 +48469,7 @@
         <v>1.33</v>
       </c>
       <c r="AP227">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ227">
         <v>1.12</v>
@@ -51971,7 +51974,7 @@
         <v>1.35</v>
       </c>
       <c r="AQ244">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR244">
         <v>1.43</v>
@@ -53410,7 +53413,7 @@
         <v>0.8</v>
       </c>
       <c r="AP251">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ251">
         <v>0.76</v>
@@ -57121,7 +57124,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ269">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR269">
         <v>1.31</v>
@@ -59181,7 +59184,7 @@
         <v>1.29</v>
       </c>
       <c r="AQ279">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR279">
         <v>1.22</v>
@@ -61444,7 +61447,7 @@
         <v>0.58</v>
       </c>
       <c r="AP290">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ290">
         <v>0.47</v>
@@ -63710,7 +63713,7 @@
         <v>0.82</v>
       </c>
       <c r="AP301">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ301">
         <v>1.18</v>
@@ -66185,7 +66188,7 @@
         <v>2.06</v>
       </c>
       <c r="AQ313">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR313">
         <v>1.47</v>
@@ -69481,7 +69484,7 @@
         <v>1.24</v>
       </c>
       <c r="AQ329">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR329">
         <v>1.39</v>
@@ -70714,7 +70717,7 @@
         <v>1</v>
       </c>
       <c r="AP335">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ335">
         <v>1</v>
@@ -74834,7 +74837,7 @@
         <v>0.29</v>
       </c>
       <c r="AP355">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ355">
         <v>0.29</v>
@@ -76073,7 +76076,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ361">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR361">
         <v>1.49</v>
@@ -81838,7 +81841,7 @@
         <v>1.06</v>
       </c>
       <c r="AP389">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AQ389">
         <v>1.18</v>
@@ -82665,7 +82668,7 @@
         <v>2.59</v>
       </c>
       <c r="AQ393">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="AR393">
         <v>1.99</v>
@@ -86037,6 +86040,212 @@
       </c>
       <c r="BP409">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="410" spans="1:68">
+      <c r="A410" s="1">
+        <v>409</v>
+      </c>
+      <c r="B410">
+        <v>7479161</v>
+      </c>
+      <c r="C410" t="s">
+        <v>68</v>
+      </c>
+      <c r="D410" t="s">
+        <v>69</v>
+      </c>
+      <c r="E410" s="2">
+        <v>45716.70833333334</v>
+      </c>
+      <c r="F410">
+        <v>35</v>
+      </c>
+      <c r="G410" t="s">
+        <v>80</v>
+      </c>
+      <c r="H410" t="s">
+        <v>93</v>
+      </c>
+      <c r="I410">
+        <v>0</v>
+      </c>
+      <c r="J410">
+        <v>1</v>
+      </c>
+      <c r="K410">
+        <v>1</v>
+      </c>
+      <c r="L410">
+        <v>1</v>
+      </c>
+      <c r="M410">
+        <v>2</v>
+      </c>
+      <c r="N410">
+        <v>3</v>
+      </c>
+      <c r="O410" t="s">
+        <v>132</v>
+      </c>
+      <c r="P410" t="s">
+        <v>469</v>
+      </c>
+      <c r="Q410">
+        <v>3.6</v>
+      </c>
+      <c r="R410">
+        <v>2.05</v>
+      </c>
+      <c r="S410">
+        <v>3.2</v>
+      </c>
+      <c r="T410">
+        <v>1.44</v>
+      </c>
+      <c r="U410">
+        <v>2.63</v>
+      </c>
+      <c r="V410">
+        <v>3.25</v>
+      </c>
+      <c r="W410">
+        <v>1.33</v>
+      </c>
+      <c r="X410">
+        <v>10</v>
+      </c>
+      <c r="Y410">
+        <v>1.06</v>
+      </c>
+      <c r="Z410">
+        <v>3.23</v>
+      </c>
+      <c r="AA410">
+        <v>3.28</v>
+      </c>
+      <c r="AB410">
+        <v>2.19</v>
+      </c>
+      <c r="AC410">
+        <v>1.07</v>
+      </c>
+      <c r="AD410">
+        <v>10</v>
+      </c>
+      <c r="AE410">
+        <v>1.36</v>
+      </c>
+      <c r="AF410">
+        <v>3.2</v>
+      </c>
+      <c r="AG410">
+        <v>1.87</v>
+      </c>
+      <c r="AH410">
+        <v>1.87</v>
+      </c>
+      <c r="AI410">
+        <v>1.83</v>
+      </c>
+      <c r="AJ410">
+        <v>1.83</v>
+      </c>
+      <c r="AK410">
+        <v>1.53</v>
+      </c>
+      <c r="AL410">
+        <v>1.31</v>
+      </c>
+      <c r="AM410">
+        <v>1.41</v>
+      </c>
+      <c r="AN410">
+        <v>1.29</v>
+      </c>
+      <c r="AO410">
+        <v>1.53</v>
+      </c>
+      <c r="AP410">
+        <v>1.22</v>
+      </c>
+      <c r="AQ410">
+        <v>1.61</v>
+      </c>
+      <c r="AR410">
+        <v>1.51</v>
+      </c>
+      <c r="AS410">
+        <v>1.36</v>
+      </c>
+      <c r="AT410">
+        <v>2.87</v>
+      </c>
+      <c r="AU410">
+        <v>5</v>
+      </c>
+      <c r="AV410">
+        <v>5</v>
+      </c>
+      <c r="AW410">
+        <v>5</v>
+      </c>
+      <c r="AX410">
+        <v>8</v>
+      </c>
+      <c r="AY410">
+        <v>12</v>
+      </c>
+      <c r="AZ410">
+        <v>17</v>
+      </c>
+      <c r="BA410">
+        <v>5</v>
+      </c>
+      <c r="BB410">
+        <v>9</v>
+      </c>
+      <c r="BC410">
+        <v>14</v>
+      </c>
+      <c r="BD410">
+        <v>1.78</v>
+      </c>
+      <c r="BE410">
+        <v>6.75</v>
+      </c>
+      <c r="BF410">
+        <v>2.23</v>
+      </c>
+      <c r="BG410">
+        <v>1.19</v>
+      </c>
+      <c r="BH410">
+        <v>4.1</v>
+      </c>
+      <c r="BI410">
+        <v>1.33</v>
+      </c>
+      <c r="BJ410">
+        <v>2.95</v>
+      </c>
+      <c r="BK410">
+        <v>1.55</v>
+      </c>
+      <c r="BL410">
+        <v>2.28</v>
+      </c>
+      <c r="BM410">
+        <v>1.88</v>
+      </c>
+      <c r="BN410">
+        <v>1.81</v>
+      </c>
+      <c r="BO410">
+        <v>2.33</v>
+      </c>
+      <c r="BP410">
+        <v>1.52</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2654" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2660" uniqueCount="484">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1078,6 +1078,9 @@
     <t>['2', '77']</t>
   </si>
   <si>
+    <t>['61']</t>
+  </si>
+  <si>
     <t>['67', '88']</t>
   </si>
   <si>
@@ -1391,9 +1394,6 @@
   </si>
   <si>
     <t>['6', '63', '88']</t>
-  </si>
-  <si>
-    <t>['61']</t>
   </si>
   <si>
     <t>['58', '90']</t>
@@ -1827,7 +1827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP432"/>
+  <dimension ref="A1:BP433"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2083,7 +2083,7 @@
         <v>94</v>
       </c>
       <c r="P2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q2">
         <v>2.88</v>
@@ -2289,7 +2289,7 @@
         <v>95</v>
       </c>
       <c r="P3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q3">
         <v>3.5</v>
@@ -2495,7 +2495,7 @@
         <v>96</v>
       </c>
       <c r="P4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q4">
         <v>3.25</v>
@@ -2907,7 +2907,7 @@
         <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q6">
         <v>3.1</v>
@@ -3319,7 +3319,7 @@
         <v>100</v>
       </c>
       <c r="P8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q8">
         <v>1.83</v>
@@ -3731,7 +3731,7 @@
         <v>95</v>
       </c>
       <c r="P10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q10">
         <v>3.6</v>
@@ -4349,7 +4349,7 @@
         <v>104</v>
       </c>
       <c r="P13" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4555,7 +4555,7 @@
         <v>105</v>
       </c>
       <c r="P14" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q14">
         <v>2.2</v>
@@ -4842,7 +4842,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ15">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -5251,7 +5251,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ17">
         <v>0.28</v>
@@ -5379,7 +5379,7 @@
         <v>107</v>
       </c>
       <c r="P18" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q18">
         <v>2.4</v>
@@ -5997,7 +5997,7 @@
         <v>110</v>
       </c>
       <c r="P21" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q21">
         <v>2.75</v>
@@ -6203,7 +6203,7 @@
         <v>111</v>
       </c>
       <c r="P22" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q22">
         <v>2.6</v>
@@ -7027,7 +7027,7 @@
         <v>95</v>
       </c>
       <c r="P26" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q26">
         <v>4.5</v>
@@ -7108,7 +7108,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ26">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR26">
         <v>2.62</v>
@@ -7851,7 +7851,7 @@
         <v>117</v>
       </c>
       <c r="P30" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q30">
         <v>2</v>
@@ -8881,7 +8881,7 @@
         <v>122</v>
       </c>
       <c r="P35" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q35">
         <v>3.25</v>
@@ -9087,7 +9087,7 @@
         <v>123</v>
       </c>
       <c r="P36" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q36">
         <v>3.25</v>
@@ -9499,7 +9499,7 @@
         <v>125</v>
       </c>
       <c r="P38" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q38">
         <v>2.4</v>
@@ -9911,7 +9911,7 @@
         <v>95</v>
       </c>
       <c r="P40" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q40">
         <v>4.5</v>
@@ -10117,7 +10117,7 @@
         <v>95</v>
       </c>
       <c r="P41" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q41">
         <v>2.4</v>
@@ -10529,7 +10529,7 @@
         <v>101</v>
       </c>
       <c r="P43" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="Q43">
         <v>4.33</v>
@@ -10607,7 +10607,7 @@
         <v>3</v>
       </c>
       <c r="AP43">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ43">
         <v>1.61</v>
@@ -11971,7 +11971,7 @@
         <v>95</v>
       </c>
       <c r="P50" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q50">
         <v>3.75</v>
@@ -13207,7 +13207,7 @@
         <v>135</v>
       </c>
       <c r="P56" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q56">
         <v>4.5</v>
@@ -14031,7 +14031,7 @@
         <v>96</v>
       </c>
       <c r="P60" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q60">
         <v>2</v>
@@ -14237,7 +14237,7 @@
         <v>95</v>
       </c>
       <c r="P61" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q61">
         <v>4.33</v>
@@ -14315,7 +14315,7 @@
         <v>3</v>
       </c>
       <c r="AP61">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ61">
         <v>1.17</v>
@@ -14443,7 +14443,7 @@
         <v>139</v>
       </c>
       <c r="P62" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q62">
         <v>2.6</v>
@@ -15267,7 +15267,7 @@
         <v>95</v>
       </c>
       <c r="P66" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q66">
         <v>5.5</v>
@@ -15348,7 +15348,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ66">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR66">
         <v>1.23</v>
@@ -16297,7 +16297,7 @@
         <v>147</v>
       </c>
       <c r="P71" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q71">
         <v>2.3</v>
@@ -16915,7 +16915,7 @@
         <v>149</v>
       </c>
       <c r="P74" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q74">
         <v>3.9</v>
@@ -17327,7 +17327,7 @@
         <v>151</v>
       </c>
       <c r="P76" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q76">
         <v>3.4</v>
@@ -17533,7 +17533,7 @@
         <v>152</v>
       </c>
       <c r="P77" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="Q77">
         <v>3.75</v>
@@ -17945,7 +17945,7 @@
         <v>153</v>
       </c>
       <c r="P79" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q79">
         <v>3.25</v>
@@ -18357,7 +18357,7 @@
         <v>155</v>
       </c>
       <c r="P81" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q81">
         <v>2.63</v>
@@ -18847,7 +18847,7 @@
         <v>2.33</v>
       </c>
       <c r="AP83">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ83">
         <v>2.06</v>
@@ -20005,7 +20005,7 @@
         <v>160</v>
       </c>
       <c r="P89" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q89">
         <v>2.1</v>
@@ -20498,7 +20498,7 @@
         <v>1.72</v>
       </c>
       <c r="AQ91">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR91">
         <v>1.53</v>
@@ -20623,7 +20623,7 @@
         <v>162</v>
       </c>
       <c r="P92" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q92">
         <v>2.85</v>
@@ -21859,7 +21859,7 @@
         <v>165</v>
       </c>
       <c r="P98" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="Q98">
         <v>3.75</v>
@@ -21940,7 +21940,7 @@
         <v>2.17</v>
       </c>
       <c r="AQ98">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR98">
         <v>1.22</v>
@@ -22143,7 +22143,7 @@
         <v>0.25</v>
       </c>
       <c r="AP99">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ99">
         <v>0.5600000000000001</v>
@@ -22683,7 +22683,7 @@
         <v>119</v>
       </c>
       <c r="P102" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Q102">
         <v>2.5</v>
@@ -22889,7 +22889,7 @@
         <v>168</v>
       </c>
       <c r="P103" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q103">
         <v>3.75</v>
@@ -25361,7 +25361,7 @@
         <v>95</v>
       </c>
       <c r="P115" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q115">
         <v>3.4</v>
@@ -25567,7 +25567,7 @@
         <v>178</v>
       </c>
       <c r="P116" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q116">
         <v>2.4</v>
@@ -25979,7 +25979,7 @@
         <v>95</v>
       </c>
       <c r="P118" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="Q118">
         <v>2.3</v>
@@ -27009,7 +27009,7 @@
         <v>182</v>
       </c>
       <c r="P123" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q123">
         <v>3.4</v>
@@ -27215,7 +27215,7 @@
         <v>183</v>
       </c>
       <c r="P124" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q124">
         <v>3</v>
@@ -28657,7 +28657,7 @@
         <v>187</v>
       </c>
       <c r="P131" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q131">
         <v>3.1</v>
@@ -29275,7 +29275,7 @@
         <v>162</v>
       </c>
       <c r="P134" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="Q134">
         <v>3.4</v>
@@ -29353,7 +29353,7 @@
         <v>0.8</v>
       </c>
       <c r="AP134">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ134">
         <v>1.44</v>
@@ -29562,7 +29562,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ135">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR135">
         <v>1.5</v>
@@ -29687,7 +29687,7 @@
         <v>190</v>
       </c>
       <c r="P136" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Q136">
         <v>3</v>
@@ -30923,7 +30923,7 @@
         <v>194</v>
       </c>
       <c r="P142" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q142">
         <v>3.25</v>
@@ -31541,7 +31541,7 @@
         <v>196</v>
       </c>
       <c r="P145" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q145">
         <v>3.2</v>
@@ -31747,7 +31747,7 @@
         <v>197</v>
       </c>
       <c r="P146" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q146">
         <v>3.1</v>
@@ -31953,7 +31953,7 @@
         <v>198</v>
       </c>
       <c r="P147" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="Q147">
         <v>3.4</v>
@@ -32365,7 +32365,7 @@
         <v>95</v>
       </c>
       <c r="P149" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q149">
         <v>3.5</v>
@@ -32571,7 +32571,7 @@
         <v>200</v>
       </c>
       <c r="P150" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q150">
         <v>2.25</v>
@@ -32983,7 +32983,7 @@
         <v>132</v>
       </c>
       <c r="P152" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33395,7 +33395,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q154">
         <v>2.6</v>
@@ -33807,7 +33807,7 @@
         <v>95</v>
       </c>
       <c r="P156" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q156">
         <v>2.25</v>
@@ -34219,7 +34219,7 @@
         <v>204</v>
       </c>
       <c r="P158" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q158">
         <v>4.75</v>
@@ -34837,7 +34837,7 @@
         <v>206</v>
       </c>
       <c r="P161" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q161">
         <v>3.75</v>
@@ -35536,7 +35536,7 @@
         <v>1.39</v>
       </c>
       <c r="AQ164">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR164">
         <v>1.43</v>
@@ -35661,7 +35661,7 @@
         <v>95</v>
       </c>
       <c r="P165" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q165">
         <v>2.75</v>
@@ -37309,7 +37309,7 @@
         <v>172</v>
       </c>
       <c r="P173" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q173">
         <v>3</v>
@@ -37721,7 +37721,7 @@
         <v>214</v>
       </c>
       <c r="P175" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q175">
         <v>2.63</v>
@@ -38005,7 +38005,7 @@
         <v>0.5</v>
       </c>
       <c r="AP176">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ176">
         <v>0.83</v>
@@ -38133,7 +38133,7 @@
         <v>216</v>
       </c>
       <c r="P177" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38751,7 +38751,7 @@
         <v>142</v>
       </c>
       <c r="P180" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q180">
         <v>3.75</v>
@@ -39163,7 +39163,7 @@
         <v>219</v>
       </c>
       <c r="P182" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q182">
         <v>3.4</v>
@@ -39575,7 +39575,7 @@
         <v>220</v>
       </c>
       <c r="P184" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q184">
         <v>3.2</v>
@@ -40399,7 +40399,7 @@
         <v>223</v>
       </c>
       <c r="P188" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q188">
         <v>5.5</v>
@@ -41017,7 +41017,7 @@
         <v>225</v>
       </c>
       <c r="P191" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q191">
         <v>2.5</v>
@@ -41223,7 +41223,7 @@
         <v>226</v>
       </c>
       <c r="P192" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q192">
         <v>5</v>
@@ -41304,7 +41304,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ192">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR192">
         <v>1.35</v>
@@ -42047,7 +42047,7 @@
         <v>95</v>
       </c>
       <c r="P196" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q196">
         <v>3</v>
@@ -43077,7 +43077,7 @@
         <v>95</v>
       </c>
       <c r="P201" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q201">
         <v>2.6</v>
@@ -44313,7 +44313,7 @@
         <v>233</v>
       </c>
       <c r="P207" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q207">
         <v>2.05</v>
@@ -44600,7 +44600,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ208">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR208">
         <v>1.36</v>
@@ -44931,7 +44931,7 @@
         <v>234</v>
       </c>
       <c r="P210" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q210">
         <v>3.1</v>
@@ -45137,7 +45137,7 @@
         <v>235</v>
       </c>
       <c r="P211" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q211">
         <v>2.38</v>
@@ -45549,7 +45549,7 @@
         <v>237</v>
       </c>
       <c r="P213" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q213">
         <v>2.4</v>
@@ -45755,7 +45755,7 @@
         <v>95</v>
       </c>
       <c r="P214" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q214">
         <v>3.75</v>
@@ -45961,7 +45961,7 @@
         <v>178</v>
       </c>
       <c r="P215" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q215">
         <v>3.2</v>
@@ -47481,7 +47481,7 @@
         <v>1.33</v>
       </c>
       <c r="AP222">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ222">
         <v>1.11</v>
@@ -47815,7 +47815,7 @@
         <v>244</v>
       </c>
       <c r="P224" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Q224">
         <v>2.88</v>
@@ -48021,7 +48021,7 @@
         <v>245</v>
       </c>
       <c r="P225" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="Q225">
         <v>3.2</v>
@@ -48717,7 +48717,7 @@
         <v>0.9</v>
       </c>
       <c r="AP228">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ228">
         <v>1</v>
@@ -48845,7 +48845,7 @@
         <v>246</v>
       </c>
       <c r="P229" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="Q229">
         <v>4</v>
@@ -49875,7 +49875,7 @@
         <v>95</v>
       </c>
       <c r="P234" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="Q234">
         <v>2.88</v>
@@ -50986,7 +50986,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ239">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR239">
         <v>1.26</v>
@@ -51111,7 +51111,7 @@
         <v>252</v>
       </c>
       <c r="P240" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q240">
         <v>2.5</v>
@@ -51729,7 +51729,7 @@
         <v>253</v>
       </c>
       <c r="P243" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Q243">
         <v>3.1</v>
@@ -51935,7 +51935,7 @@
         <v>254</v>
       </c>
       <c r="P244" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q244">
         <v>3.5</v>
@@ -52347,7 +52347,7 @@
         <v>244</v>
       </c>
       <c r="P246" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q246">
         <v>3.6</v>
@@ -52965,7 +52965,7 @@
         <v>131</v>
       </c>
       <c r="P249" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q249">
         <v>3.5</v>
@@ -53867,7 +53867,7 @@
         <v>0.91</v>
       </c>
       <c r="AP253">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ253">
         <v>1.28</v>
@@ -53995,7 +53995,7 @@
         <v>262</v>
       </c>
       <c r="P254" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q254">
         <v>2.5</v>
@@ -55025,7 +55025,7 @@
         <v>266</v>
       </c>
       <c r="P259" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q259">
         <v>5.5</v>
@@ -55231,7 +55231,7 @@
         <v>267</v>
       </c>
       <c r="P260" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q260">
         <v>3.25</v>
@@ -55643,7 +55643,7 @@
         <v>269</v>
       </c>
       <c r="P262" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q262">
         <v>3.5</v>
@@ -56261,7 +56261,7 @@
         <v>95</v>
       </c>
       <c r="P265" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q265">
         <v>3.2</v>
@@ -56467,7 +56467,7 @@
         <v>271</v>
       </c>
       <c r="P266" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q266">
         <v>2.25</v>
@@ -57085,7 +57085,7 @@
         <v>274</v>
       </c>
       <c r="P269" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q269">
         <v>3.5</v>
@@ -57703,7 +57703,7 @@
         <v>277</v>
       </c>
       <c r="P272" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q272">
         <v>3.5</v>
@@ -57909,7 +57909,7 @@
         <v>95</v>
       </c>
       <c r="P273" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q273">
         <v>6</v>
@@ -57990,7 +57990,7 @@
         <v>1.28</v>
       </c>
       <c r="AQ273">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR273">
         <v>1.28</v>
@@ -58527,7 +58527,7 @@
         <v>279</v>
       </c>
       <c r="P276" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q276">
         <v>2.5</v>
@@ -58939,7 +58939,7 @@
         <v>281</v>
       </c>
       <c r="P278" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Q278">
         <v>2.6</v>
@@ -60256,7 +60256,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ284">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR284">
         <v>1.42</v>
@@ -60793,7 +60793,7 @@
         <v>285</v>
       </c>
       <c r="P287" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q287">
         <v>3.75</v>
@@ -61205,7 +61205,7 @@
         <v>286</v>
       </c>
       <c r="P289" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q289">
         <v>2.38</v>
@@ -61411,7 +61411,7 @@
         <v>287</v>
       </c>
       <c r="P290" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q290">
         <v>2.6</v>
@@ -61695,7 +61695,7 @@
         <v>1.17</v>
       </c>
       <c r="AP291">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ291">
         <v>1</v>
@@ -62235,7 +62235,7 @@
         <v>289</v>
       </c>
       <c r="P294" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q294">
         <v>3.4</v>
@@ -62853,7 +62853,7 @@
         <v>290</v>
       </c>
       <c r="P297" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q297">
         <v>3.25</v>
@@ -63677,7 +63677,7 @@
         <v>291</v>
       </c>
       <c r="P301" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q301">
         <v>3</v>
@@ -63883,7 +63883,7 @@
         <v>204</v>
       </c>
       <c r="P302" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q302">
         <v>2.5</v>
@@ -64295,7 +64295,7 @@
         <v>293</v>
       </c>
       <c r="P304" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q304">
         <v>3.75</v>
@@ -64501,7 +64501,7 @@
         <v>294</v>
       </c>
       <c r="P305" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q305">
         <v>6.5</v>
@@ -64582,7 +64582,7 @@
         <v>0.89</v>
       </c>
       <c r="AQ305">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR305">
         <v>1.29</v>
@@ -64913,7 +64913,7 @@
         <v>200</v>
       </c>
       <c r="P307" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q307">
         <v>2.2</v>
@@ -65531,7 +65531,7 @@
         <v>231</v>
       </c>
       <c r="P310" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q310">
         <v>2.88</v>
@@ -67591,7 +67591,7 @@
         <v>95</v>
       </c>
       <c r="P320" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="Q320">
         <v>3.1</v>
@@ -68287,7 +68287,7 @@
         <v>1.5</v>
       </c>
       <c r="AP323">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ323">
         <v>1.17</v>
@@ -68621,7 +68621,7 @@
         <v>302</v>
       </c>
       <c r="P325" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Q325">
         <v>2.5</v>
@@ -68827,7 +68827,7 @@
         <v>303</v>
       </c>
       <c r="P326" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q326">
         <v>3</v>
@@ -69239,7 +69239,7 @@
         <v>296</v>
       </c>
       <c r="P328" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q328">
         <v>3.5</v>
@@ -69651,7 +69651,7 @@
         <v>95</v>
       </c>
       <c r="P330" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q330">
         <v>3.4</v>
@@ -69857,7 +69857,7 @@
         <v>305</v>
       </c>
       <c r="P331" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q331">
         <v>2.88</v>
@@ -70063,7 +70063,7 @@
         <v>306</v>
       </c>
       <c r="P332" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q332">
         <v>2.63</v>
@@ -70475,7 +70475,7 @@
         <v>308</v>
       </c>
       <c r="P334" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q334">
         <v>3.1</v>
@@ -70553,7 +70553,7 @@
         <v>0.77</v>
       </c>
       <c r="AP334">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ334">
         <v>0.72</v>
@@ -70681,7 +70681,7 @@
         <v>309</v>
       </c>
       <c r="P335" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q335">
         <v>3</v>
@@ -70887,7 +70887,7 @@
         <v>95</v>
       </c>
       <c r="P336" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q336">
         <v>5.5</v>
@@ -71093,7 +71093,7 @@
         <v>95</v>
       </c>
       <c r="P337" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q337">
         <v>2.2</v>
@@ -71299,7 +71299,7 @@
         <v>95</v>
       </c>
       <c r="P338" t="s">
-        <v>459</v>
+        <v>354</v>
       </c>
       <c r="Q338">
         <v>2.75</v>
@@ -72741,7 +72741,7 @@
         <v>314</v>
       </c>
       <c r="P345" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q345">
         <v>3</v>
@@ -73440,7 +73440,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ348">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR348">
         <v>1.45</v>
@@ -73643,7 +73643,7 @@
         <v>1</v>
       </c>
       <c r="AP349">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ349">
         <v>1.28</v>
@@ -73977,7 +73977,7 @@
         <v>95</v>
       </c>
       <c r="P351" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q351">
         <v>3.1</v>
@@ -74595,7 +74595,7 @@
         <v>95</v>
       </c>
       <c r="P354" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Q354">
         <v>4.33</v>
@@ -74801,7 +74801,7 @@
         <v>197</v>
       </c>
       <c r="P355" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q355">
         <v>2.75</v>
@@ -75909,7 +75909,7 @@
         <v>2.07</v>
       </c>
       <c r="AP360">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ360">
         <v>2</v>
@@ -76736,7 +76736,7 @@
         <v>1.83</v>
       </c>
       <c r="AQ364">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR364">
         <v>1.82</v>
@@ -77479,7 +77479,7 @@
         <v>326</v>
       </c>
       <c r="P368" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q368">
         <v>2.1</v>
@@ -77969,7 +77969,7 @@
         <v>0.73</v>
       </c>
       <c r="AP370">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ370">
         <v>0.67</v>
@@ -78590,7 +78590,7 @@
         <v>1.78</v>
       </c>
       <c r="AQ373">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR373">
         <v>1.42</v>
@@ -81187,7 +81187,7 @@
         <v>334</v>
       </c>
       <c r="P386" t="s">
-        <v>459</v>
+        <v>354</v>
       </c>
       <c r="Q386">
         <v>3</v>
@@ -82629,7 +82629,7 @@
         <v>336</v>
       </c>
       <c r="P393" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q393">
         <v>2.05</v>
@@ -83041,7 +83041,7 @@
         <v>104</v>
       </c>
       <c r="P395" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q395">
         <v>2.38</v>
@@ -84561,7 +84561,7 @@
         <v>1.13</v>
       </c>
       <c r="AP402">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AQ402">
         <v>1</v>
@@ -85594,7 +85594,7 @@
         <v>2.28</v>
       </c>
       <c r="AQ407">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AR407">
         <v>1.54</v>
@@ -90045,7 +90045,7 @@
         <v>353</v>
       </c>
       <c r="P429" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q429">
         <v>2.1</v>
@@ -90820,6 +90820,212 @@
       </c>
       <c r="BP432">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="433" spans="1:68">
+      <c r="A433" s="1">
+        <v>432</v>
+      </c>
+      <c r="B433">
+        <v>7479169</v>
+      </c>
+      <c r="C433" t="s">
+        <v>68</v>
+      </c>
+      <c r="D433" t="s">
+        <v>69</v>
+      </c>
+      <c r="E433" s="2">
+        <v>45725.375</v>
+      </c>
+      <c r="F433">
+        <v>36</v>
+      </c>
+      <c r="G433" t="s">
+        <v>85</v>
+      </c>
+      <c r="H433" t="s">
+        <v>76</v>
+      </c>
+      <c r="I433">
+        <v>0</v>
+      </c>
+      <c r="J433">
+        <v>0</v>
+      </c>
+      <c r="K433">
+        <v>0</v>
+      </c>
+      <c r="L433">
+        <v>1</v>
+      </c>
+      <c r="M433">
+        <v>0</v>
+      </c>
+      <c r="N433">
+        <v>1</v>
+      </c>
+      <c r="O433" t="s">
+        <v>354</v>
+      </c>
+      <c r="P433" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q433">
+        <v>7</v>
+      </c>
+      <c r="R433">
+        <v>2.4</v>
+      </c>
+      <c r="S433">
+        <v>1.91</v>
+      </c>
+      <c r="T433">
+        <v>1.33</v>
+      </c>
+      <c r="U433">
+        <v>3.25</v>
+      </c>
+      <c r="V433">
+        <v>2.63</v>
+      </c>
+      <c r="W433">
+        <v>1.44</v>
+      </c>
+      <c r="X433">
+        <v>6.5</v>
+      </c>
+      <c r="Y433">
+        <v>1.11</v>
+      </c>
+      <c r="Z433">
+        <v>6.6</v>
+      </c>
+      <c r="AA433">
+        <v>4.6</v>
+      </c>
+      <c r="AB433">
+        <v>1.43</v>
+      </c>
+      <c r="AC433">
+        <v>1.04</v>
+      </c>
+      <c r="AD433">
+        <v>10</v>
+      </c>
+      <c r="AE433">
+        <v>1.22</v>
+      </c>
+      <c r="AF433">
+        <v>4</v>
+      </c>
+      <c r="AG433">
+        <v>1.75</v>
+      </c>
+      <c r="AH433">
+        <v>2</v>
+      </c>
+      <c r="AI433">
+        <v>1.91</v>
+      </c>
+      <c r="AJ433">
+        <v>1.8</v>
+      </c>
+      <c r="AK433">
+        <v>2.75</v>
+      </c>
+      <c r="AL433">
+        <v>1.15</v>
+      </c>
+      <c r="AM433">
+        <v>1.1</v>
+      </c>
+      <c r="AN433">
+        <v>1.71</v>
+      </c>
+      <c r="AO433">
+        <v>1.82</v>
+      </c>
+      <c r="AP433">
+        <v>1.78</v>
+      </c>
+      <c r="AQ433">
+        <v>1.72</v>
+      </c>
+      <c r="AR433">
+        <v>1.53</v>
+      </c>
+      <c r="AS433">
+        <v>1.62</v>
+      </c>
+      <c r="AT433">
+        <v>3.15</v>
+      </c>
+      <c r="AU433">
+        <v>4</v>
+      </c>
+      <c r="AV433">
+        <v>5</v>
+      </c>
+      <c r="AW433">
+        <v>10</v>
+      </c>
+      <c r="AX433">
+        <v>10</v>
+      </c>
+      <c r="AY433">
+        <v>17</v>
+      </c>
+      <c r="AZ433">
+        <v>18</v>
+      </c>
+      <c r="BA433">
+        <v>7</v>
+      </c>
+      <c r="BB433">
+        <v>6</v>
+      </c>
+      <c r="BC433">
+        <v>13</v>
+      </c>
+      <c r="BD433">
+        <v>3.3</v>
+      </c>
+      <c r="BE433">
+        <v>7</v>
+      </c>
+      <c r="BF433">
+        <v>1.38</v>
+      </c>
+      <c r="BG433">
+        <v>1.22</v>
+      </c>
+      <c r="BH433">
+        <v>3.7</v>
+      </c>
+      <c r="BI433">
+        <v>1.4</v>
+      </c>
+      <c r="BJ433">
+        <v>2.7</v>
+      </c>
+      <c r="BK433">
+        <v>1.64</v>
+      </c>
+      <c r="BL433">
+        <v>2.1</v>
+      </c>
+      <c r="BM433">
+        <v>1.96</v>
+      </c>
+      <c r="BN433">
+        <v>1.73</v>
+      </c>
+      <c r="BO433">
+        <v>2.48</v>
+      </c>
+      <c r="BP433">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -93270,13 +93270,13 @@
         <v>8</v>
       </c>
       <c r="BA444">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB444">
         <v>0</v>
       </c>
       <c r="BC444">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD444">
         <v>1.38</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2798" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2804" uniqueCount="501">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1878,7 +1878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP456"/>
+  <dimension ref="A1:BP457"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -2421,7 +2421,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ3">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -4272,7 +4272,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ12">
         <v>0.42</v>
@@ -7156,7 +7156,7 @@
         <v>1</v>
       </c>
       <c r="AP26">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ26">
         <v>1.68</v>
@@ -9219,7 +9219,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ36">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR36">
         <v>1.57</v>
@@ -12103,7 +12103,7 @@
         <v>1</v>
       </c>
       <c r="AQ50">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR50">
         <v>1.4</v>
@@ -13542,7 +13542,7 @@
         <v>2</v>
       </c>
       <c r="AP57">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ57">
         <v>0.95</v>
@@ -17662,7 +17662,7 @@
         <v>3</v>
       </c>
       <c r="AP77">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ77">
         <v>1.16</v>
@@ -18901,7 +18901,7 @@
         <v>1.68</v>
       </c>
       <c r="AQ83">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR83">
         <v>1.1</v>
@@ -24463,7 +24463,7 @@
         <v>2.53</v>
       </c>
       <c r="AQ110">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR110">
         <v>1.76</v>
@@ -25490,7 +25490,7 @@
         <v>1.75</v>
       </c>
       <c r="AP115">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ115">
         <v>2.05</v>
@@ -26932,7 +26932,7 @@
         <v>0.6</v>
       </c>
       <c r="AP122">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ122">
         <v>0.95</v>
@@ -29201,7 +29201,7 @@
         <v>1.68</v>
       </c>
       <c r="AQ133">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR133">
         <v>1.89</v>
@@ -32497,7 +32497,7 @@
         <v>1.74</v>
       </c>
       <c r="AQ149">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR149">
         <v>1.31</v>
@@ -33524,7 +33524,7 @@
         <v>0.5</v>
       </c>
       <c r="AP154">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ154">
         <v>0.89</v>
@@ -34554,7 +34554,7 @@
         <v>1.14</v>
       </c>
       <c r="AP159">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ159">
         <v>0.95</v>
@@ -34969,7 +34969,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ161">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR161">
         <v>1.36</v>
@@ -39707,7 +39707,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ184">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR184">
         <v>1.86</v>
@@ -39910,7 +39910,7 @@
         <v>0.43</v>
       </c>
       <c r="AP185">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ185">
         <v>0.79</v>
@@ -46708,7 +46708,7 @@
         <v>0.5</v>
       </c>
       <c r="AP218">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ218">
         <v>0.84</v>
@@ -48153,7 +48153,7 @@
         <v>1.84</v>
       </c>
       <c r="AQ225">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR225">
         <v>1.38</v>
@@ -48562,7 +48562,7 @@
         <v>1.33</v>
       </c>
       <c r="AP227">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ227">
         <v>1</v>
@@ -49801,7 +49801,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ233">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR233">
         <v>1.32</v>
@@ -53506,7 +53506,7 @@
         <v>0.8</v>
       </c>
       <c r="AP251">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ251">
         <v>0.68</v>
@@ -54539,7 +54539,7 @@
         <v>1.26</v>
       </c>
       <c r="AQ256">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR256">
         <v>1.63</v>
@@ -61540,7 +61540,7 @@
         <v>0.58</v>
       </c>
       <c r="AP290">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ290">
         <v>0.58</v>
@@ -62985,7 +62985,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ297">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR297">
         <v>1.55</v>
@@ -63806,7 +63806,7 @@
         <v>0.82</v>
       </c>
       <c r="AP301">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ301">
         <v>1.21</v>
@@ -64427,7 +64427,7 @@
         <v>1.84</v>
       </c>
       <c r="AQ304">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR304">
         <v>1.45</v>
@@ -69371,7 +69371,7 @@
         <v>1.37</v>
       </c>
       <c r="AQ328">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR328">
         <v>1.45</v>
@@ -70810,7 +70810,7 @@
         <v>1</v>
       </c>
       <c r="AP335">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ335">
         <v>1.11</v>
@@ -74727,7 +74727,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ354">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR354">
         <v>1.38</v>
@@ -74930,7 +74930,7 @@
         <v>0.29</v>
       </c>
       <c r="AP355">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ355">
         <v>0.42</v>
@@ -81934,7 +81934,7 @@
         <v>1.06</v>
       </c>
       <c r="AP389">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ389">
         <v>1.21</v>
@@ -82555,7 +82555,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ392">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR392">
         <v>1.41</v>
@@ -86260,7 +86260,7 @@
         <v>1.53</v>
       </c>
       <c r="AP410">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AQ410">
         <v>1.53</v>
@@ -87293,7 +87293,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ415">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="AR415">
         <v>1.62</v>
@@ -95815,6 +95815,212 @@
       </c>
       <c r="BP456">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="457" spans="1:68">
+      <c r="A457" s="1">
+        <v>456</v>
+      </c>
+      <c r="B457">
+        <v>7479196</v>
+      </c>
+      <c r="C457" t="s">
+        <v>68</v>
+      </c>
+      <c r="D457" t="s">
+        <v>69</v>
+      </c>
+      <c r="E457" s="2">
+        <v>45732.39583333334</v>
+      </c>
+      <c r="F457">
+        <v>38</v>
+      </c>
+      <c r="G457" t="s">
+        <v>80</v>
+      </c>
+      <c r="H457" t="s">
+        <v>86</v>
+      </c>
+      <c r="I457">
+        <v>0</v>
+      </c>
+      <c r="J457">
+        <v>0</v>
+      </c>
+      <c r="K457">
+        <v>0</v>
+      </c>
+      <c r="L457">
+        <v>0</v>
+      </c>
+      <c r="M457">
+        <v>1</v>
+      </c>
+      <c r="N457">
+        <v>1</v>
+      </c>
+      <c r="O457" t="s">
+        <v>95</v>
+      </c>
+      <c r="P457" t="s">
+        <v>437</v>
+      </c>
+      <c r="Q457">
+        <v>3.25</v>
+      </c>
+      <c r="R457">
+        <v>2</v>
+      </c>
+      <c r="S457">
+        <v>3.6</v>
+      </c>
+      <c r="T457">
+        <v>1.5</v>
+      </c>
+      <c r="U457">
+        <v>2.5</v>
+      </c>
+      <c r="V457">
+        <v>3.4</v>
+      </c>
+      <c r="W457">
+        <v>1.3</v>
+      </c>
+      <c r="X457">
+        <v>10</v>
+      </c>
+      <c r="Y457">
+        <v>1.06</v>
+      </c>
+      <c r="Z457">
+        <v>2.61</v>
+      </c>
+      <c r="AA457">
+        <v>3.28</v>
+      </c>
+      <c r="AB457">
+        <v>2.61</v>
+      </c>
+      <c r="AC457">
+        <v>1.07</v>
+      </c>
+      <c r="AD457">
+        <v>8</v>
+      </c>
+      <c r="AE457">
+        <v>1.38</v>
+      </c>
+      <c r="AF457">
+        <v>3</v>
+      </c>
+      <c r="AG457">
+        <v>2.23</v>
+      </c>
+      <c r="AH457">
+        <v>1.58</v>
+      </c>
+      <c r="AI457">
+        <v>1.83</v>
+      </c>
+      <c r="AJ457">
+        <v>1.83</v>
+      </c>
+      <c r="AK457">
+        <v>1.42</v>
+      </c>
+      <c r="AL457">
+        <v>1.28</v>
+      </c>
+      <c r="AM457">
+        <v>1.5</v>
+      </c>
+      <c r="AN457">
+        <v>1.22</v>
+      </c>
+      <c r="AO457">
+        <v>2.06</v>
+      </c>
+      <c r="AP457">
+        <v>1.16</v>
+      </c>
+      <c r="AQ457">
+        <v>2.11</v>
+      </c>
+      <c r="AR457">
+        <v>1.5</v>
+      </c>
+      <c r="AS457">
+        <v>1.23</v>
+      </c>
+      <c r="AT457">
+        <v>2.73</v>
+      </c>
+      <c r="AU457">
+        <v>4</v>
+      </c>
+      <c r="AV457">
+        <v>3</v>
+      </c>
+      <c r="AW457">
+        <v>11</v>
+      </c>
+      <c r="AX457">
+        <v>7</v>
+      </c>
+      <c r="AY457">
+        <v>16</v>
+      </c>
+      <c r="AZ457">
+        <v>13</v>
+      </c>
+      <c r="BA457">
+        <v>7</v>
+      </c>
+      <c r="BB457">
+        <v>2</v>
+      </c>
+      <c r="BC457">
+        <v>9</v>
+      </c>
+      <c r="BD457">
+        <v>1.68</v>
+      </c>
+      <c r="BE457">
+        <v>6.95</v>
+      </c>
+      <c r="BF457">
+        <v>2.82</v>
+      </c>
+      <c r="BG457">
+        <v>1.14</v>
+      </c>
+      <c r="BH457">
+        <v>4.4</v>
+      </c>
+      <c r="BI457">
+        <v>1.3</v>
+      </c>
+      <c r="BJ457">
+        <v>2.97</v>
+      </c>
+      <c r="BK457">
+        <v>1.56</v>
+      </c>
+      <c r="BL457">
+        <v>2.21</v>
+      </c>
+      <c r="BM457">
+        <v>1.85</v>
+      </c>
+      <c r="BN457">
+        <v>1.85</v>
+      </c>
+      <c r="BO457">
+        <v>2.51</v>
+      </c>
+      <c r="BP457">
+        <v>1.44</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/England Championship_20242025.xlsx
@@ -99325,10 +99325,10 @@
         <v>6</v>
       </c>
       <c r="BB473">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC473">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD473">
         <v>1.75</v>
